--- a/Results/Hydrogen/hydrogen ozone depletion results.xlsx
+++ b/Results/Hydrogen/hydrogen ozone depletion results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.651706613531649e-07</v>
+        <v>6.651706613531691e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.145166026168658e-07</v>
+        <v>9.145166026168618e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.886506705675613e-07</v>
+        <v>3.886506705675614e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>9.145166026168658e-07</v>
+        <v>9.145166026168618e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>9.145166026168658e-07</v>
+        <v>9.145166026168618e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.17028791569359e-06</v>
+        <v>1.170287915693594e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583624398793716e-07</v>
+        <v>7.583624398793637e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.145166026168658e-07</v>
+        <v>9.145166026168618e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.710107555988503e-06</v>
+        <v>3.710107555988487e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.000979962771291e-07</v>
+        <v>8.000979962771264e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.2834470182992e-07</v>
+        <v>2.858056405541034e-06</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.146815117158659e-08</v>
+        <v>7.146815117158667e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.289208792807713e-08</v>
+        <v>7.289208792807718e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.289208792807711e-08</v>
+        <v>7.289208792807715e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.979649723668914e-08</v>
+        <v>6.979649723668912e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.242081946543861e-08</v>
+        <v>7.242081946543865e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>6.933311182666962e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.216353902409849e-07</v>
+        <v>8.736415401978694e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.990345209973994e-08</v>
+        <v>8.990345209973983e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.601949473044726e-08</v>
+        <v>8.601925736621136e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.79676060796246e-08</v>
+        <v>8.796760607962465e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.060176395991115e-08</v>
+        <v>9.060176395991121e-08</v>
       </c>
       <c r="G4" t="n">
         <v>1.220987756510045e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.310842478698964e-07</v>
+        <v>1.310842478698961e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247230978797541e-07</v>
+        <v>9.045186165855604e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.019489769561349e-08</v>
+        <v>9.019489769561394e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.686774140965345e-08</v>
+        <v>8.686774140965348e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.737489341768641e-08</v>
+        <v>8.737489341768635e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.558818217367325e-08</v>
+        <v>9.558818217367317e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.867588981244255e-08</v>
+        <v>9.86758898124425e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.55865646549511e-08</v>
+        <v>9.558656465495119e-08</v>
       </c>
       <c r="E5" t="n">
         <v>9.883174185922798e-08</v>
@@ -650,22 +650,22 @@
         <v>9.883174185922798e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.605156758369295e-08</v>
+        <v>9.605156758369288e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.558818217367325e-08</v>
+        <v>9.558818217367317e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.867588981244255e-08</v>
+        <v>9.86758898124425e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.558818217367325e-08</v>
+        <v>9.558818217367317e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.558818217367325e-08</v>
+        <v>9.558818217367317e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.558818217367325e-08</v>
+        <v>9.558818217367317e-08</v>
       </c>
     </row>
     <row r="6">
@@ -678,13 +678,13 @@
         <v>1.264874851429994e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.76896336753196e-07</v>
+        <v>1.768963367531962e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.834282182585278e-07</v>
+        <v>1.834282182585281e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.639813380197947e-07</v>
+        <v>1.639813380197949e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.311640775478343e-07</v>
@@ -693,19 +693,19 @@
         <v>1.741123613369167e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73648975926988e-07</v>
+        <v>1.736489759269884e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.767366835656664e-07</v>
+        <v>1.767366835656663e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.736582443555256e-07</v>
+        <v>1.736582443555255e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.256114362518046e-07</v>
+        <v>1.256114362518045e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.229130964863802e-07</v>
+        <v>2.229130964863803e-07</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.450186398299921e-07</v>
+        <v>3.450186398299922e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>4.290694212158804e-07</v>
+        <v>4.290694212158803e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>4.259817466955902e-07</v>
+        <v>4.259817466955903e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.224990991591154e-07</v>
+        <v>5.224990991591157e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>4.290694032919899e-07</v>
+        <v>4.290694032919893e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>4.264450989871306e-07</v>
+        <v>4.26445098987131e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>4.259817135771107e-07</v>
+        <v>4.25981713577111e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>4.290694212158804e-07</v>
+        <v>4.290694212158803e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>4.259817135771107e-07</v>
+        <v>4.25981713577111e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.240347432883454e-07</v>
+        <v>3.790714046110026e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>4.259817135771107e-07</v>
+        <v>4.25981713577111e-07</v>
       </c>
     </row>
     <row r="8">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.618847530618515e-07</v>
+        <v>9.61884753061853e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.196254784845937e-06</v>
@@ -770,22 +770,22 @@
         <v>1.196254784845937e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.519081480508304e-07</v>
+        <v>9.519081480508303e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.619239155570964e-07</v>
+        <v>9.619239155570966e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.196254784845937e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.010721441791359e-07</v>
+        <v>9.010721441791365e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.592999478218269e-07</v>
+        <v>9.592999478218274e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.212678980879043e-07</v>
+        <v>9.212678980879048e-07</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.546022317476415e-07</v>
+        <v>9.546022317476426e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.188324372544741e-06</v>
+        <v>1.18832437254474e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.571445271557736e-07</v>
+        <v>9.57144527155774e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.188324372544741e-06</v>
+        <v>1.18832437254474e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.188324372544741e-06</v>
+        <v>1.18832437254474e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.505259064902512e-07</v>
+        <v>9.505259064902517e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.546304251772352e-07</v>
+        <v>9.546304251772356e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.188324372544741e-06</v>
+        <v>1.18832437254474e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.298618767373186e-07</v>
+        <v>9.298618767373179e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.535502916159398e-07</v>
+        <v>9.5355029161594e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.380994068155212e-07</v>
+        <v>9.380994068155221e-07</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.475130347171895e-07</v>
+        <v>1.475130347171903e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.8383899116608e-07</v>
+        <v>6.838389911660797e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.439260096538659e-07</v>
+        <v>4.439260096538676e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8383899116608e-07</v>
+        <v>6.838389911660797e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8383899116608e-07</v>
+        <v>6.838389911660797e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.186226459757386e-07</v>
+        <v>6.186226459757308e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.675904616680547e-07</v>
+        <v>3.675904616680559e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8383899116608e-07</v>
+        <v>6.838389911660797e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.726095295142044e-06</v>
+        <v>2.726095295142048e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.446507954769084e-07</v>
+        <v>5.446507954769099e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.988645116904099e-07</v>
+        <v>1.753245644778113e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.444262604538299e-08</v>
+        <v>5.444262604538207e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.547887594298073e-08</v>
+        <v>5.547887594297947e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.547887594298073e-08</v>
+        <v>5.547887594297948e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.490934771142498e-08</v>
+        <v>5.490934771142485e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.756452016117613e-08</v>
+        <v>5.756452016117498e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.443971439316291e-08</v>
+        <v>5.443971439316314e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.78989496148292e-08</v>
+        <v>8.789894961482968e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.924052549912064e-08</v>
+        <v>6.924052549911983e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.577308971864911e-08</v>
+        <v>8.974800379447457e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.821874712574304e-08</v>
+        <v>6.821874712574174e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.968366978411768e-08</v>
+        <v>6.968366978411643e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.836858293309133e-08</v>
+        <v>6.698478010390939e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.45054914871892e-08</v>
+        <v>9.450549148719122e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.963995255366066e-08</v>
+        <v>6.963995255365937e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.221353818243024e-08</v>
+        <v>9.221353818243163e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.629819472816317e-08</v>
+        <v>6.629819472816416e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.665318060853867e-08</v>
+        <v>6.665318060853909e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.030873602672211e-08</v>
+        <v>7.030873602672543e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.343354179473747e-08</v>
+        <v>7.34335417947373e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.030817142273139e-08</v>
+        <v>7.030817142273467e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.279352432969962e-08</v>
+        <v>7.279352432970152e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.279352432969962e-08</v>
+        <v>7.279352432970152e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.077836934498386e-08</v>
+        <v>7.077836934498714e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.030873602672211e-08</v>
+        <v>7.030873602672543e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.343354179473747e-08</v>
+        <v>7.34335417947373e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.030873602672211e-08</v>
+        <v>7.030873602672543e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.030873602672211e-08</v>
+        <v>7.030873602672543e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.030873602672211e-08</v>
+        <v>7.030873602672543e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.970295806046362e-08</v>
+        <v>8.970295806046441e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.204650566046922e-07</v>
+        <v>1.204650566046912e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.238033691448619e-07</v>
+        <v>1.238033691448631e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.128055641474688e-07</v>
+        <v>1.128055641474686e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.334158602433163e-08</v>
+        <v>9.334158602433062e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.184164536378071e-07</v>
+        <v>1.184164536378078e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.179468203197173e-07</v>
+        <v>1.179468203197186e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.210716260875583e-07</v>
+        <v>1.21071626087558e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.179523709729644e-07</v>
+        <v>1.179523709729654e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.917831382451025e-08</v>
+        <v>8.917831382451098e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.474498960940458e-07</v>
+        <v>1.47449896094047e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.144458524949809e-07</v>
+        <v>2.14445852494981e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.643621599381841e-07</v>
+        <v>2.643621599381834e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.612373747481765e-07</v>
+        <v>2.612373747481769e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.183585702326986e-07</v>
+        <v>3.183585702326966e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.643621526576795e-07</v>
+        <v>2.643621526576784e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.61706987488433e-07</v>
+        <v>2.617069874884333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.61237354170171e-07</v>
+        <v>2.612373541701716e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.643621599381841e-07</v>
+        <v>2.643621599381834e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.61237354170171e-07</v>
+        <v>2.612373541701716e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.34126182990185e-07</v>
+        <v>2.341261829901852e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.61237354170171e-07</v>
+        <v>2.612373541701716e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.612930077641651e-07</v>
+        <v>9.612930077641653e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.185957163084507e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.534567430148294e-07</v>
+        <v>9.534567430148296e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.185957163084507e-06</v>
@@ -1166,22 +1166,22 @@
         <v>1.185957163084507e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.493788248246642e-07</v>
+        <v>9.493788248246644e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.565431502931296e-07</v>
+        <v>9.565431502931298e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.185957163084507e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.008988771526798e-07</v>
+        <v>9.008988771526803e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.503312476463112e-07</v>
+        <v>9.503312476463119e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.532768342919339e-07</v>
+        <v>9.610340821585925e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.476878106886045e-07</v>
+        <v>9.476878106886043e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.176928233850819e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.444964185917552e-07</v>
+        <v>9.444964185917545e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.176928233850819e-06</v>
@@ -1206,22 +1206,22 @@
         <v>1.176928233850819e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.428467233301125e-07</v>
+        <v>9.428467233301134e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.457597776250101e-07</v>
+        <v>9.457597776250111e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.176928233850819e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.231135809602035e-07</v>
+        <v>9.231135809602032e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.432238565800784e-07</v>
+        <v>9.432238565800791e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.444305665504088e-07</v>
+        <v>9.444305665504083e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.684115361692709e-07</v>
+        <v>2.684115361692735e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.377296150015385e-07</v>
+        <v>3.377296150015392e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.277963524738288e-07</v>
+        <v>2.277963524738251e-07</v>
       </c>
       <c r="E2" t="n">
         <v>4.752036481341727e-07</v>
@@ -1322,22 +1322,22 @@
         <v>4.752036481341727e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.996003791307125e-07</v>
+        <v>4.996003791307138e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.044317049764867e-07</v>
+        <v>4.044317049764686e-07</v>
       </c>
       <c r="I2" t="n">
         <v>4.752036481341727e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.220415052425716e-06</v>
+        <v>1.22041505242572e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.448715532207177e-07</v>
+        <v>5.448715532207506e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.876440021599355e-07</v>
+        <v>5.876440021599345e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.893887053238742e-08</v>
+        <v>5.893887053238827e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.516582858269667e-08</v>
+        <v>5.51658285826959e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.893887053238742e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.04119441459553e-08</v>
+        <v>6.041194414595568e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.041194414595601e-08</v>
+        <v>6.041194414595568e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.909743560655042e-08</v>
+        <v>5.909743560655098e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.893887053238742e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.99935657162367e-08</v>
+        <v>5.999356571623768e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.893887053238661e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.893887053238742e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.893887053238742e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.008238354639046e-07</v>
+        <v>6.955987126236817e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.854986415291593e-08</v>
+        <v>6.854986415292767e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.887144518093511e-08</v>
+        <v>6.887111604943084e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.88925643747838e-08</v>
+        <v>6.889256437478576e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.070121073507949e-08</v>
+        <v>7.070121073508239e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.009824005380445e-07</v>
+        <v>1.009824005380571e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.091995555556208e-07</v>
+        <v>1.09199555555624e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.01878530647745e-07</v>
+        <v>1.018785306477439e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.025200001969296e-07</v>
+        <v>1.02520000196928e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.939300626067851e-08</v>
+        <v>6.939300626068478e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.966067796934977e-08</v>
+        <v>6.966067796935501e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.085189186332992e-08</v>
+        <v>8.085189186333129e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.080157235463742e-08</v>
+        <v>8.080157235464038e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.085095861458865e-08</v>
+        <v>8.085095861459168e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.207601514682302e-08</v>
+        <v>8.207601514682975e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.207601514682302e-08</v>
+        <v>8.207601514682975e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.101045693749155e-08</v>
+        <v>8.101045693749404e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.085189186332992e-08</v>
+        <v>8.085189186333129e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.190658704717584e-08</v>
+        <v>8.190658704718073e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.085189186332992e-08</v>
+        <v>8.085189186333129e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.085189186332992e-08</v>
+        <v>8.085189186333129e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.085189186332992e-08</v>
+        <v>8.085189186333129e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.087042663100655e-07</v>
+        <v>1.087042663100692e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.501457263446668e-07</v>
+        <v>1.50145726346583e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.58593370601612e-07</v>
+        <v>1.58593370601618e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.399318850551338e-07</v>
+        <v>1.399318850551358e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.111704003324703e-07</v>
+        <v>1.111704003324708e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.501837699017629e-07</v>
+        <v>1.501837699017632e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500252048280681e-07</v>
+        <v>1.500252048280624e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.510799000114539e-07</v>
+        <v>1.5107990001145e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.500333254429189e-07</v>
+        <v>1.500333254429177e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.079367086740631e-07</v>
+        <v>1.079367086740641e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.931883801877525e-07</v>
+        <v>1.931883801877544e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.631479067484024e-07</v>
+        <v>2.631479067484281e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.237948198342282e-07</v>
+        <v>3.237948198342679e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.238451650456679e-07</v>
+        <v>3.238451650457041e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.949431684100954e-07</v>
+        <v>3.949431684101656e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.248998275058499e-07</v>
+        <v>3.248998275058196e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.240037044170925e-07</v>
+        <v>3.240037044171211e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.238451393429286e-07</v>
+        <v>3.238451393429578e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.248998345267932e-07</v>
+        <v>3.248998345268083e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.238451393429286e-07</v>
+        <v>3.238451393429578e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.474164824271174e-07</v>
+        <v>2.886769352117322e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.238451393429286e-07</v>
+        <v>3.238451393429578e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1550,34 +1550,34 @@
         <v>5.711656339046955e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206842989184607e-06</v>
+        <v>1.206842989184608e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.592185194276444e-08</v>
+        <v>3.592185194276437e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.964684810564937e-07</v>
+        <v>9.964684810564918e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.964684810564937e-07</v>
+        <v>9.964684810564918e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.700466237019496e-07</v>
+        <v>5.700466237019579e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.281251597253214e-08</v>
+        <v>3.281251597253433e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.964684810564935e-07</v>
+        <v>9.964684810564918e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.371500598471984e-06</v>
+        <v>1.371500598471986e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.13677964039394e-07</v>
+        <v>6.136779640394424e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674226905299178e-07</v>
+        <v>6.674226905299182e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.651551084625722e-07</v>
+        <v>5.651551084625733e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.191800005800699e-06</v>
+        <v>1.191800005800698e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.784689956308711e-08</v>
+        <v>3.784689956308719e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.865853149444118e-07</v>
+        <v>9.865853149444128e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.865853149444118e-07</v>
+        <v>9.865853149444128e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.670580168773022e-07</v>
+        <v>5.670580168773047e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.658706154904041e-08</v>
+        <v>3.658706154904149e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.865853149444118e-07</v>
+        <v>9.865853149444128e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.364974525469398e-06</v>
+        <v>1.3649745254694e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.107600117257048e-07</v>
+        <v>6.107600117257973e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.632936771544461e-07</v>
+        <v>6.632936771544471e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.93020517916748e-07</v>
+        <v>1.930205179167091e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.567427364819265e-07</v>
+        <v>2.567427364819261e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.717677948667373e-07</v>
+        <v>1.717677948665187e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.933874534988123e-07</v>
+        <v>2.933874534988155e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.933874534988123e-07</v>
+        <v>2.933874534988155e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.795768030329858e-07</v>
+        <v>3.795768030329556e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.890933125390771e-07</v>
+        <v>2.890933125391867e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.933874534988123e-07</v>
+        <v>2.933874534988155e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.809511653008771e-07</v>
+        <v>9.809511653009586e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.515092495209994e-07</v>
+        <v>3.515092495211207e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.525009403705549e-07</v>
+        <v>4.525009403702074e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951489e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.180555251339389e-08</v>
+        <v>5.180555251339336e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951489e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.590084141095886e-08</v>
+        <v>5.590084141095919e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.590084141095884e-08</v>
+        <v>5.590084141095879e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.520293644031279e-08</v>
+        <v>5.520293644019868e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951489e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.608347072618096e-08</v>
+        <v>5.608347072618089e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951501e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951489e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.504719649941151e-08</v>
+        <v>5.504719649951489e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.105147414162405e-08</v>
+        <v>9.105147414142586e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.253897927794254e-08</v>
+        <v>6.253897927793629e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.281035857492196e-08</v>
+        <v>9.222046342375494e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.286347269133216e-08</v>
+        <v>6.286347269132716e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.442764116672292e-08</v>
+        <v>6.442764116671845e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.353712286293815e-08</v>
+        <v>6.35371228627814e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.857563758921232e-08</v>
+        <v>9.857563758953358e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.441765714880596e-08</v>
+        <v>6.441765714879587e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.46192184942432e-08</v>
+        <v>6.461921849429592e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.29499054814334e-08</v>
+        <v>6.294990548129203e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.352402193428768e-08</v>
+        <v>6.35240219342552e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.407663557116e-08</v>
+        <v>7.407663557112345e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.402801875925793e-08</v>
+        <v>7.402801875925641e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.407575110472312e-08</v>
+        <v>7.407575110477372e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.51328630521323e-08</v>
+        <v>7.513286305213433e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.51328630521323e-08</v>
+        <v>7.513286305213433e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.423237551206073e-08</v>
+        <v>7.423237551211573e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407663557116e-08</v>
+        <v>7.407663557112345e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.511290979792981e-08</v>
+        <v>7.511290979792876e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.407663557116e-08</v>
+        <v>7.407663557112345e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.407663557116e-08</v>
+        <v>7.407663557112345e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.407663557116e-08</v>
+        <v>7.407663557112345e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.886143361549933e-08</v>
+        <v>9.886143361518614e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.347419433204384e-07</v>
+        <v>1.347419433221484e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.422081539269608e-07</v>
+        <v>1.422081539269226e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.260050858448053e-07</v>
+        <v>1.260050858448016e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.010481820058196e-07</v>
+        <v>1.010481820058192e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349193447889152e-07</v>
+        <v>1.349193447889391e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.347636048485596e-07</v>
+        <v>1.347636048483289e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.357998790747839e-07</v>
+        <v>1.357998790747834e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.347706605499615e-07</v>
+        <v>1.347706605498364e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.819453236128286e-08</v>
+        <v>9.819453236116424e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.722664246974566e-07</v>
+        <v>1.722664246971749e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.243163960205564e-07</v>
+        <v>2.243163960203735e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.745895115943332e-07</v>
+        <v>2.745895115943392e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.746381505062756e-07</v>
+        <v>2.746381505062625e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.337446266715931e-07</v>
+        <v>3.337446266715752e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.756743961375126e-07</v>
+        <v>2.756743961375194e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.747938683471364e-07</v>
+        <v>2.74793868347102e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.746381284062336e-07</v>
+        <v>2.746381284060074e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.756744026330044e-07</v>
+        <v>2.756744026330095e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.746381284062336e-07</v>
+        <v>2.746381284060074e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.454815283284698e-07</v>
+        <v>2.454815283283367e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.746381284062336e-07</v>
+        <v>2.746381284060074e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.709927100153058e-07</v>
+        <v>5.709927100153604e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.206673282712639e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.341309731079303e-08</v>
+        <v>3.34130973109038e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.967854867729925e-07</v>
+        <v>9.967854867729934e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.967854867729925e-07</v>
+        <v>9.967854867729934e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.695713428358416e-07</v>
+        <v>5.695713428357308e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.125015593165702e-08</v>
+        <v>3.125015593152823e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.967854867729925e-07</v>
+        <v>9.967854867729934e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.370827874554989e-06</v>
+        <v>1.370827874554801e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.135498401006259e-07</v>
+        <v>6.135498401004869e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.671209314619255e-07</v>
+        <v>6.671209314618197e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.641277738043565e-07</v>
+        <v>5.641277738043364e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.190747122219756e-06</v>
+        <v>1.190747122219755e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.473720538157147e-08</v>
+        <v>3.473720538167546e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.846912122078877e-07</v>
+        <v>9.846912122078866e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.846912122078877e-07</v>
+        <v>9.846912122078866e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.652893645244489e-07</v>
+        <v>5.652893645244557e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.386096008483651e-08</v>
+        <v>3.38609600847955e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.846912122078877e-07</v>
+        <v>9.846912122078866e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361951388985485e-06</v>
+        <v>1.361951388985529e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.08305488379406e-07</v>
+        <v>6.08305488379338e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.617086331283654e-07</v>
+        <v>6.617086331284063e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2105,31 +2105,31 @@
         <v>2.021409557848446e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394058599055418e-07</v>
+        <v>1.394058599055401e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.860452532413279e-07</v>
+        <v>1.86045253241327e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.860452532413279e-07</v>
+        <v>1.86045253241327e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.180869472938347e-07</v>
+        <v>3.180869472937945e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.360056276851501e-07</v>
+        <v>2.360056276851493e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.860452532413279e-07</v>
+        <v>1.86045253241327e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.13939883864555e-07</v>
+        <v>9.139398838645546e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.271744490846709e-07</v>
+        <v>2.271744490846706e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.919824820513359e-07</v>
+        <v>2.919824820513354e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.942000662450276e-08</v>
+        <v>4.942000662450279e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.167317095285267e-08</v>
+        <v>5.167317095285262e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.167317095285267e-08</v>
+        <v>5.167317095285262e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.169497298726959e-08</v>
+        <v>5.169497298726924e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.25711576034306e-08</v>
+        <v>5.257115760343071e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.153986906758268e-08</v>
+        <v>5.153986906758244e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.382844247701337e-08</v>
+        <v>5.823882886917266e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.763740479516331e-08</v>
+        <v>5.763740479516161e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.765354994579322e-08</v>
+        <v>5.765354994578847e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.784280952083249e-08</v>
+        <v>5.784280952083273e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.920877332639837e-08</v>
+        <v>5.920877332639843e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.839393278885959e-08</v>
+        <v>8.398354639670035e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.88280891544428e-08</v>
+        <v>8.88280891544431e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.92701174050207e-08</v>
+        <v>8.485973101286176e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.92430659696281e-08</v>
+        <v>8.41902389539941e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.764273358703919e-08</v>
+        <v>5.764273358703886e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.84102411354948e-08</v>
+        <v>5.841024113549513e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.858610737589895e-08</v>
+        <v>6.858610737589912e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.854091973238646e-08</v>
+        <v>6.854091973238647e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.85850803511059e-08</v>
+        <v>6.858508035110564e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.942499982982546e-08</v>
+        <v>6.942499982982531e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.942499982982546e-08</v>
+        <v>6.942499982982531e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.874121129558609e-08</v>
+        <v>6.874121129558588e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.858610737589895e-08</v>
+        <v>6.858610737589912e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.961739591174764e-08</v>
+        <v>6.961739591174737e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.858610737589895e-08</v>
+        <v>6.858610737589912e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.858610737589895e-08</v>
+        <v>6.858610737589912e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.858610737589895e-08</v>
+        <v>6.858610737589912e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.114754977240214e-08</v>
+        <v>9.114754977240119e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.227538233194218e-07</v>
+        <v>1.227538233178996e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.295753841224742e-07</v>
+        <v>1.295753841224737e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.151442433243422e-07</v>
+        <v>1.15144243324342e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.307357826966837e-08</v>
+        <v>9.307357826966833e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2313072924176e-07</v>
+        <v>1.231307292417585e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.229756253223471e-07</v>
+        <v>1.229756253223467e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.240069138579203e-07</v>
+        <v>1.2400691385792e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.229818803753238e-07</v>
+        <v>1.22981880375323e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.055632693461152e-08</v>
+        <v>9.055632693461144e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.562227115860503e-07</v>
+        <v>1.562227115860496e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.017777755573603e-07</v>
+        <v>2.01777775557359e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.46181202481518e-07</v>
+        <v>2.461812024815178e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.462264092339703e-07</v>
+        <v>2.462264092339693e-07</v>
       </c>
       <c r="E7" t="n">
         <v>2.985504458215143e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.472576715715526e-07</v>
+        <v>2.472576715715523e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.463814940447185e-07</v>
+        <v>2.463814940447171e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.462263901250308e-07</v>
+        <v>2.462263901250301e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.472576786608789e-07</v>
+        <v>2.472576786608788e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.462263901250308e-07</v>
+        <v>2.462263901250301e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.19427835653694e-07</v>
+        <v>1.902576453820702e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.462263901250308e-07</v>
+        <v>2.462263901250301e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.702909729747512e-07</v>
+        <v>5.702909729747518e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206067817808555e-06</v>
+        <v>1.206067817808554e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.026118776718028e-08</v>
+        <v>3.026118776718043e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.956849416095829e-07</v>
+        <v>9.956849416095831e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.956849416095829e-07</v>
+        <v>9.956849416095833e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.680480485318483e-07</v>
+        <v>5.680480485318486e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.845538807154025e-08</v>
+        <v>2.845538807154054e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.956849416095829e-07</v>
+        <v>9.956849416095833e-07</v>
       </c>
       <c r="J8" t="n">
         <v>1.366744791912019e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.120014577396548e-07</v>
+        <v>6.120014577396551e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674930865384458e-07</v>
+        <v>6.674930865384456e-07</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.627637060433096e-07</v>
+        <v>5.627637060433088e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.189412395480075e-06</v>
+        <v>1.189412395480074e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.118943640308875e-08</v>
+        <v>3.118943640308869e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.821216543456323e-07</v>
+        <v>9.821216543456321e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.821216543456323e-07</v>
+        <v>9.821216543456321e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.629589539004025e-07</v>
+        <v>5.629589539004024e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.045764308194084e-08</v>
+        <v>3.045764308194098e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.821216543456323e-07</v>
+        <v>9.821216543456321e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.357045268181962e-06</v>
+        <v>1.357045268181963e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.050483252354662e-07</v>
+        <v>6.050483252354658e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.601261682982884e-07</v>
+        <v>6.601261682982886e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15204242713303e-07</v>
+        <v>2.152042427133e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.347979805044388e-07</v>
+        <v>2.347979805044367e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.967110820847253e-07</v>
+        <v>1.967110820847223e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.789229292124438e-07</v>
+        <v>3.789229292124458e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.789229292124438e-07</v>
+        <v>3.789229292124458e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.285558527460911e-07</v>
+        <v>4.285558527460839e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.533757532110347e-07</v>
+        <v>3.533757532110297e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.789229292124438e-07</v>
+        <v>3.789229292124458e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06781190373185e-06</v>
+        <v>1.067811903731846e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.347613317959157e-07</v>
+        <v>4.347613317958935e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.852416688421956e-07</v>
+        <v>3.85241668842191e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.467719030070854e-08</v>
+        <v>5.467719030070811e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.969019451427514e-08</v>
+        <v>5.96901945142766e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.969019451427615e-08</v>
+        <v>5.969019451427661e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.905798412985709e-08</v>
+        <v>5.905798412985635e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.994365318265628e-08</v>
+        <v>5.994365318265715e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.890150842588291e-08</v>
+        <v>5.890150842588178e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.009541154751471e-07</v>
+        <v>6.972189792965182e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.857464483886281e-08</v>
+        <v>6.857464483886126e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.911172295120876e-08</v>
+        <v>6.911172295120852e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.882800142427907e-08</v>
+        <v>6.882800142427897e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.079342249231192e-08</v>
+        <v>7.079342249230935e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.987837363362774e-08</v>
+        <v>6.987837363362632e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.099673539985025e-07</v>
+        <v>1.099673539985004e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.019962602319179e-07</v>
+        <v>7.076404268642707e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.028532261726558e-07</v>
+        <v>1.028532261726537e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.958106085298372e-08</v>
+        <v>6.9581060852982e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.977623178930665e-08</v>
+        <v>6.977623178930495e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.034334157770024e-08</v>
+        <v>8.034334157769774e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.028993520034098e-08</v>
+        <v>8.028993520033859e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.034252539623891e-08</v>
+        <v>8.03425253962367e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.137817806364592e-08</v>
+        <v>8.137817806364334e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.137817806364592e-08</v>
+        <v>8.137817806364334e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.049981728167458e-08</v>
+        <v>8.049981728167232e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.034334157770024e-08</v>
+        <v>8.034334157769774e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.138548633447409e-08</v>
+        <v>8.1385486334473e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.034334157770024e-08</v>
+        <v>8.034334157769774e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.034334157770024e-08</v>
+        <v>8.034334157769774e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.034334157770024e-08</v>
+        <v>8.034334157769774e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.084190599305035e-07</v>
+        <v>1.084190599305006e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497259654686847e-07</v>
+        <v>1.497259654686804e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.583535720438236e-07</v>
+        <v>1.583535720438186e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.395102884085601e-07</v>
+        <v>1.395102884085555e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.107683340263651e-07</v>
+        <v>1.107683340263617e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.499340834427972e-07</v>
+        <v>1.49934083442793e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.497776077393429e-07</v>
+        <v>1.497776077393383e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.508197524955968e-07</v>
+        <v>1.508197524955938e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49785735738347e-07</v>
+        <v>1.497857357383425e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.076508036831256e-07</v>
+        <v>1.076508036831227e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.929800691415872e-07</v>
+        <v>1.929800691415808e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.610199290272097e-07</v>
+        <v>2.610199290271932e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.211704969303396e-07</v>
+        <v>3.211704969303305e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.212239291317191e-07</v>
+        <v>3.212239291317069e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.917401733705174e-07</v>
+        <v>3.917401733704958e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.222660418024421e-07</v>
+        <v>3.222660418024177e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.213803790116668e-07</v>
+        <v>3.213803790116643e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.212239033076989e-07</v>
+        <v>3.212239033076895e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.222660480644856e-07</v>
+        <v>3.222660480644649e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.212239033076989e-07</v>
+        <v>3.212239033076895e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.454163466241331e-07</v>
+        <v>2.454163466241175e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.212239033076989e-07</v>
+        <v>3.212239033076895e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.726079164659571e-07</v>
+        <v>5.726079164659563e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.208781072950083e-06</v>
+        <v>1.208781072950082e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.632223986867864e-08</v>
+        <v>3.632223986867768e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.98367976755392e-07</v>
+        <v>9.983679767553909e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.983679767553917e-07</v>
+        <v>9.983679767553909e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.714468849406377e-07</v>
+        <v>5.714468849406338e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.353605425327921e-08</v>
+        <v>3.353605425327827e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.983679767553917e-07</v>
+        <v>9.983679767553909e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.375104276976853e-06</v>
+        <v>1.375104276976851e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.155914714759695e-07</v>
+        <v>6.155914714759269e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.712625840405669e-07</v>
+        <v>6.712625840405658e-07</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.658888635895567e-07</v>
+        <v>5.658888635895559e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.192374943306635e-06</v>
+        <v>1.192374943306634e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.782899196353036e-08</v>
+        <v>3.782899196352931e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.871861892539568e-07</v>
+        <v>9.871861892539558e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.871861892539568e-07</v>
+        <v>9.871861892539558e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6751868907151e-07</v>
+        <v>5.675186890715065e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.669982608634622e-08</v>
+        <v>3.66998260863451e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.871861892539568e-07</v>
+        <v>9.871861892539558e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.366590708601565e-06</v>
+        <v>1.366590708601563e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.111837013987508e-07</v>
+        <v>6.11183701398709e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.647388155952301e-07</v>
+        <v>6.647388155952291e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.212381940206897e-07</v>
+        <v>1.212381940206896e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.260614206980183e-07</v>
+        <v>1.260614206980184e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.447612693967904e-07</v>
+        <v>1.447612693967903e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.918620519011127e-07</v>
+        <v>1.918620519011315e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.918620519011127e-07</v>
+        <v>1.918620519011315e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.239557343130947e-07</v>
+        <v>2.239557343130894e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.939118075107038e-07</v>
+        <v>1.93911807510704e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.918620519011127e-07</v>
+        <v>1.918620519011315e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.708898504316585e-07</v>
+        <v>5.708898504316583e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.749240912159105e-07</v>
+        <v>1.749240912159106e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.042822863572647e-07</v>
+        <v>2.042822863572645e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
       <c r="C3" t="n">
         <v>5.153134762405945e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.634633210089125e-08</v>
+        <v>5.634633210089123e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.634633210089129e-08</v>
+        <v>5.634633210089123e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.603140014959355e-08</v>
+        <v>5.603140014959353e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.691379750000735e-08</v>
+        <v>5.69137975000073e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.587552229371642e-08</v>
+        <v>5.587552229371649e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.508766856880561e-08</v>
+        <v>6.508766856880554e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.405602588764055e-08</v>
+        <v>6.405602588764053e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.493330869811288e-08</v>
+        <v>6.476949573581952e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.435817369657024e-08</v>
+        <v>6.43581736965702e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.610924372015068e-08</v>
+        <v>6.61092437201507e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.524354642468274e-08</v>
+        <v>9.335145385016319e-08</v>
       </c>
       <c r="H4" t="n">
         <v>1.021521070218849e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.612594377509658e-08</v>
+        <v>9.423385120057699e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.641426483429237e-08</v>
+        <v>6.641426483429231e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.477994034404903e-08</v>
+        <v>6.477994034404902e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.513791563818532e-08</v>
+        <v>6.513791563818303e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.453418125473945e-08</v>
+        <v>7.453418125473954e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.448391929422201e-08</v>
+        <v>7.448391929422198e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.453356423376244e-08</v>
+        <v>7.453356423376252e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.548614878535387e-08</v>
+        <v>7.548614878535402e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.548614878535387e-08</v>
+        <v>7.548614878535402e-08</v>
       </c>
       <c r="G5" t="n">
         <v>7.469005911061659e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.453418125473945e-08</v>
+        <v>7.453418125473954e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.557245646103037e-08</v>
+        <v>7.557245646103045e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.453418125473945e-08</v>
+        <v>7.453418125473954e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.453418125473945e-08</v>
+        <v>7.453418125473954e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.453418125473945e-08</v>
+        <v>7.453418125473954e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.99504176409718e-08</v>
+        <v>9.995041764097188e-08</v>
       </c>
       <c r="C6" t="n">
         <v>1.366130199922847e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.443663376745013e-07</v>
+        <v>1.443663376745014e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.276485439962902e-07</v>
+        <v>1.2764854399629e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.021036889046733e-07</v>
+        <v>1.021036889046734e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.368940375699005e-07</v>
+        <v>1.368940375699006e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.367381597146809e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.377764349203143e-07</v>
+        <v>1.377764349203145e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.367453894347391e-07</v>
+        <v>1.367453894347393e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.926706645540781e-08</v>
+        <v>9.926706645540779e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.751660323366896e-07</v>
+        <v>1.751660323366892e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.222151731883003e-07</v>
+        <v>2.222151731883001e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.719898246378542e-07</v>
+        <v>2.719898246378541e-07</v>
       </c>
       <c r="D7" t="n">
         <v>2.720401076283873e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.305752681740161e-07</v>
+        <v>3.305752681740153e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.730783567984774e-07</v>
+        <v>2.730783567984771e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.721959644542487e-07</v>
+        <v>2.721959644542479e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.720400865983714e-07</v>
+        <v>2.720400865983716e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.730783618046626e-07</v>
+        <v>2.730783618046628e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.720400865983714e-07</v>
+        <v>2.720400865983716e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.431713449361817e-07</v>
+        <v>2.093016214489792e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.720400865983714e-07</v>
+        <v>2.720400865983716e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.73362391735212e-07</v>
+        <v>5.733623917352129e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.209911892359383e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.470238000527157e-08</v>
+        <v>3.470238000527153e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.999773368974298e-07</v>
+        <v>9.999773368974292e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.999773368974298e-07</v>
+        <v>9.999773368974294e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.737892289414357e-07</v>
+        <v>5.737892289414356e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.392942445161234e-08</v>
+        <v>3.39294244516123e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.999773368974298e-07</v>
+        <v>9.999773368974294e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.382377541671313e-06</v>
+        <v>1.382377541671312e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.182696682964022e-07</v>
+        <v>6.182696682964025e-07</v>
       </c>
       <c r="L8" t="n">
         <v>6.729540559041427e-07</v>
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.654840150611575e-07</v>
+        <v>5.654840150611579e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.192150306689497e-06</v>
+        <v>1.192150306689498e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.563079208381624e-08</v>
+        <v>3.56307920838162e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.864228515761298e-07</v>
+        <v>9.8642285157613e-07</v>
       </c>
       <c r="F9" t="n">
         <v>9.864228515761298e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.673183720756932e-07</v>
+        <v>5.673183720756933e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.531879330335906e-08</v>
+        <v>3.5318793303359e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.864228515761298e-07</v>
@@ -3198,10 +3198,10 @@
         <v>1.367839843002902e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.104801234575742e-07</v>
+        <v>6.104801234575743e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.64429376035833e-07</v>
+        <v>6.644293760358331e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.063842549447459e-07</v>
+        <v>1.063842549447457e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.183990167086202e-07</v>
+        <v>1.183990167086214e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.285320992297967e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.458122036519743e-07</v>
+        <v>1.458122036519393e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.458122036519743e-07</v>
+        <v>1.458122036519393e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.433825436144065e-07</v>
+        <v>1.433825436144004e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.660258916891163e-07</v>
+        <v>1.660258916891127e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.458122036519743e-07</v>
+        <v>1.458122036519393e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56917319753726e-07</v>
+        <v>2.56917319753728e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.047173153462807e-07</v>
+        <v>1.047173153462808e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.336452489062968e-07</v>
+        <v>1.336452489062966e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.68538292013825e-08</v>
+        <v>4.685382920138267e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.079547830253641e-08</v>
+        <v>5.079547830252889e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.079547830253639e-08</v>
+        <v>5.079547830252888e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.10548833935331e-08</v>
+        <v>5.10548833935343e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.19444499242199e-08</v>
+        <v>5.194444992420984e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.089736169550317e-08</v>
+        <v>5.089736169550346e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.326769433113654e-08</v>
+        <v>8.326769433113721e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.73274198554253e-08</v>
+        <v>5.732741985542514e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.804660080341178e-08</v>
+        <v>5.804660080341185e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.780042445278234e-08</v>
+        <v>5.78004244527807e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.916537128856103e-08</v>
+        <v>5.916537128856083e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.342521602916643e-08</v>
+        <v>8.342521602916267e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.950377255481283e-08</v>
+        <v>8.950377255481025e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.922824701249828e-08</v>
+        <v>5.922824701248585e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.417046208783073e-08</v>
+        <v>8.417046208782977e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.775041566355473e-08</v>
+        <v>5.775041566355474e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.82335353325894e-08</v>
+        <v>5.823353533258985e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.69098902054836e-08</v>
+        <v>6.690989020548387e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.68668827688225e-08</v>
+        <v>6.686688276882272e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.690925439390026e-08</v>
+        <v>6.690925439390052e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.767691974059423e-08</v>
+        <v>6.767691974059077e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.767691974059423e-08</v>
+        <v>6.767691974059077e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.706741190351338e-08</v>
+        <v>6.706741190351546e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.69098902054836e-08</v>
+        <v>6.690989020548387e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.795697843420034e-08</v>
+        <v>6.795697843418819e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.69098902054836e-08</v>
+        <v>6.690989020548387e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.69098902054836e-08</v>
+        <v>6.690989020548387e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.69098902054836e-08</v>
+        <v>6.690989020548387e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3450,31 +3450,31 @@
         <v>8.919201300142936e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.201658665646623e-07</v>
+        <v>1.201658665646622e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.269557996416754e-07</v>
+        <v>1.269557996416756e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.127295623219912e-07</v>
+        <v>1.127295623219886e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.106387862608211e-08</v>
+        <v>9.106387862608444e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.206276089019665e-07</v>
+        <v>1.206276089019646e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.204700872043332e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215171754326535e-07</v>
+        <v>1.215171754326547e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.204762341515394e-07</v>
+        <v>1.204762341515392e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.861100672221477e-08</v>
+        <v>8.861100672221471e-08</v>
       </c>
       <c r="L6" t="n">
         <v>1.531426510564062e-07</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.978429250086058e-07</v>
+        <v>1.97842925008606e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.414617555158055e-07</v>
+        <v>2.414617555158052e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.41504779367353e-07</v>
+        <v>2.415047793673527e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.929366945686364e-07</v>
+        <v>2.929366945686387e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.42551845854819e-07</v>
+        <v>2.425518458548069e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.416622846504964e-07</v>
+        <v>2.41662284650497e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.415047629524664e-07</v>
+        <v>2.415047629524662e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.425518511811829e-07</v>
+        <v>2.425518511811808e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.415047629524664e-07</v>
+        <v>2.415047629524662e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.162069294785589e-07</v>
+        <v>2.15180563752603e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.415047629524664e-07</v>
+        <v>2.415047629524662e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.714605312138742e-07</v>
+        <v>5.714605312138737e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.207822696639414e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.046675125959667e-08</v>
+        <v>3.046675125959653e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.966126915387465e-07</v>
+        <v>9.966126915387463e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.966126915387467e-07</v>
+        <v>9.966126915387463e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.720011509307666e-07</v>
+        <v>5.720011509307662e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.990478520057699e-08</v>
+        <v>2.990478520057681e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.966126915387465e-07</v>
+        <v>9.966126915387463e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.382353241751083e-06</v>
+        <v>1.382353241751081e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.147606327686488e-07</v>
+        <v>6.147606327686486e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.707206256930868e-07</v>
+        <v>6.707206256930867e-07</v>
       </c>
     </row>
     <row r="9">
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.634265118705515e-07</v>
+        <v>5.634265118705511e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.190008250608652e-06</v>
+        <v>1.190008250608653e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.125401448268472e-08</v>
+        <v>3.125401448268455e-08</v>
       </c>
       <c r="E9" t="n">
         <v>9.824899466384876e-07</v>
@@ -3582,22 +3582,22 @@
         <v>9.824899466384876e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.644768532951742e-07</v>
+        <v>5.64476853295174e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.102745508374701e-08</v>
+        <v>3.10274550837469e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.824899466384876e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.363635611409168e-06</v>
+        <v>1.363635611409166e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.060625119644022e-07</v>
+        <v>6.060625119644019e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.613865369439547e-07</v>
+        <v>6.613865369439543e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.766439132527106e-07</v>
+        <v>1.766439132527079e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.413678465215278e-07</v>
+        <v>1.41367846521528e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.713561481769583e-07</v>
+        <v>1.713561481769538e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.833018930098732e-07</v>
+        <v>2.833018930098664e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.833018930098732e-07</v>
+        <v>2.833018930098664e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.788642494698268e-07</v>
+        <v>3.788642494698241e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.319996164058594e-07</v>
+        <v>3.319996164058542e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.833018930098732e-07</v>
+        <v>2.833018930098664e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.075410452094662e-06</v>
+        <v>1.075410452094657e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.457565485923295e-07</v>
+        <v>3.457565485923312e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.170563873745552e-07</v>
+        <v>3.170563873745524e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.40101131591378e-08</v>
+        <v>5.401011315913714e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.880685631910285e-08</v>
+        <v>5.880685631910296e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.880685631910287e-08</v>
+        <v>5.880685631910296e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.834732931642447e-08</v>
+        <v>5.834732931642356e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.922378259203611e-08</v>
+        <v>5.922378259203538e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.819255721649834e-08</v>
+        <v>5.81925572164962e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.940474360113878e-08</v>
+        <v>6.867648054411139e-08</v>
       </c>
       <c r="C4" t="n">
         <v>6.746471193613842e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.812483156189595e-08</v>
+        <v>6.812483156189453e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.770204611319157e-08</v>
+        <v>6.770204611319032e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.970273529214856e-08</v>
+        <v>6.970273529214806e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.955951570106486e-08</v>
+        <v>9.955951570106221e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084199255763955e-07</v>
+        <v>1.084199255763917e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.970770591965322e-08</v>
+        <v>1.004359689766764e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.012710892331749e-07</v>
+        <v>1.012710892331712e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.84476449007871e-08</v>
+        <v>6.844764490078441e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.872685578030823e-08</v>
+        <v>6.87268557803065e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.901987278427847e-08</v>
+        <v>7.901987278427724e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.896519312413112e-08</v>
+        <v>7.89651931241299e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.901904785353726e-08</v>
+        <v>7.901904785353336e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.000630718976025e-08</v>
+        <v>8.000630718976051e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.000630718976025e-08</v>
+        <v>8.000630718976051e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.917464488420456e-08</v>
+        <v>7.917464488420155e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.901987278427847e-08</v>
+        <v>7.901987278427724e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.005109815981637e-08</v>
+        <v>8.005109815981661e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.901987278427847e-08</v>
+        <v>7.901987278427724e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.901987278427847e-08</v>
+        <v>7.901987278427724e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.901987278427847e-08</v>
+        <v>7.901987278427724e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.066421794516438e-07</v>
+        <v>1.06642179451642e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.470600016596961e-07</v>
+        <v>1.470600016596963e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.555482139878808e-07</v>
+        <v>1.555482139878796e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.370714356528428e-07</v>
+        <v>1.370714356528442e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.089311770437699e-07</v>
+        <v>1.089311770437707e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47303656871852e-07</v>
+        <v>1.473036568718507e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.471488847724633e-07</v>
+        <v>1.471488847724635e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.481801101474637e-07</v>
+        <v>1.481801101474655e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.471568453614895e-07</v>
+        <v>1.471568453614892e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.058897466156917e-07</v>
+        <v>1.058897466156903e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.894615254674265e-07</v>
+        <v>1.894615254674261e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.582722815894852e-07</v>
+        <v>2.582722815895054e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.177823389851836e-07</v>
+        <v>3.177823389852126e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.178370436901953e-07</v>
+        <v>3.178370436902227e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.876047021830073e-07</v>
+        <v>3.876047021830422e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.188682375697605e-07</v>
+        <v>3.188682375697885e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.179917907452572e-07</v>
+        <v>3.179917907452842e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.17837018645331e-07</v>
+        <v>3.178370186453594e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188682440208689e-07</v>
+        <v>3.188682440208967e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.17837018645331e-07</v>
+        <v>3.178370186453594e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.819247888487733e-07</v>
+        <v>2.833249866001937e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.17837018645331e-07</v>
+        <v>3.178370186453594e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.731203115254545e-07</v>
+        <v>5.731203115254531e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.207655281151201e-06</v>
+        <v>1.207655281151202e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.588885666679955e-08</v>
+        <v>3.588885666679891e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>9.995396310036018e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>9.995396310036018e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.716820257315585e-07</v>
+        <v>5.716820257315582e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.295371791897256e-08</v>
+        <v>3.295371791897211e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>9.995396310036018e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.374163132589592e-06</v>
+        <v>1.37416313258959e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.164160213516866e-07</v>
+        <v>6.164160213517005e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.720383972943355e-07</v>
+        <v>6.720383972943345e-07</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.658984657521893e-07</v>
+        <v>5.658984657521877e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.190058398340922e-06</v>
+        <v>1.190058398340923e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.706864139015911e-08</v>
+        <v>3.706864139015713e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.87081166982797e-07</v>
+        <v>9.870811669827976e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.87081166982797e-07</v>
+        <v>9.870811669827976e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.671107653749762e-07</v>
+        <v>5.671107653749767e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.587842638614389e-08</v>
+        <v>3.587842638614206e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.870811669827972e-07</v>
+        <v>9.870811669827976e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.365764632101805e-06</v>
+        <v>1.365764632101802e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.108176296535089e-07</v>
+        <v>6.108176296535233e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.647188664909146e-07</v>
+        <v>6.647188664909138e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.192091674979993e-07</v>
+        <v>1.192091674977187e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.247027282163955e-07</v>
+        <v>1.247027282164053e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.387546650529714e-07</v>
+        <v>1.387546650531726e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.615920838866328e-07</v>
+        <v>1.615920838866305e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.615920838866328e-07</v>
+        <v>1.615920838866305e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.557269304224117e-07</v>
+        <v>1.557269304226085e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.842228356565722e-07</v>
+        <v>1.842228356564022e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.615920838866328e-07</v>
+        <v>1.615920838866305e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.843754977458383e-07</v>
+        <v>1.843754977457667e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.208092184789939e-07</v>
+        <v>1.208092184787639e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.437148963112713e-07</v>
+        <v>1.437148963108235e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.020022798751845e-08</v>
+        <v>5.020022798752001e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.438009855124224e-08</v>
+        <v>5.438009855124385e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.43800985512423e-08</v>
+        <v>5.438009855124387e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.445872872380895e-08</v>
+        <v>5.44587287238554e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.534157225054649e-08</v>
+        <v>5.534157225054709e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.430262303190899e-08</v>
+        <v>5.430262303189605e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.930709787798958e-08</v>
+        <v>6.240607821584041e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.151841977814363e-08</v>
+        <v>6.151841977814711e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.213881420750555e-08</v>
+        <v>6.213850192852807e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.182455998806129e-08</v>
+        <v>6.182455998806448e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.339805742715369e-08</v>
+        <v>6.339805742715605e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2562183907726e-08</v>
+        <v>6.256218390780325e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.822952213234428e-08</v>
+        <v>9.822952213242882e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.344502743449009e-08</v>
+        <v>9.03460470963529e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.349894146120586e-08</v>
+        <v>9.088105572810441e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.190039909928581e-08</v>
+        <v>6.190039909917767e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.245560620303233e-08</v>
+        <v>6.245560620281968e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.164802921066835e-08</v>
+        <v>7.16480292103107e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.160177829017689e-08</v>
+        <v>7.160177829018393e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.16473916423505e-08</v>
+        <v>7.164739164226667e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.24770335435922e-08</v>
+        <v>7.247703354359825e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.24770335435922e-08</v>
+        <v>7.247703354359825e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.180413490212434e-08</v>
+        <v>7.180413490227004e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.164802921066835e-08</v>
+        <v>7.16480292103107e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.268697842895246e-08</v>
+        <v>7.268697842896174e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.164802921066835e-08</v>
+        <v>7.16480292103107e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.164802921066835e-08</v>
+        <v>7.16480292103107e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.164802921066835e-08</v>
+        <v>7.16480292103107e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.579391058062789e-08</v>
+        <v>9.579391058065838e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300917762299997e-07</v>
+        <v>1.300917762300091e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.374930922295944e-07</v>
+        <v>1.374930922295651e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.217518933302575e-07</v>
+        <v>1.217518933302648e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.780278609652606e-08</v>
+        <v>9.780278609653183e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.304876041014253e-07</v>
+        <v>1.304876041014462e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.30331498410526e-07</v>
+        <v>1.303314984102302e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.313704476281288e-07</v>
+        <v>1.31370447628137e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.303382859203156e-07</v>
+        <v>1.303382859202289e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.51523571643258e-08</v>
+        <v>9.515235716464268e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.664088967781474e-07</v>
+        <v>1.664088967782748e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.180134272132362e-07</v>
+        <v>2.180134272130771e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.668001939874254e-07</v>
+        <v>2.668001939874451e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.668464629635232e-07</v>
+        <v>2.668464629632144e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.242376709448105e-07</v>
+        <v>3.242376709448353e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.678853889297928e-07</v>
+        <v>2.678853889298127e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67002550599451e-07</v>
+        <v>2.670025505995313e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.668464449076998e-07</v>
+        <v>2.66846444907572e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.678853941262027e-07</v>
+        <v>2.678853941262227e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.668464449076998e-07</v>
+        <v>2.66846444907572e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.053569542877801e-07</v>
+        <v>2.385524102674521e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.668464449076998e-07</v>
+        <v>2.66846444907572e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.732000418763737e-07</v>
+        <v>5.732000418764543e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.204002895071934e-06</v>
+        <v>1.204002895071936e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.306609632203492e-08</v>
+        <v>3.30660963221478e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.972925179877184e-07</v>
+        <v>9.97292517987719e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.972925179877184e-07</v>
+        <v>9.97292517987719e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.731472613425974e-07</v>
+        <v>5.731472613426011e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.235724206136878e-08</v>
+        <v>3.235724206135308e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.972925179877184e-07</v>
+        <v>9.97292517987719e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3883881264981e-06</v>
+        <v>1.388388126497969e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.162288991408142e-07</v>
+        <v>6.162288991410043e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.727582248273605e-07</v>
+        <v>6.727582248273289e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.653001382144611e-07</v>
+        <v>5.653001382144474e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.186319511968624e-06</v>
+        <v>1.186319511968625e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.394092059238858e-08</v>
+        <v>3.394092059262716e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.8336365182229e-07</v>
+        <v>9.833636518222906e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.8336365182229e-07</v>
+        <v>9.833636518222906e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.65758787379046e-07</v>
+        <v>5.657587873789712e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.365485700554367e-08</v>
+        <v>3.365485700560387e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.8336365182229e-07</v>
+        <v>9.833636518222906e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.368591187709708e-06</v>
+        <v>1.368591187709642e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.077178422281963e-07</v>
+        <v>6.077178422282929e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.635023831870174e-07</v>
+        <v>6.635023831870771e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.040361738924154e-07</v>
+        <v>1.040361738924171e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.145327242796108e-07</v>
+        <v>1.145327242796077e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.212428010142867e-07</v>
+        <v>1.212428010142885e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.231161287571192e-07</v>
+        <v>1.231161287571172e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.231161287571192e-07</v>
+        <v>1.231161287571172e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246154643426311e-07</v>
+        <v>1.246154643426488e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.616074575865214e-07</v>
+        <v>1.616074575865178e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.231161287571192e-07</v>
+        <v>1.231161287571172e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.524220233465234e-07</v>
+        <v>1.524220233465195e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.034287307375557e-07</v>
+        <v>1.034287307375527e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.276547924451354e-07</v>
+        <v>1.276547924451313e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.520825789954613e-08</v>
+        <v>4.520825789954438e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.886966049801352e-08</v>
+        <v>4.886966049801328e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.886966049801332e-08</v>
+        <v>4.886966049801328e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.917350386852376e-08</v>
+        <v>4.91735038685238e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.006397443029895e-08</v>
+        <v>5.006397443029901e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.901566082716078e-08</v>
+        <v>4.901566082716075e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.891165755574913e-08</v>
+        <v>5.524334576054353e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.444411954825573e-08</v>
+        <v>5.444411954825279e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.495273576320281e-08</v>
+        <v>5.495273576320083e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.502327228638669e-08</v>
+        <v>5.502327228638655e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.621780388441857e-08</v>
+        <v>5.621780388441663e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.906950059711229e-08</v>
+        <v>7.906950059711088e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.535030463740065e-08</v>
+        <v>8.535030463740137e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.629165936368371e-08</v>
+        <v>7.995997115888597e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.961516885990041e-08</v>
+        <v>5.606051092543404e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.469134720318331e-08</v>
+        <v>5.469134720318152e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.527217899858572e-08</v>
+        <v>5.527217899858372e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.387840617639984e-08</v>
+        <v>6.387840617639995e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.383805168143326e-08</v>
+        <v>6.383805168143245e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.387773263699025e-08</v>
+        <v>6.387773263699026e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.462740723869453e-08</v>
+        <v>6.462740723869477e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.462740723869453e-08</v>
+        <v>6.462740723869477e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.403624921776293e-08</v>
+        <v>6.403624921776305e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.387840617639984e-08</v>
+        <v>6.387840617639995e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.492671977953816e-08</v>
+        <v>6.492671977953821e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.387840617639984e-08</v>
+        <v>6.387840617639995e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.387840617639984e-08</v>
+        <v>6.387840617639995e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.387840617639984e-08</v>
+        <v>6.387840617639995e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.483023114426733e-08</v>
+        <v>8.48302311442671e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.134264453593883e-07</v>
+        <v>1.134264453593869e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.197428865616886e-07</v>
+        <v>1.19742886561689e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066365387311272e-07</v>
+        <v>1.066365387311282e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.661700396360249e-08</v>
+        <v>8.66170039636017e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.139046825000001e-07</v>
+        <v>1.139046825000012e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.137468394591594e-07</v>
+        <v>1.137468394591589e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.147951530617762e-07</v>
+        <v>1.147951530617765e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.137525223263663e-07</v>
+        <v>1.137525223263658e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.429309030479288e-08</v>
+        <v>8.429309030479206e-08</v>
       </c>
       <c r="L6" t="n">
         <v>1.4395265474334e-07</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.943341286111167e-07</v>
+        <v>1.943341286111012e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.371636747043358e-07</v>
+        <v>2.371636747043148e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.372040440025384e-07</v>
+        <v>2.372040440025186e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.87723305847204e-07</v>
+        <v>2.877233058471783e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.382523375007745e-07</v>
+        <v>2.382523375007541e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.373618722406659e-07</v>
+        <v>2.373618722406454e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.372040291993023e-07</v>
+        <v>2.372040291992824e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.382523428024406e-07</v>
+        <v>2.382523428024204e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.372040291993023e-07</v>
+        <v>2.372040291992824e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.113572971631249e-07</v>
+        <v>2.113572971631073e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372040291993023e-07</v>
+        <v>2.372040291992824e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.722201809973951e-07</v>
+        <v>5.722201809973931e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.19984645261241e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>2.859360368627567e-08</v>
+        <v>2.859360368627549e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.942787850283567e-07</v>
+        <v>9.942787850283559e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.942787850283567e-07</v>
+        <v>9.942787850283559e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.702305827206389e-07</v>
+        <v>5.70230582720637e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.795110563859544e-08</v>
+        <v>2.795110563859529e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.942787850283567e-07</v>
+        <v>9.942787850283559e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.381583323909192e-06</v>
+        <v>1.381583323909194e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.119052460771475e-07</v>
+        <v>6.119052460771181e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.692590912163312e-07</v>
+        <v>6.692590912163309e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.641472419444792e-07</v>
+        <v>5.641472419444775e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.182109300715924e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>2.93139998611843e-08</v>
+        <v>2.931399986118401e-08</v>
       </c>
       <c r="E9" t="n">
         <v>9.798825648238867e-07</v>
@@ -4770,22 +4770,22 @@
         <v>9.798825648238867e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.624835262685579e-07</v>
+        <v>5.624835262685559e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.905457417908434e-08</v>
+        <v>2.905457417908415e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.798825648238867e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361485920342494e-06</v>
+        <v>1.361485920342496e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.03240155577804e-07</v>
+        <v>6.032401555777749e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.598798565236771e-07</v>
+        <v>6.598798565236766e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.560961347220065e-07</v>
+        <v>3.560961347220091e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.531020946357712e-07</v>
+        <v>6.531020946357721e-07</v>
       </c>
       <c r="D2" t="n">
         <v>2.777235679896083e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.531020946357712e-07</v>
+        <v>6.531020946357721e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.531020946357712e-07</v>
+        <v>6.531020946357721e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>8.231272119052897e-07</v>
+        <v>8.231272119052904e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.942039671587986e-07</v>
+        <v>4.942039671588003e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.531020946357712e-07</v>
+        <v>6.531020946357721e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.684764984685209e-06</v>
+        <v>4.684764984685198e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.344568638617015e-07</v>
+        <v>6.34456863861704e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.237044952111574e-07</v>
+        <v>9.237044952111563e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.73974508951843e-08</v>
+        <v>6.739745089518424e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.859087087664944e-08</v>
+        <v>6.859087087664939e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.859087087664944e-08</v>
+        <v>6.85908708766494e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.516383999953648e-08</v>
+        <v>6.516383999953611e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.780933812941653e-08</v>
+        <v>6.780933812941655e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.469637756763035e-08</v>
+        <v>6.469637756763024e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.098877029529407e-07</v>
+        <v>1.098877029529405e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.373158931371558e-08</v>
+        <v>8.373158931371532e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.940774043682236e-08</v>
+        <v>7.940774043682212e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.198894315522429e-08</v>
+        <v>8.198894315522425e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.425617879239848e-08</v>
+        <v>8.425617879239842e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.156014313309012e-08</v>
+        <v>1.103551653848465e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.109272805104471e-08</v>
+        <v>1.1810917316867e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.130006635147269e-07</v>
+        <v>1.130006635147266e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.14362402624005e-07</v>
+        <v>1.143624026240046e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.082121162776525e-08</v>
+        <v>8.082121162776484e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.107175938146416e-08</v>
+        <v>8.107175938146376e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.676423622620796e-08</v>
+        <v>8.676423622620812e-08</v>
       </c>
       <c r="C5" t="n">
         <v>8.987719678799417e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.676277835289847e-08</v>
+        <v>8.676277835289911e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.011301921084401e-08</v>
+        <v>9.011301921084395e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.011301921084401e-08</v>
+        <v>9.011301921084395e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.723169865811411e-08</v>
+        <v>8.723169865811388e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.676423622620796e-08</v>
+        <v>8.676423622620812e-08</v>
       </c>
       <c r="I5" t="n">
         <v>8.987719678799417e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.676423622620796e-08</v>
+        <v>8.676423622620812e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.676423622620796e-08</v>
+        <v>8.676423622620812e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.676423622620796e-08</v>
+        <v>8.676423622620812e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.130123491631601e-07</v>
+        <v>1.130123491631595e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.561264561677584e-07</v>
+        <v>1.561264561677585e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.610248846178489e-07</v>
+        <v>1.61024884617849e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.452259628581426e-07</v>
+        <v>1.452259628581428e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.175274007191999e-07</v>
+        <v>1.175274007192e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.532464711462334e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.527790087144875e-07</v>
+        <v>1.527790087144882e-07</v>
       </c>
       <c r="I6" t="n">
         <v>1.558919692761135e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.527868238719592e-07</v>
+        <v>1.527868238719594e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.122736630564385e-07</v>
+        <v>1.122736630564387e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.943186097291787e-07</v>
+        <v>1.943186097291793e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.832825809701791e-07</v>
+        <v>2.832825809701794e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.507931927258474e-07</v>
+        <v>3.507931927258472e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.476802580091083e-07</v>
+        <v>3.47680258009108e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.251067224271194e-07</v>
+        <v>4.251067224271193e-07</v>
       </c>
       <c r="F7" t="n">
         <v>3.507931785745979e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.481476945959672e-07</v>
+        <v>3.481476945959669e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.476802321640612e-07</v>
+        <v>3.47680232164062e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.507931927258474e-07</v>
+        <v>3.507931927258472e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.476802321640612e-07</v>
+        <v>3.47680232164062e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.103679910235565e-07</v>
+        <v>3.103679910235574e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.476802321640612e-07</v>
+        <v>3.47680232164062e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.65289457013254e-07</v>
+        <v>9.652894570132538e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.197373097715513e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.672328457073084e-07</v>
+        <v>9.672328457073086e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.197373097715513e-06</v>
@@ -5126,22 +5126,22 @@
         <v>1.197373097715513e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.550233233214001e-07</v>
+        <v>9.550233233214009e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.634073528195443e-07</v>
+        <v>9.634073528195435e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.197373097715513e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.719132496815177e-07</v>
+        <v>8.719132496815174e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.589739079474124e-07</v>
+        <v>9.589739079474118e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.64567965495884e-07</v>
+        <v>9.544258566348231e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5157,7 +5157,7 @@
         <v>1.186895926487244e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.551093124164413e-07</v>
+        <v>9.551093124164407e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.186895926487244e-06</v>
@@ -5166,22 +5166,22 @@
         <v>1.186895926487244e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.501309858543979e-07</v>
+        <v>9.501309858543973e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.535592660464116e-07</v>
+        <v>9.535592660464103e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.186895926487244e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.163243769348025e-07</v>
+        <v>9.163243769348021e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.51746067447631e-07</v>
+        <v>9.517460674476301e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.540295713763991e-07</v>
+        <v>9.499062410252693e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.968825189032748e-07</v>
+        <v>1.96882518903276e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.648617551279033e-07</v>
+        <v>5.648617551279043e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.595006678443495e-07</v>
+        <v>2.595006678443443e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.648617551279033e-07</v>
+        <v>5.648617551279043e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.648617551279033e-07</v>
+        <v>5.648617551279043e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.293924905039503e-07</v>
+        <v>6.293924905039599e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.454916584920241e-07</v>
+        <v>4.454916584920243e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.648617551279033e-07</v>
+        <v>5.648617551279043e-07</v>
       </c>
       <c r="J2" t="n">
         <v>3.992482381813273e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.233694574212836e-07</v>
+        <v>5.233694574212837e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.611249086409633e-07</v>
+        <v>1.016135369881469e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309566e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.905329070027208e-08</v>
+        <v>5.905329070027209e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309571e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.013712750401048e-08</v>
+        <v>6.013712750401053e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.013712750401051e-08</v>
+        <v>6.013712750401053e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.835755863408798e-08</v>
+        <v>5.835755863408827e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309571e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.100391111263299e-08</v>
+        <v>6.1003911112633e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309571e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309571e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.78898048930952e-08</v>
+        <v>5.788980489309571e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.223961580027756e-08</v>
+        <v>9.592538001557454e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.465229649753332e-08</v>
+        <v>7.465229649753348e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.077614941218219e-08</v>
+        <v>7.077614941218306e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.327949749368415e-08</v>
+        <v>7.327949749368421e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.518674242454312e-08</v>
+        <v>7.518674242454317e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.270736954127055e-08</v>
+        <v>9.639313375656743e-08</v>
       </c>
       <c r="H4" t="n">
         <v>1.027861239810654e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.535372201981543e-08</v>
+        <v>9.903948623511205e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.461748556371343e-08</v>
+        <v>9.981514618538891e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.206051668620321e-08</v>
+        <v>7.206051668620383e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.214723458764019e-08</v>
+        <v>7.21472345876408e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.567383277576502e-08</v>
+        <v>7.567383277576498e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.878793899530291e-08</v>
+        <v>7.878793899530292e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.56730090710929e-08</v>
+        <v>7.567300907109335e-08</v>
       </c>
       <c r="E5" t="n">
         <v>7.853469720658336e-08</v>
@@ -5402,22 +5402,22 @@
         <v>7.853469720658336e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.614158651675793e-08</v>
+        <v>7.61415865167581e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.567383277576502e-08</v>
+        <v>7.567383277576503e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.878793899530291e-08</v>
+        <v>7.878793899530292e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.567383277576502e-08</v>
+        <v>7.567383277576503e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.567383277576502e-08</v>
+        <v>7.567383277576503e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.567383277576502e-08</v>
+        <v>7.567383277576503e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.72522017824712e-08</v>
+        <v>9.725220178247096e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.321476151558101e-07</v>
+        <v>1.321476151567018e-07</v>
       </c>
       <c r="D6" t="n">
         <v>1.359079900658172e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.234167309458512e-07</v>
+        <v>1.234167309458511e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.012306140696216e-07</v>
+        <v>1.012306140696215e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.29736835235486e-07</v>
+        <v>1.297368352354863e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2926908149473e-07</v>
+        <v>1.292690814947301e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.323831877140312e-07</v>
+        <v>1.323831877140311e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.292753736309899e-07</v>
+        <v>1.292753736309903e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.665747181245744e-08</v>
+        <v>9.665747181245764e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.627133894713952e-07</v>
+        <v>1.627133894713956e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.352757505984564e-07</v>
+        <v>2.352757505984565e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.904964125100594e-07</v>
+        <v>2.904964125100591e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.873823245087658e-07</v>
+        <v>2.873823245087659e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.506262729053702e-07</v>
+        <v>3.506262729053697e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.904963993062337e-07</v>
+        <v>2.904963993062331e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.878500600315145e-07</v>
+        <v>2.878500600315146e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.873823062905217e-07</v>
+        <v>2.873823062905214e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.904964125100594e-07</v>
+        <v>2.904964125100591e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.873823062905217e-07</v>
+        <v>2.873823062905214e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.217708469651424e-07</v>
+        <v>2.217708469651427e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.873823062905217e-07</v>
+        <v>2.873823062905214e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5513,7 +5513,7 @@
         <v>1.193267196643413e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.625094516831998e-07</v>
+        <v>9.625094516832004e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.193267196643413e-06</v>
@@ -5522,10 +5522,10 @@
         <v>1.193267196643413e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.535361665197506e-07</v>
+        <v>9.535361665197511e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.590571061370841e-07</v>
+        <v>9.590571061370852e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.193267196643413e-06</v>
@@ -5534,10 +5534,10 @@
         <v>8.759450991640322e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.553557572828937e-07</v>
+        <v>9.553557572828947e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.611522972909862e-07</v>
+        <v>9.461286957975025e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.511033658499039e-07</v>
+        <v>9.511033658499044e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.182289698969398e-06</v>
+        <v>1.182289698969399e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.504776424194978e-07</v>
+        <v>9.504776424194984e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.182289698969398e-06</v>
+        <v>1.182289698969399e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.182289698969398e-06</v>
+        <v>1.182289698969399e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.468232537008817e-07</v>
+        <v>9.46823253700882e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.490792858743453e-07</v>
+        <v>9.49079285874346e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.182289698969398e-06</v>
+        <v>1.182289698969399e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.152553438162461e-07</v>
+        <v>9.152553438162473e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.475644992253943e-07</v>
+        <v>9.475644992253947e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.438217111703406e-07</v>
+        <v>9.438217111703416e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.398673500217769e-07</v>
+        <v>2.39867350021765e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.149853463913447e-07</v>
+        <v>6.149853463913403e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.04400145292984e-07</v>
+        <v>3.044001452929847e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.149853463913447e-07</v>
+        <v>6.149853463913403e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.149853463913447e-07</v>
+        <v>6.149853463913403e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.116727542545965e-07</v>
+        <v>6.116727542544124e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.253182447689089e-07</v>
+        <v>4.253182447689147e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.149853463913447e-07</v>
+        <v>6.149853463913403e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.664070906609963e-06</v>
+        <v>3.664070906609947e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.838220254220767e-07</v>
+        <v>3.83822025422044e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.090090900055433e-07</v>
+        <v>3.090090900055488e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319946e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.393665913020973e-08</v>
+        <v>5.393665913020943e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319971e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.509325620716306e-08</v>
+        <v>5.509325620716305e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.509325620716307e-08</v>
+        <v>5.509325620716314e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.52968900591707e-08</v>
+        <v>5.529689005917092e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319971e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.794023501666341e-08</v>
+        <v>5.794023501666361e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319971e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319971e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.482968786319969e-08</v>
+        <v>5.482968786319971e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.841196973265062e-08</v>
+        <v>6.84119697326493e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.07295103682139e-08</v>
+        <v>7.072951036821381e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.214910656700446e-08</v>
+        <v>9.214910656700621e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.954237899580745e-08</v>
+        <v>6.954237899580737e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.136784127794926e-08</v>
+        <v>7.136784127795086e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.887917192862174e-08</v>
+        <v>6.887917192862017e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.737653416716405e-08</v>
+        <v>9.737653416716292e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.376592570880507e-08</v>
+        <v>9.376592570880459e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.46565185204019e-08</v>
+        <v>7.07365861205004e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.809283467624119e-08</v>
+        <v>6.809283467624168e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.844769381149408e-08</v>
+        <v>6.844769381149309e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.130587891965227e-08</v>
+        <v>7.130587891965207e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.4416426073116e-08</v>
+        <v>7.441642607311634e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.130547512987706e-08</v>
+        <v>7.130547512987668e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.357047423991299e-08</v>
+        <v>7.357047423991363e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.357047423991299e-08</v>
+        <v>7.357047423991363e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.177308111562326e-08</v>
+        <v>7.177308111562221e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.130587891965227e-08</v>
+        <v>7.1305878919652e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4416426073116e-08</v>
+        <v>7.441642607311634e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.130587891965227e-08</v>
+        <v>7.1305878919652e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.130587891965227e-08</v>
+        <v>7.1305878919652e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.130587891965227e-08</v>
+        <v>7.1305878919652e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.182134390365076e-08</v>
+        <v>9.182134390365202e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.239315618911926e-07</v>
+        <v>1.239315618911933e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.278042716320732e-07</v>
+        <v>1.278042716320722e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.158665772737773e-07</v>
+        <v>1.158665772737794e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.537219187795522e-08</v>
+        <v>9.5372191877954e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.220916136326177e-07</v>
+        <v>1.220916136326155e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.216244114368908e-07</v>
+        <v>1.216244114368896e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.247349585901105e-07</v>
+        <v>1.247349585901075e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.216302685095497e-07</v>
+        <v>1.216302685095492e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.126773663012741e-08</v>
+        <v>9.126773663012643e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.527562074898278e-07</v>
+        <v>1.527562074898243e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.148700249999861e-07</v>
+        <v>2.148700249999881e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.649821829130193e-07</v>
+        <v>2.64982182913005e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.618716535945754e-07</v>
+        <v>2.618716535945829e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.192210467329621e-07</v>
+        <v>3.192210467329735e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.649821712938654e-07</v>
+        <v>2.649821712938585e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.623388379555263e-07</v>
+        <v>2.623388379555337e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.618716357595557e-07</v>
+        <v>2.618716357595504e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.649821829130193e-07</v>
+        <v>2.64982182913005e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.618716357595557e-07</v>
+        <v>2.618716357595504e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.346387253972295e-07</v>
+        <v>2.346387253972321e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.618716357595557e-07</v>
+        <v>2.618716357595504e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.59979950043961e-07</v>
+        <v>9.599799500439634e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.188974659142724e-06</v>
+        <v>1.188974659142726e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.583496963008526e-07</v>
+        <v>9.583496963008532e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.188974659142724e-06</v>
+        <v>1.188974659142726e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.188974659142724e-06</v>
+        <v>1.188974659142726e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.50763641301008e-07</v>
+        <v>9.507636413010038e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.563610203375724e-07</v>
+        <v>9.563610203375739e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.188974659142724e-06</v>
+        <v>1.188974659142726e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.808188356371138e-07</v>
+        <v>8.808188356371153e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.557518307159802e-07</v>
+        <v>9.557518307159819e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.592810371159169e-07</v>
+        <v>9.592810371159171e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.47782734454083e-07</v>
+        <v>9.477827344540857e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.178941964164343e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.471189103033132e-07</v>
+        <v>9.471189103033147e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.178941964164343e-06</v>
@@ -5958,22 +5958,22 @@
         <v>1.178941964164343e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.440316567055504e-07</v>
+        <v>9.440316567055509e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.463165058678696e-07</v>
+        <v>9.463165058678702e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.178941964164343e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.155729087435037e-07</v>
+        <v>9.155729087435042e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.460611203535082e-07</v>
+        <v>9.460611203535101e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.475021557093149e-07</v>
+        <v>9.475021557093166e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.969081520027089e-07</v>
+        <v>3.969081520027084e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.229367595232684e-07</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.018701484619341e-07</v>
+        <v>3.018701484619327e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.229367595232684e-07</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.229367595232684e-07</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.201105697131449e-07</v>
+        <v>6.201105697131402e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.883587143939524e-07</v>
+        <v>3.883587143939523e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.229367595232684e-07</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.138392858270241e-06</v>
+        <v>4.138392858270232e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.752498235558046e-07</v>
+        <v>5.752498235558027e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.706752325266192e-06</v>
+        <v>4.899771097310254e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.83505369811473e-08</v>
+        <v>5.835053698114726e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.968801715928855e-08</v>
+        <v>5.968801715928852e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.968801715928855e-08</v>
+        <v>5.968801715928852e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.906513040302765e-08</v>
+        <v>5.906513040302736e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.167724093411512e-08</v>
+        <v>6.167724093411511e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.860391420116018e-08</v>
+        <v>5.860391420115937e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.292855088204987e-08</v>
+        <v>7.292855088204951e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.487557007779527e-08</v>
+        <v>7.487557007779539e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.159761745789661e-08</v>
+        <v>1.004180843924457e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.349245999633202e-08</v>
+        <v>7.349245999633197e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.578370555964563e-08</v>
+        <v>7.578370555964555e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.86470974644211e-08</v>
+        <v>7.338976708391723e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.065811553528126e-07</v>
+        <v>1.065811553528116e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.012592079955085e-07</v>
+        <v>7.600187761500524e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.031350439096038e-07</v>
+        <v>1.031350439096031e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>7.278185614642497e-08</v>
+        <v>7.278185614642478e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.296101933719053e-08</v>
+        <v>7.296101933718987e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.730533202570369e-08</v>
+        <v>7.730533202570356e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.037865875865918e-08</v>
+        <v>8.037865875865922e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.73046739031297e-08</v>
+        <v>7.730467390312971e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.984454206426356e-08</v>
+        <v>7.984454206426361e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.984454206426356e-08</v>
+        <v>7.984454206426361e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.776654822757186e-08</v>
+        <v>7.776654822757123e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.730533202570369e-08</v>
+        <v>7.730533202570356e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.037865875865918e-08</v>
+        <v>8.037865875865922e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.730533202570369e-08</v>
+        <v>7.730533202570356e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.730533202570369e-08</v>
+        <v>7.730533202570356e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.730533202570369e-08</v>
+        <v>7.730533202570356e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.008789276429574e-07</v>
+        <v>1.008789276429571e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.381277104209744e-07</v>
+        <v>1.381277104199427e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.427492372831631e-07</v>
+        <v>1.427492372831625e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.286972101252929e-07</v>
+        <v>1.28697210125293e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.047333015808153e-07</v>
+        <v>1.047333015808154e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.360194694207557e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.355582532190536e-07</v>
+        <v>1.35558253219053e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.386315799518433e-07</v>
+        <v>1.386315799518435e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.355650685893209e-07</v>
+        <v>1.355650685893203e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.00234741374535e-07</v>
+        <v>1.002347413745346e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.717837085197349e-07</v>
+        <v>1.71783708519735e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.688713720580463e-07</v>
+        <v>2.688713720580458e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.33498137117382e-07</v>
+        <v>3.334981371173817e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.304248352224622e-07</v>
+        <v>3.304248352224619e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.045295091840252e-07</v>
+        <v>4.045295091840249e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.334981266603181e-07</v>
+        <v>3.334981266603179e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.308860265862942e-07</v>
+        <v>3.308860265862938e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.304248103844265e-07</v>
+        <v>3.304248103844258e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.33498137117382e-07</v>
+        <v>3.334981371173817e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.304248103844265e-07</v>
+        <v>3.304248103844258e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.529180378441518e-07</v>
+        <v>2.947605169258929e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.304248103844265e-07</v>
+        <v>3.304248103844258e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.592860285960924e-07</v>
+        <v>9.592860285960918e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.197246761700717e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.615840604008918e-07</v>
+        <v>9.615840604008914e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.197246761700717e-06</v>
@@ -6314,22 +6314,22 @@
         <v>1.197246761700717e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.540161238500728e-07</v>
+        <v>9.540161238500721e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.602995891377659e-07</v>
+        <v>9.602995891377657e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.197246761700717e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.78764798028547e-07</v>
+        <v>8.787647980285461e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.54730897319074e-07</v>
+        <v>9.547308973190734e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.58590038297739e-07</v>
+        <v>9.328338525724903e-07</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.49052970281303e-07</v>
+        <v>9.490529702813018e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.183594503542899e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.499890970430216e-07</v>
+        <v>9.49989097043021e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.183594503542899e-06</v>
@@ -6354,22 +6354,22 @@
         <v>1.183594503542899e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.46886767322105e-07</v>
+        <v>9.468867673221043e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.49472349518432e-07</v>
+        <v>9.494723495184314e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.183594503542899e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.162909823430216e-07</v>
+        <v>9.162909823430212e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.471983618608593e-07</v>
+        <v>9.47198361860858e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.383049294554578e-07</v>
+        <v>9.48776131937759e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.727870798792139e-07</v>
+        <v>1.72787079879214e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>5.108427244839812e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.156547014459424e-07</v>
+        <v>5.156547014459429e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>5.108427244839812e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>5.108427244839812e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.747169855348137e-07</v>
+        <v>6.747169855348104e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.354918971803248e-07</v>
+        <v>3.354918971803247e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>5.108427244839812e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.46997948197067e-06</v>
+        <v>2.469979481970668e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.253197565402279e-07</v>
+        <v>4.25319756540229e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.629948173332109e-07</v>
+        <v>5.629948173332102e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.399713790114905e-08</v>
+        <v>5.399713790114899e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.502038858557966e-08</v>
+        <v>5.502038858557964e-08</v>
       </c>
       <c r="F3" t="n">
         <v>5.502038858557966e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.440623733886753e-08</v>
+        <v>5.440623733886681e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.701291601858971e-08</v>
+        <v>5.701291601858965e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3945594922532e-08</v>
+        <v>5.394559492253225e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.531602235901444e-08</v>
+        <v>8.70123614221464e-08</v>
       </c>
       <c r="C4" t="n">
         <v>6.760262663879413e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.475188252241799e-08</v>
+        <v>6.475172933807698e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.664750893541328e-08</v>
+        <v>6.664750893541323e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.833029116893818e-08</v>
+        <v>6.833029116893815e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.577666477534965e-08</v>
+        <v>6.577666477535055e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.284810059040807e-08</v>
+        <v>6.534343628334485e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.838334345507209e-08</v>
+        <v>6.838334345507201e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.729345154843856e-08</v>
+        <v>9.128495905584146e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.463714951648908e-08</v>
+        <v>6.463714951648976e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.543294855959454e-08</v>
+        <v>6.543294855959384e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.973763256699548e-08</v>
+        <v>6.97376325669955e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.280495366305301e-08</v>
+        <v>7.280495366305295e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.973703541565855e-08</v>
+        <v>6.973703541565846e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.224148344778333e-08</v>
+        <v>7.224148344778329e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.224148344778333e-08</v>
+        <v>7.224148344778329e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.019827498333055e-08</v>
+        <v>7.019827498333137e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.973763256699548e-08</v>
+        <v>6.97376325669955e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.280495366305301e-08</v>
+        <v>7.280495366305295e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.973763256699548e-08</v>
+        <v>6.97376325669955e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.973763256699548e-08</v>
+        <v>6.97376325669955e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.973763256699548e-08</v>
+        <v>6.97376325669955e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.913781908831146e-08</v>
+        <v>8.913781908831212e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.198409192926175e-07</v>
+        <v>1.198409192926174e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.23147977675152e-07</v>
+        <v>1.231479776751514e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.121940777571658e-07</v>
+        <v>1.121940777571657e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.276227641757619e-08</v>
+        <v>9.27622764175761e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.177675716117381e-07</v>
+        <v>1.177675716117385e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.173069291953869e-07</v>
+        <v>1.173069291953864e-07</v>
       </c>
       <c r="I6" t="n">
         <v>1.203742502914603e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.173124651593437e-07</v>
+        <v>1.173124651593429e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.86145634117106e-08</v>
+        <v>8.861456341171023e-08</v>
       </c>
       <c r="L6" t="n">
         <v>1.467319200979988e-07</v>
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.304213879858233e-07</v>
+        <v>2.304213879858232e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848220774795363e-07</v>
+        <v>2.848220774795362e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.817547815942713e-07</v>
+        <v>2.817547815942701e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.440597097362104e-07</v>
+        <v>3.4405970973621e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.848220701027334e-07</v>
+        <v>2.848220701027333e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.822153987998137e-07</v>
+        <v>2.822153987998139e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.817547563834789e-07</v>
+        <v>2.81754756383478e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848220774795363e-07</v>
+        <v>2.848220774795362e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.817547563834789e-07</v>
+        <v>2.81754756383478e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.508053099918383e-07</v>
+        <v>2.508053099918374e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.817547563834789e-07</v>
+        <v>2.81754756383478e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,34 +6695,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.602895140529447e-07</v>
+        <v>9.60289514052944e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.189484380474566e-06</v>
+        <v>1.189484380474567e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.506776638253949e-07</v>
+        <v>9.506776638253945e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.189484380474566e-06</v>
+        <v>1.189484380474567e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.189484380474566e-06</v>
+        <v>1.189484380474567e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.470008697156013e-07</v>
+        <v>9.47000869715601e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.566076163338546e-07</v>
+        <v>9.566076163338544e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.189484380474566e-06</v>
+        <v>1.189484380474567e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.032896156218804e-07</v>
+        <v>9.032896156218801e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.5347785602257e-07</v>
+        <v>9.534778560225699e-07</v>
       </c>
       <c r="L8" t="n">
         <v>9.613822779078152e-07</v>
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.470790844882116e-07</v>
+        <v>9.47079084488211e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.177849092694762e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.43164572232215e-07</v>
+        <v>9.431645722322149e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.177849092694762e-06</v>
@@ -6750,22 +6750,22 @@
         <v>1.177849092694762e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.416515786379545e-07</v>
+        <v>9.416515786379535e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.455856410445464e-07</v>
+        <v>9.455856410445466e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.177849092694762e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.238862592037777e-07</v>
+        <v>9.238862592037774e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.443052557190064e-07</v>
+        <v>9.443052557190063e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.434164754260603e-07</v>
+        <v>9.475255633350877e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.820193323740755e-07</v>
+        <v>1.82019332374075e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.553456445086601e-07</v>
+        <v>6.553456445086613e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.11333885179225e-07</v>
+        <v>4.113338851792241e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.553456445086601e-07</v>
+        <v>6.553456445086613e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.553456445086601e-07</v>
+        <v>6.553456445086613e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.080152697677241e-07</v>
+        <v>6.080152697677407e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.978107569365768e-07</v>
+        <v>3.978107569365772e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.553456445086601e-07</v>
+        <v>6.553456445086613e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.045317346214749e-06</v>
+        <v>2.045317346214746e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.218609484135253e-07</v>
+        <v>3.218609484135259e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.263753521252713e-07</v>
+        <v>2.246737150840503e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.303252058156959e-08</v>
+        <v>5.303252058156963e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.395905034587972e-08</v>
+        <v>5.395905034587981e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.395905034587973e-08</v>
+        <v>5.395905034587978e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.315811105959113e-08</v>
+        <v>5.315811105959152e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.580792028958771e-08</v>
+        <v>5.580792028958779e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.268930812069938e-08</v>
+        <v>5.268930812069904e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.340284777611403e-08</v>
+        <v>6.340284777611119e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.6187311138517e-08</v>
+        <v>6.618731113851724e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.556123842342602e-08</v>
+        <v>6.275322720317992e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.534783775919296e-08</v>
+        <v>6.534783775919299e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.656276689062058e-08</v>
+        <v>6.656276689062066e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.387165071500512e-08</v>
+        <v>8.439843229131308e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.889001148127692e-08</v>
+        <v>8.889001148127745e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.652145994500186e-08</v>
+        <v>6.652145994500366e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.517224100358689e-08</v>
+        <v>8.801284138634334e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.261093872624772e-08</v>
+        <v>6.261093872624697e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.357429231382496e-08</v>
+        <v>6.35742923138249e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.760390411068558e-08</v>
+        <v>6.760390411068634e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.072251627957501e-08</v>
+        <v>7.072251627957506e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.760330230693144e-08</v>
+        <v>6.760330230693156e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.015231055228742e-08</v>
+        <v>7.015231055228756e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.015231055228742e-08</v>
+        <v>7.015231055228756e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.807270704957931e-08</v>
+        <v>6.807270704957882e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.760390411068558e-08</v>
+        <v>6.760390411068634e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.072251627957501e-08</v>
+        <v>7.072251627957506e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.760390411068558e-08</v>
+        <v>6.760390411068634e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.760390411068558e-08</v>
+        <v>6.760390411068634e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.760390411068558e-08</v>
+        <v>6.760390411068634e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.571017254152741e-08</v>
+        <v>8.571017254152694e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.14396023237107e-07</v>
+        <v>1.143960232375076e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.172311479368948e-07</v>
+        <v>1.172311479368945e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.073137769005131e-07</v>
+        <v>1.073137769005133e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.931655356741944e-08</v>
+        <v>8.931655356741948e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.122864052446022e-07</v>
+        <v>1.122864052446014e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.118176023055835e-07</v>
+        <v>1.118176023055836e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.149362144745975e-07</v>
+        <v>1.149362144745977e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.118227331044265e-07</v>
+        <v>1.118227331044253e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.522521363453013e-08</v>
+        <v>8.522521363452935e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.390889957084217e-07</v>
+        <v>1.390889957084214e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7054,34 +7054,34 @@
         <v>2.114822788659347e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.60747137548268e-07</v>
+        <v>2.607471375482682e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.576285450506062e-07</v>
+        <v>2.576285450506057e-07</v>
       </c>
       <c r="E7" t="n">
         <v>3.139989364887204e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6074713046031e-07</v>
+        <v>2.607471304603101e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.580973283182722e-07</v>
+        <v>2.58097328318272e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.576285253793797e-07</v>
+        <v>2.576285253793794e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.60747137548268e-07</v>
+        <v>2.607471375482682e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.576285253793797e-07</v>
+        <v>2.576285253793794e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.308912171928326e-07</v>
+        <v>2.298064500273432e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.576285253793797e-07</v>
+        <v>2.576285253793794e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.580715571454849e-07</v>
+        <v>9.580715571454845e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.184255866847179e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.519747947008154e-07</v>
+        <v>9.51974794700815e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.184255866847179e-06</v>
@@ -7106,10 +7106,10 @@
         <v>1.184255866847179e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.47196904475291e-07</v>
+        <v>9.471969044752903e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.533902824056248e-07</v>
+        <v>9.533902824056247e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.184255866847179e-06</v>
@@ -7118,10 +7118,10 @@
         <v>9.128451095632979e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.541718630517402e-07</v>
+        <v>9.541718630517404e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.503454513300549e-07</v>
+        <v>9.50345451330055e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.450410572403338e-07</v>
+        <v>9.450410572403333e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.174794047074503e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.425581315496526e-07</v>
+        <v>9.425581315496517e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.174794047074503e-06</v>
@@ -7146,22 +7146,22 @@
         <v>1.174794047074503e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.406221970404848e-07</v>
+        <v>9.406221970404837e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.431417473113777e-07</v>
+        <v>9.431417473113775e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.174794047074503e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.266390912835078e-07</v>
+        <v>9.266390912835076e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.434531126198851e-07</v>
+        <v>9.434531126198844e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.419024237229948e-07</v>
+        <v>9.448565393588735e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.06222654356799e-07</v>
+        <v>5.062226543567986e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.671049605677917e-07</v>
+        <v>6.671049605677908e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.560460404301907e-07</v>
+        <v>2.560460404301913e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.671049605677917e-07</v>
+        <v>6.671049605677908e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671049605677917e-07</v>
+        <v>6.671049605677908e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>7.718337712660476e-07</v>
+        <v>7.718337712660448e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.842551739745267e-07</v>
+        <v>4.842551739745289e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.671049605677917e-07</v>
+        <v>6.671049605677908e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.554122772374572e-06</v>
+        <v>3.554122772374571e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.244263381076666e-07</v>
+        <v>6.244263381076681e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.203568833445771e-07</v>
+        <v>4.203568833445779e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.294723086391631e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.465739713047128e-08</v>
+        <v>6.465739713047138e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.294723086391631e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.590768192698672e-08</v>
+        <v>6.59076819269868e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.590768192698672e-08</v>
+        <v>6.590768192698679e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.341522600175851e-08</v>
+        <v>6.341522600175861e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.294723086391631e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.606375380082352e-08</v>
+        <v>6.606375380082363e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.29472308639163e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.294723086391631e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.294723086391631e-08</v>
+        <v>6.294723086391633e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.853735851410265e-08</v>
+        <v>7.853735851410272e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.117223279961631e-08</v>
+        <v>8.117223279961612e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.687313259016676e-08</v>
+        <v>7.687313259016674e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.95737425193779e-08</v>
+        <v>7.957374251937678e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.172294182451208e-08</v>
+        <v>8.172294182451203e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.069571174037821e-07</v>
+        <v>1.069571174037823e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.147616996408724e-07</v>
+        <v>1.147616996408725e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.16538814510099e-08</v>
+        <v>1.096056452028473e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.112431940312954e-07</v>
+        <v>1.112431940312955e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>7.836832895530324e-08</v>
+        <v>7.836832895530327e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.858523912277071e-08</v>
+        <v>7.858523912277076e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.367362809985323e-08</v>
+        <v>8.367362809985333e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.679015103676047e-08</v>
+        <v>8.679015103676064e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.367244904557218e-08</v>
+        <v>8.367244904557228e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.675166253061034e-08</v>
+        <v>8.675166253061045e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.675166253061034e-08</v>
+        <v>8.675166253061045e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.414162323769541e-08</v>
+        <v>8.414162323769557e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.367362809985323e-08</v>
+        <v>8.367362809985333e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.679015103676047e-08</v>
+        <v>8.679015103676064e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.367362809985323e-08</v>
+        <v>8.367362809985333e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.367362809985323e-08</v>
+        <v>8.367362809985333e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.367362809985323e-08</v>
+        <v>8.367362809985333e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.088407724338533e-07</v>
+        <v>1.088407724338534e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497290795650209e-07</v>
+        <v>1.497290795665471e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.544793048037804e-07</v>
+        <v>1.544793048037807e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.393943686858498e-07</v>
+        <v>1.393943686858502e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.13133252152997e-07</v>
+        <v>1.131332521529973e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.471091453686373e-07</v>
+        <v>1.471091453686375e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466411502309141e-07</v>
+        <v>1.466411502309143e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.497576731677022e-07</v>
+        <v>1.497576731677026e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.466485789634857e-07</v>
+        <v>1.466485789634861e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.081386110195877e-07</v>
+        <v>1.081386110195879e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.861268055411397e-07</v>
+        <v>1.861268055411403e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.796060956004484e-07</v>
+        <v>2.796060956004486e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4640135858232e-07</v>
+        <v>3.464013585823207e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.432848615408191e-07</v>
+        <v>3.432848615408195e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.198852831165366e-07</v>
+        <v>4.198852831165373e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.464013468389853e-07</v>
+        <v>3.46401346838986e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.437528307832548e-07</v>
+        <v>3.437528307832554e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.432848356454129e-07</v>
+        <v>3.432848356454133e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4640135858232e-07</v>
+        <v>3.464013585823207e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.432848356454129e-07</v>
+        <v>3.432848356454133e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.048922282155768e-07</v>
+        <v>3.063891344691541e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.432848356454129e-07</v>
+        <v>3.432848356454133e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.598131685813156e-07</v>
+        <v>9.598131685813158e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.195013134710443e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.659021162909778e-07</v>
+        <v>9.65902116290978e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.195013134710443e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.195013134710443e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.539473993370026e-07</v>
+        <v>9.53947399337002e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.613582117981294e-07</v>
+        <v>9.613582117981299e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.195013134710443e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.945598358425242e-07</v>
+        <v>8.945598358425241e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.570887758942141e-07</v>
+        <v>9.570887758942139e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.384773749156308e-07</v>
+        <v>9.63316503016842e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7530,34 +7530,34 @@
         <v>9.510347979893053e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.184813155924982e-06</v>
+        <v>1.184813155924981e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.535149067236383e-07</v>
+        <v>9.535149067236387e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.184813155924982e-06</v>
+        <v>1.184813155924981e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.184813155924982e-06</v>
+        <v>1.184813155924981e-06</v>
       </c>
       <c r="G9" t="n">
         <v>9.486429195383485e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.516724887813913e-07</v>
+        <v>9.516724887813905e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.184813155924982e-06</v>
+        <v>1.184813155924981e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.244864602515112e-07</v>
+        <v>9.244864602515114e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.499258737056274e-07</v>
+        <v>9.499258737056276e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.423686817430951e-07</v>
+        <v>9.524670382604044e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.984562540200128e-07</v>
+        <v>1.984562540200129e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.67957410715379e-07</v>
+        <v>5.679574107153634e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.579252718966955e-07</v>
+        <v>4.579252718966981e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.679574107153789e-07</v>
+        <v>5.679574107153634e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.679574107153789e-07</v>
+        <v>5.679574107153634e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.595927124764865e-07</v>
+        <v>6.595927124765129e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.309112799012107e-07</v>
+        <v>3.30911279901211e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.67957410715379e-07</v>
+        <v>5.679574107153634e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.203828208276984e-06</v>
+        <v>3.203828208276981e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.341222405233023e-07</v>
+        <v>4.341222405233018e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>6.446636552686845e-07</v>
+        <v>5.742624636048826e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.648613816354751e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.724101265926808e-08</v>
+        <v>5.724101265926788e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.648613816354751e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.830232435828826e-08</v>
+        <v>5.830232435828817e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.830232435828826e-08</v>
+        <v>5.830232435828816e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.695146291902421e-08</v>
+        <v>5.695146291902348e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.648613816354704e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.958420465312273e-08</v>
+        <v>5.958420465312265e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.648613816354751e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.648613816354751e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.648613816354751e-08</v>
+        <v>5.648613816354677e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.961663120971039e-08</v>
+        <v>9.266190658235317e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.209182042454034e-08</v>
+        <v>7.20918204245405e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.874885201663605e-08</v>
+        <v>6.874885201663269e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.08848540861464e-08</v>
+        <v>7.088485408614574e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.26781149300934e-08</v>
+        <v>7.267811493009334e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.312723133783049e-08</v>
+        <v>7.008195596518686e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.938523782923766e-08</v>
+        <v>9.938523782923768e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.575997307192934e-08</v>
+        <v>9.575997307192908e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.686663426690837e-08</v>
+        <v>7.183051625962772e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.919266782289967e-08</v>
+        <v>6.919266782289999e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.979487387080499e-08</v>
+        <v>6.979487387080524e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.333671928682741e-08</v>
+        <v>7.33367192868272e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.643478577640301e-08</v>
+        <v>7.643478577640306e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.333597864569289e-08</v>
+        <v>7.33359786456929e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.606582906959384e-08</v>
+        <v>7.60658290695939e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.606582906959384e-08</v>
+        <v>7.60658290695939e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.380204404230418e-08</v>
+        <v>7.380204404230385e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.333671928682741e-08</v>
+        <v>7.33367192868272e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.643478577640301e-08</v>
+        <v>7.643478577640306e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.333671928682741e-08</v>
+        <v>7.33367192868272e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.333671928682741e-08</v>
+        <v>7.33367192868272e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.333671928682741e-08</v>
+        <v>7.33367192868272e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.400845676587559e-08</v>
+        <v>9.400845676587588e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.271386430603763e-07</v>
+        <v>1.271386430611337e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.306864919480155e-07</v>
+        <v>1.306864919480152e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.188675929819749e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.784982542253037e-08</v>
+        <v>9.784982542253027e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.248525758142737e-07</v>
+        <v>1.248525758142736e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.243872510589561e-07</v>
+        <v>1.243872510589558e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.274853175483727e-07</v>
+        <v>1.274853175483728e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.243932212735461e-07</v>
+        <v>1.24393221273546e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.344415507262027e-08</v>
+        <v>9.344415507262006e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.561204418495446e-07</v>
+        <v>1.561204418495441e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.339802182581247e-07</v>
+        <v>2.339802182581242e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.890106407041829e-07</v>
+        <v>2.89010640704183e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.859125977697169e-07</v>
+        <v>2.859125977697173e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.489394891022996e-07</v>
+        <v>3.489394891022995e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.89010632284056e-07</v>
+        <v>2.890106322840555e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.863778989700827e-07</v>
+        <v>2.863778989700832e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.859125742146081e-07</v>
+        <v>2.859125742146069e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.890106407041829e-07</v>
+        <v>2.89010640704183e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.859125742146081e-07</v>
+        <v>2.859125742146069e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.558227731265065e-07</v>
+        <v>2.20520462067668e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.859125742146081e-07</v>
+        <v>2.859125742146069e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.621942091671551e-07</v>
+        <v>9.621942091671553e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.191094169148416e-06</v>
+        <v>1.191094169148415e-06</v>
       </c>
       <c r="D8" t="n">
         <v>9.552097875347029e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191094169148416e-06</v>
+        <v>1.191094169148415e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191094169148416e-06</v>
+        <v>1.191094169148415e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.503852576339488e-07</v>
+        <v>9.503852576339491e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.594910966189629e-07</v>
+        <v>9.594910966189632e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191094169148416e-06</v>
+        <v>1.191094169148415e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.924718252191186e-07</v>
+        <v>8.924718252191181e-07</v>
       </c>
       <c r="K8" t="n">
         <v>9.55828554066831e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.539561196565781e-07</v>
+        <v>9.530545946794433e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>9.493138418347028e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.180242318970955e-06</v>
+        <v>1.180242318970954e-06</v>
       </c>
       <c r="D9" t="n">
         <v>9.464694110313826e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.180242318970955e-06</v>
+        <v>1.180242318970954e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.180242318970955e-06</v>
+        <v>1.180242318970954e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.444993911146541e-07</v>
+        <v>9.444993911146547e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.482187085352912e-07</v>
+        <v>9.482187085352908e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.180242318970955e-06</v>
+        <v>1.180242318970954e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.209443160471569e-07</v>
+        <v>9.209443160471563e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.467216759317001e-07</v>
+        <v>9.467216759316999e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.459673236730038e-07</v>
+        <v>9.4560095150249e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ozone depletion results.xlsx
+++ b/Results/Hydrogen/hydrogen ozone depletion results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.651706613531691e-07</v>
+        <v>6.651706613531729e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.145166026168618e-07</v>
+        <v>9.145166026168603e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.886506705675614e-07</v>
+        <v>3.886506705675617e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>9.145166026168618e-07</v>
+        <v>9.145166026168603e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>9.145166026168618e-07</v>
+        <v>9.145166026168603e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.170287915693594e-06</v>
+        <v>1.170287915693583e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583624398793637e-07</v>
+        <v>7.583624398793613e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.145166026168618e-07</v>
+        <v>9.145166026168603e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.710107555988487e-06</v>
+        <v>3.710107555988503e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>8.000979962771264e-07</v>
+        <v>8.000979962771263e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.858056405541034e-06</v>
+        <v>5.283447018299208e-07</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>7.146815117158667e-08</v>
+        <v>7.146815117158661e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>7.289208792807718e-08</v>
+        <v>7.289208792807714e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>7.289208792807715e-08</v>
+        <v>7.289208792807714e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.979649723668912e-08</v>
+        <v>6.97964972366892e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>7.242081946543865e-08</v>
+        <v>7.242081946543869e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.933311182666962e-08</v>
+        <v>6.933311182666949e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.736415401978694e-08</v>
+        <v>8.736415401978689e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.990345209973983e-08</v>
+        <v>8.990345209973942e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.601925736621136e-08</v>
+        <v>8.601949473044726e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.796760607962465e-08</v>
+        <v>8.796760607962473e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>9.060176395991121e-08</v>
+        <v>9.060176395991117e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.220987756510045e-07</v>
+        <v>1.220987756510046e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.310842478698961e-07</v>
+        <v>1.310842478698963e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.045186165855604e-08</v>
+        <v>1.247230978797541e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.019489769561394e-08</v>
+        <v>1.268610746429592e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.686774140965348e-08</v>
+        <v>8.686774140965324e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.737489341768635e-08</v>
+        <v>8.737489341768643e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.558818217367317e-08</v>
+        <v>9.558818217367315e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.86758898124425e-08</v>
+        <v>9.867588981244244e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.558656465495119e-08</v>
+        <v>9.558656465495107e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.883174185922798e-08</v>
+        <v>9.883174185922789e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.883174185922798e-08</v>
+        <v>9.883174185922789e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.605156758369288e-08</v>
+        <v>9.605156758369289e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.558818217367317e-08</v>
+        <v>9.558818217367315e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.86758898124425e-08</v>
+        <v>9.867588981244244e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.558818217367317e-08</v>
+        <v>9.558818217367315e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.558818217367317e-08</v>
+        <v>9.558818217367315e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.558818217367317e-08</v>
+        <v>9.558818217367315e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.264874851429994e-07</v>
+        <v>1.264874851429993e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.768963367531962e-07</v>
+        <v>1.768963367553359e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.834282182585281e-07</v>
+        <v>1.834282182585277e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.639813380197949e-07</v>
+        <v>1.639813380197947e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.311640775478343e-07</v>
+        <v>1.311640775478342e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.741123613369167e-07</v>
+        <v>1.741123613369166e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.736489759269884e-07</v>
+        <v>1.736489759269881e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.767366835656663e-07</v>
+        <v>1.767366835656661e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.736582443555255e-07</v>
+        <v>1.736582443555252e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.256114362518045e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.229130964863803e-07</v>
+        <v>2.229130964863801e-07</v>
       </c>
     </row>
     <row r="7">
@@ -715,34 +715,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.450186398299922e-07</v>
+        <v>3.450186398299924e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>4.290694212158803e-07</v>
+        <v>4.290694212158801e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>4.259817466955903e-07</v>
+        <v>4.259817466955902e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>5.224990991591157e-07</v>
+        <v>5.224990991591156e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>4.290694032919893e-07</v>
+        <v>4.290694032919895e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>4.26445098987131e-07</v>
+        <v>4.264450989871308e-07</v>
       </c>
       <c r="H7" t="n">
         <v>4.25981713577111e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>4.290694212158803e-07</v>
+        <v>4.290694212158801e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>4.25981713577111e-07</v>
+        <v>4.259817135771109e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.790714046110026e-07</v>
+        <v>3.240347432883453e-07</v>
       </c>
       <c r="L7" t="n">
         <v>4.25981713577111e-07</v>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.61884753061853e-07</v>
+        <v>9.618847530618522e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.196254784845937e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.681262228516213e-07</v>
+        <v>9.681262228516215e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.196254784845937e-06</v>
@@ -770,22 +770,22 @@
         <v>1.196254784845937e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.519081480508303e-07</v>
+        <v>9.519081480508309e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.619239155570966e-07</v>
+        <v>9.619239155570971e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.196254784845937e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.010721441791365e-07</v>
+        <v>9.010721441791361e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.592999478218274e-07</v>
+        <v>9.592999478218282e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.212678980879048e-07</v>
+        <v>9.212678980879043e-07</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.546022317476426e-07</v>
+        <v>9.546022317476422e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.18832437254474e-06</v>
+        <v>1.188324372544741e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.57144527155774e-07</v>
+        <v>9.571445271557733e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.18832437254474e-06</v>
+        <v>1.188324372544741e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.18832437254474e-06</v>
+        <v>1.188324372544741e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.505259064902517e-07</v>
+        <v>9.505259064902516e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.546304251772356e-07</v>
+        <v>9.546304251772352e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.18832437254474e-06</v>
+        <v>1.188324372544741e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.298618767373179e-07</v>
+        <v>9.29861876737318e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.5355029161594e-07</v>
+        <v>9.535502916159398e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.380994068155221e-07</v>
+        <v>9.565226839205542e-07</v>
       </c>
     </row>
   </sheetData>
@@ -914,34 +914,34 @@
         <v>1.475130347171903e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.838389911660797e-07</v>
+        <v>6.838389911660792e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.439260096538676e-07</v>
+        <v>4.439260096538662e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.838389911660797e-07</v>
+        <v>6.838389911660792e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.838389911660797e-07</v>
+        <v>6.838389911660792e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.186226459757308e-07</v>
+        <v>6.186226459757295e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.675904616680559e-07</v>
+        <v>3.675904616680553e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.838389911660797e-07</v>
+        <v>6.838389911660792e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.726095295142048e-06</v>
+        <v>2.726095295142049e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.446507954769099e-07</v>
+        <v>5.446507954769093e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.753245644778113e-07</v>
+        <v>1.753245644778097e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.444262604538207e-08</v>
+        <v>5.444262604538139e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.547887594297947e-08</v>
+        <v>5.547887594297984e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.547887594297948e-08</v>
+        <v>5.547887594298086e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.490934771142485e-08</v>
+        <v>5.49093477114241e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.756452016117498e-08</v>
+        <v>5.756452016117526e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.443971439316314e-08</v>
+        <v>5.443971439316263e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.789894961482968e-08</v>
+        <v>6.651514678564649e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.924052549911983e-08</v>
+        <v>6.924052549912012e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.974800379447457e-08</v>
+        <v>8.974800379447538e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.821874712574174e-08</v>
+        <v>6.821874712574116e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.968366978411643e-08</v>
+        <v>6.968366978411532e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.698478010390939e-08</v>
+        <v>8.836858293309386e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.450549148719122e-08</v>
+        <v>9.450549148719053e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.963995255365937e-08</v>
+        <v>6.963995255365935e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.221353818243163e-08</v>
+        <v>6.858014111086841e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.629819472816416e-08</v>
+        <v>6.629819472816505e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.665318060853909e-08</v>
+        <v>6.665318060854031e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.030873602672543e-08</v>
+        <v>7.030873602672601e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.34335417947373e-08</v>
+        <v>7.34335417947353e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.030817142273467e-08</v>
+        <v>7.030817142273557e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.279352432970152e-08</v>
+        <v>7.279352432970044e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.279352432970152e-08</v>
+        <v>7.279352432970071e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.077836934498714e-08</v>
+        <v>7.077836934498628e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.030873602672543e-08</v>
+        <v>7.030873602672601e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.34335417947373e-08</v>
+        <v>7.34335417947353e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.030873602672543e-08</v>
+        <v>7.030873602672601e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.030873602672543e-08</v>
+        <v>7.030873602672601e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.030873602672543e-08</v>
+        <v>7.030873602672601e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.970295806046441e-08</v>
+        <v>8.970295806046272e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.204650566046912e-07</v>
+        <v>1.204650566051792e-07</v>
       </c>
       <c r="D6" t="n">
         <v>1.238033691448631e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.128055641474686e-07</v>
+        <v>1.128055641474674e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.334158602433062e-08</v>
+        <v>9.334158602433013e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.184164536378078e-07</v>
+        <v>1.184164536378084e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.179468203197186e-07</v>
+        <v>1.179468203197195e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.21071626087558e-07</v>
+        <v>1.210716260875565e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.179523709729654e-07</v>
+        <v>1.179523709729652e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.917831382451098e-08</v>
+        <v>8.917831382451304e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47449896094047e-07</v>
+        <v>1.474498960940471e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.14445852494981e-07</v>
+        <v>2.144458524949816e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.643621599381834e-07</v>
+        <v>2.643621599381836e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.612373747481769e-07</v>
+        <v>2.612373747481765e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.183585702326966e-07</v>
+        <v>3.183585702326962e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.643621526576784e-07</v>
+        <v>2.643621526576768e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.617069874884333e-07</v>
+        <v>2.617069874884336e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.612373541701716e-07</v>
+        <v>2.612373541701734e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.643621599381834e-07</v>
+        <v>2.643621599381836e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.612373541701716e-07</v>
+        <v>2.612373541701734e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.341261829901852e-07</v>
+        <v>2.341261829901865e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.612373541701716e-07</v>
+        <v>2.612373541701734e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.612930077641653e-07</v>
+        <v>9.612930077641645e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.185957163084507e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.534567430148296e-07</v>
+        <v>9.534567430148303e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.185957163084507e-06</v>
@@ -1166,22 +1166,22 @@
         <v>1.185957163084507e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.493788248246644e-07</v>
+        <v>9.493788248246632e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.565431502931298e-07</v>
+        <v>9.565431502931288e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.185957163084507e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.008988771526803e-07</v>
+        <v>9.008988771526812e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.503312476463119e-07</v>
+        <v>9.503312476463095e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.610340821585925e-07</v>
+        <v>9.610340821585901e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.476878106886043e-07</v>
+        <v>9.476878106886036e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.176928233850819e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.444964185917545e-07</v>
+        <v>9.444964185917542e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.176928233850819e-06</v>
@@ -1206,22 +1206,22 @@
         <v>1.176928233850819e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.428467233301134e-07</v>
+        <v>9.428467233301125e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.457597776250111e-07</v>
+        <v>9.45759777625009e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.176928233850819e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.231135809602032e-07</v>
+        <v>9.231135809602029e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.432238565800791e-07</v>
+        <v>9.432238565800785e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.444305665504083e-07</v>
+        <v>9.475842820453202e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.684115361692735e-07</v>
+        <v>2.684115361692702e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.377296150015392e-07</v>
+        <v>3.377296150015388e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.277963524738251e-07</v>
+        <v>2.277963524738293e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.752036481341727e-07</v>
+        <v>4.752036481341675e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.752036481341727e-07</v>
+        <v>4.752036481341675e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.996003791307138e-07</v>
+        <v>4.996003791307242e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.044317049764686e-07</v>
+        <v>4.044317049764738e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.752036481341727e-07</v>
+        <v>4.752036481341675e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.22041505242572e-06</v>
+        <v>1.220415052425719e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.448715532207506e-07</v>
+        <v>5.448715532207486e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.876440021599345e-07</v>
+        <v>5.876440021599351e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.893887053238827e-08</v>
+        <v>5.893887053238868e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.51658285826959e-08</v>
+        <v>5.516582858269598e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.893887053238828e-08</v>
+        <v>5.893887053238893e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.041194414595568e-08</v>
+        <v>6.041194414595592e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.041194414595568e-08</v>
+        <v>6.041194414595619e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.909743560655098e-08</v>
+        <v>5.909743560655121e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.893887053238828e-08</v>
+        <v>5.893887053238894e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.999356571623768e-08</v>
+        <v>5.99935657162377e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.893887053238828e-08</v>
+        <v>5.893887053238894e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.893887053238828e-08</v>
+        <v>5.893887053238893e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.893887053238828e-08</v>
+        <v>5.893887053238893e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.955987126236817e-08</v>
+        <v>1.008238354638956e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.854986415292767e-08</v>
+        <v>6.85498641529188e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.887111604943084e-08</v>
+        <v>6.88714451809248e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.889256437478576e-08</v>
+        <v>6.889256437478184e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.070121073508239e-08</v>
+        <v>7.070121073508047e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.009824005380571e-07</v>
+        <v>6.971843633652768e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09199555555624e-07</v>
+        <v>1.091995555556219e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.018785306477439e-07</v>
+        <v>7.061456644622121e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02520000196928e-07</v>
+        <v>1.025200001969132e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.939300626068478e-08</v>
+        <v>6.939300626067934e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.966067796935501e-08</v>
+        <v>6.966067796935321e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.085189186333129e-08</v>
+        <v>8.085189186332941e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.080157235464038e-08</v>
+        <v>8.080157235464091e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.085095861459168e-08</v>
+        <v>8.085095861459082e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.207601514682975e-08</v>
+        <v>8.207601514683053e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.207601514682975e-08</v>
+        <v>8.207601514683053e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.101045693749404e-08</v>
+        <v>8.101045693749119e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.085189186333129e-08</v>
+        <v>8.085189186332941e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.190658704718073e-08</v>
+        <v>8.190658704718272e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.085189186333129e-08</v>
+        <v>8.085189186332941e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.085189186333129e-08</v>
+        <v>8.085189186332941e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.085189186333129e-08</v>
+        <v>8.085189186332941e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.087042663100692e-07</v>
+        <v>1.087042663100691e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.50145726346583e-07</v>
+        <v>1.501457263465836e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.58593370601618e-07</v>
+        <v>1.585933706016204e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.399318850551358e-07</v>
+        <v>1.399318850551353e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.111704003324708e-07</v>
+        <v>1.1117040033247e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.501837699017632e-07</v>
+        <v>1.501837699017647e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500252048280624e-07</v>
+        <v>1.500252048280627e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5107990001145e-07</v>
+        <v>1.510799000114511e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.500333254429177e-07</v>
+        <v>1.500333254429225e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.079367086740641e-07</v>
+        <v>1.079367086740627e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.931883801877544e-07</v>
+        <v>1.931883801877562e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.631479067484281e-07</v>
+        <v>2.631479067484249e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.237948198342679e-07</v>
+        <v>3.237948198342674e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.238451650457041e-07</v>
+        <v>3.238451650457061e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.949431684101656e-07</v>
+        <v>3.949431684101668e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.248998275058196e-07</v>
+        <v>3.24899827505821e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.240037044171211e-07</v>
+        <v>3.240037044171208e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.238451393429578e-07</v>
+        <v>3.238451393429469e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.248998345268083e-07</v>
+        <v>3.248998345268082e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.238451393429578e-07</v>
+        <v>3.238451393429469e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.886769352117322e-07</v>
+        <v>2.886769352117147e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.238451393429578e-07</v>
+        <v>3.238451393429511e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1550,34 +1550,34 @@
         <v>5.711656339046955e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206842989184608e-06</v>
+        <v>1.206842989184607e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.592185194276437e-08</v>
+        <v>3.592185194276417e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.964684810564918e-07</v>
+        <v>9.964684810564903e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.964684810564918e-07</v>
+        <v>9.964684810564903e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.700466237019579e-07</v>
+        <v>5.700466237019583e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.281251597253433e-08</v>
+        <v>3.281251597253452e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.964684810564918e-07</v>
+        <v>9.964684810564903e-07</v>
       </c>
       <c r="J8" t="n">
         <v>1.371500598471986e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.136779640394424e-07</v>
+        <v>6.136779640394429e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674226905299182e-07</v>
+        <v>6.674226905299175e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.651551084625733e-07</v>
+        <v>5.651551084625736e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.191800005800698e-06</v>
+        <v>1.191800005800699e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.784689956308719e-08</v>
+        <v>3.78468995630876e-08</v>
       </c>
       <c r="E9" t="n">
         <v>9.865853149444128e-07</v>
@@ -1602,22 +1602,22 @@
         <v>9.865853149444128e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.670580168773047e-07</v>
+        <v>5.670580168773052e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.658706154904149e-08</v>
+        <v>3.658706154904132e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.865853149444128e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3649745254694e-06</v>
+        <v>1.364974525469399e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.107600117257973e-07</v>
+        <v>6.107600117257975e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.632936771544471e-07</v>
+        <v>6.632936771544477e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.930205179167091e-07</v>
+        <v>1.930205179167467e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.567427364819261e-07</v>
+        <v>2.567427364819262e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.717677948665187e-07</v>
+        <v>1.717677948667371e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.933874534988155e-07</v>
+        <v>2.933874534988121e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.933874534988155e-07</v>
+        <v>2.933874534988121e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.795768030329556e-07</v>
+        <v>3.795768030329382e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.890933125391867e-07</v>
+        <v>2.890933125390752e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.933874534988155e-07</v>
+        <v>2.933874534988121e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.809511653009586e-07</v>
+        <v>9.809511653008765e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.515092495211207e-07</v>
+        <v>3.515092495209962e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.525009403702074e-07</v>
+        <v>4.525009403705531e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.504719649951489e-08</v>
+        <v>5.504719649941047e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.180555251339336e-08</v>
+        <v>5.180555251339389e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.504719649951489e-08</v>
+        <v>5.504719649941046e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.590084141095919e-08</v>
+        <v>5.590084141095882e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.590084141095879e-08</v>
+        <v>5.590084141095882e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.520293644019868e-08</v>
+        <v>5.520293644031196e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.504719649951489e-08</v>
+        <v>5.504719649941046e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.608347072618089e-08</v>
+        <v>5.608347072618096e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.504719649951501e-08</v>
+        <v>5.504719649941047e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.504719649951489e-08</v>
+        <v>5.504719649941046e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.504719649951489e-08</v>
+        <v>5.504719649941046e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.105147414142586e-08</v>
+        <v>9.10514741416204e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.253897927793629e-08</v>
+        <v>6.253897927794259e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.222046342375494e-08</v>
+        <v>9.222046342392537e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.286347269132716e-08</v>
+        <v>6.286347269133237e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.442764116671845e-08</v>
+        <v>6.442764116672289e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.35371228627814e-08</v>
+        <v>9.120721408252172e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.857563758953358e-08</v>
+        <v>9.857563758921073e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.441765714879587e-08</v>
+        <v>6.441765714880621e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.461921849429592e-08</v>
+        <v>6.461921849424194e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.294990548129203e-08</v>
+        <v>6.294990548143357e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.35240219342552e-08</v>
+        <v>6.352402193428534e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.407663557112345e-08</v>
+        <v>7.407663557115943e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.402801875925641e-08</v>
+        <v>7.402801875925795e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.407575110477372e-08</v>
+        <v>7.407575110472261e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.513286305213433e-08</v>
+        <v>7.513286305213256e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.513286305213433e-08</v>
+        <v>7.513286305213256e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.423237551211573e-08</v>
+        <v>7.423237551206089e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407663557112345e-08</v>
+        <v>7.407663557115943e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.511290979792876e-08</v>
+        <v>7.511290979792982e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.407663557112345e-08</v>
+        <v>7.407663557115943e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.407663557112345e-08</v>
+        <v>7.407663557115943e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.407663557112345e-08</v>
+        <v>7.407663557115943e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.886143361518614e-08</v>
+        <v>9.886143361549724e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.347419433221484e-07</v>
+        <v>1.347419433204388e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.422081539269226e-07</v>
+        <v>1.422081539269602e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.260050858448016e-07</v>
+        <v>1.260050858448053e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.010481820058192e-07</v>
+        <v>1.010481820058196e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349193447889391e-07</v>
+        <v>1.349193447889149e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.347636048483289e-07</v>
+        <v>1.347636048485596e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.357998790747834e-07</v>
+        <v>1.357998790747835e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.347706605498364e-07</v>
+        <v>1.347706605499621e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.819453236116424e-08</v>
+        <v>9.819453236127965e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.722664246971749e-07</v>
+        <v>1.722664246974548e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.243163960203735e-07</v>
+        <v>2.243163960205558e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.745895115943392e-07</v>
+        <v>2.745895115943333e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.746381505062625e-07</v>
+        <v>2.746381505062766e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.337446266715752e-07</v>
+        <v>3.337446266715934e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.756743961375194e-07</v>
+        <v>2.756743961375125e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74793868347102e-07</v>
+        <v>2.747938683471349e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.746381284060074e-07</v>
+        <v>2.746381284062335e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.756744026330095e-07</v>
+        <v>2.75674402633005e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.746381284060074e-07</v>
+        <v>2.746381284062335e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.454815283283367e-07</v>
+        <v>2.454815283284676e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.746381284060074e-07</v>
+        <v>2.746381284062335e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.709927100153604e-07</v>
+        <v>5.709927100153066e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206673282712639e-06</v>
+        <v>1.20667328271264e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.34130973109038e-08</v>
+        <v>3.341309731079307e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.967854867729934e-07</v>
+        <v>9.967854867729927e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.967854867729934e-07</v>
+        <v>9.967854867729927e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.695713428357308e-07</v>
+        <v>5.695713428358408e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.125015593152823e-08</v>
+        <v>3.125015593165609e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.967854867729934e-07</v>
+        <v>9.967854867729927e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.370827874554801e-06</v>
+        <v>1.370827874554988e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.135498401004869e-07</v>
+        <v>6.135498401006255e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.671209314618197e-07</v>
+        <v>6.671209314619245e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.641277738043364e-07</v>
+        <v>5.641277738043558e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.190747122219755e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.473720538167546e-08</v>
+        <v>3.473720538157054e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.846912122078866e-07</v>
+        <v>9.846912122078883e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.846912122078866e-07</v>
+        <v>9.846912122078883e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.652893645244557e-07</v>
+        <v>5.652893645244476e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.38609600847955e-08</v>
+        <v>3.386096008483532e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.846912122078866e-07</v>
+        <v>9.846912122078883e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361951388985529e-06</v>
+        <v>1.361951388985484e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.08305488379338e-07</v>
+        <v>6.083054883794049e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.617086331284063e-07</v>
+        <v>6.617086331283648e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.430818418219328e-07</v>
+        <v>1.430818418219322e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.021409557848446e-07</v>
+        <v>2.021409557848441e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394058599055401e-07</v>
+        <v>1.394058599055381e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.86045253241327e-07</v>
+        <v>1.860452532413253e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.86045253241327e-07</v>
+        <v>1.860452532413253e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.180869472937945e-07</v>
+        <v>3.180869472938011e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.360056276851493e-07</v>
+        <v>2.360056276851484e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.86045253241327e-07</v>
+        <v>1.860452532413253e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.139398838645546e-07</v>
+        <v>9.139398838645532e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.271744490846706e-07</v>
+        <v>2.271744490846728e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.919824820513354e-07</v>
+        <v>2.919824820513345e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.1539869067582e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.942000662450279e-08</v>
+        <v>4.942000662450269e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.153986906758194e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.167317095285262e-08</v>
+        <v>5.167317095285261e-08</v>
       </c>
       <c r="F3" t="n">
         <v>5.167317095285262e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.169497298726924e-08</v>
+        <v>5.16949729872688e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.153986906758194e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.257115760343071e-08</v>
+        <v>5.257115760343028e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.153986906758194e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.153986906758194e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.153986906758244e-08</v>
+        <v>5.153986906758194e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.823882886917266e-08</v>
+        <v>5.823882886917265e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.763740479516161e-08</v>
+        <v>5.763740479516209e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.765354994578847e-08</v>
+        <v>5.765329530731227e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.784280952083273e-08</v>
+        <v>5.784280952083274e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.920877332639843e-08</v>
+        <v>5.920877332639862e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.398354639670035e-08</v>
+        <v>8.398354639670263e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.88280891544431e-08</v>
+        <v>8.882808915444292e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.485973101286176e-08</v>
+        <v>8.485973101286379e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.41902389539941e-08</v>
+        <v>8.419023895399402e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.764273358703886e-08</v>
+        <v>5.764273358703846e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.841024113549513e-08</v>
+        <v>5.841024113549502e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.858610737589912e-08</v>
+        <v>6.858610737589773e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.854091973238647e-08</v>
+        <v>6.854091973238528e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.858508035110564e-08</v>
+        <v>6.858508035110437e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.942499982982531e-08</v>
+        <v>6.942499982982412e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.942499982982531e-08</v>
+        <v>6.942499982982412e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.874121129558588e-08</v>
+        <v>6.874121129558466e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.858610737589912e-08</v>
+        <v>6.858610737589773e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.961739591174737e-08</v>
+        <v>6.961739591174622e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.858610737589912e-08</v>
+        <v>6.858610737589773e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.858610737589912e-08</v>
+        <v>6.858610737589773e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.858610737589912e-08</v>
+        <v>6.858610737589773e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.114754977240119e-08</v>
+        <v>9.11475497724e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.227538233178996e-07</v>
+        <v>1.227538233194209e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.295753841224737e-07</v>
+        <v>1.295753841224727e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.15144243324342e-07</v>
+        <v>1.151442433243396e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.307357826966833e-08</v>
+        <v>9.307357826966711e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.231307292417585e-07</v>
+        <v>1.231307292417553e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.229756253223467e-07</v>
+        <v>1.229756253223444e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2400691385792e-07</v>
+        <v>1.240069138579188e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.22981880375323e-07</v>
+        <v>1.229818803753225e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.055632693461144e-08</v>
+        <v>9.055632693461026e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.562227115860496e-07</v>
+        <v>1.56222711586047e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.01777775557359e-07</v>
+        <v>2.017777755573644e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.461812024815178e-07</v>
+        <v>2.461812024815246e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.462264092339693e-07</v>
+        <v>2.462264092339761e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.985504458215143e-07</v>
+        <v>2.985504458215232e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.472576715715523e-07</v>
+        <v>2.472576715715594e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.463814940447171e-07</v>
+        <v>2.463814940447241e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.462263901250301e-07</v>
+        <v>2.462263901250375e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.472576786608788e-07</v>
+        <v>2.472576786608855e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.462263901250301e-07</v>
+        <v>2.462263901250375e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.902576453820702e-07</v>
+        <v>2.194278356537009e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.462263901250301e-07</v>
+        <v>2.462263901250375e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.702909729747518e-07</v>
+        <v>5.702909729747515e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.206067817808554e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.026118776718043e-08</v>
+        <v>3.026118776717987e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.956849416095831e-07</v>
+        <v>9.956849416095827e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.956849416095833e-07</v>
+        <v>9.956849416095827e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.680480485318486e-07</v>
+        <v>5.68048048531849e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.845538807154054e-08</v>
+        <v>2.845538807153997e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.956849416095833e-07</v>
+        <v>9.956849416095827e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.366744791912019e-06</v>
+        <v>1.366744791912017e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.120014577396551e-07</v>
+        <v>6.120014577396682e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674930865384456e-07</v>
+        <v>6.674930865384454e-07</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.627637060433088e-07</v>
+        <v>5.627637060433089e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.189412395480074e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.118943640308869e-08</v>
+        <v>3.118943640308798e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.821216543456321e-07</v>
+        <v>9.821216543456315e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.821216543456321e-07</v>
+        <v>9.821216543456315e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.629589539004024e-07</v>
+        <v>5.629589539004033e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.045764308194098e-08</v>
+        <v>3.045764308194032e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.821216543456321e-07</v>
+        <v>9.821216543456317e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.357045268181963e-06</v>
+        <v>1.357045268181961e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.050483252354658e-07</v>
+        <v>6.050483252354791e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.601261682982886e-07</v>
+        <v>6.601261682982879e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.152042427133e-07</v>
+        <v>2.152042427132999e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.347979805044367e-07</v>
+        <v>2.347979805044364e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.967110820847223e-07</v>
+        <v>1.967110820847214e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>3.789229292124458e-07</v>
+        <v>3.789229292124395e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.789229292124458e-07</v>
+        <v>3.789229292124395e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.285558527460839e-07</v>
+        <v>4.285558527460869e-07</v>
       </c>
       <c r="H2" t="n">
         <v>3.533757532110297e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.789229292124458e-07</v>
+        <v>3.789229292124395e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.067811903731846e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.347613317958935e-07</v>
+        <v>4.347613317958937e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.85241668842191e-07</v>
+        <v>3.852416688421908e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.467719030070811e-08</v>
+        <v>5.467719030070814e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.96901945142766e-08</v>
+        <v>5.969019451427657e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.969019451427661e-08</v>
+        <v>5.969019451427657e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.905798412985635e-08</v>
+        <v>5.905798412985643e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.994365318265715e-08</v>
+        <v>5.994365318265718e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.890150842588178e-08</v>
+        <v>5.890150842588185e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.972189792965182e-08</v>
+        <v>6.972189792965175e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.857464483886126e-08</v>
+        <v>6.857464483886109e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.911172295120852e-08</v>
+        <v>6.911138403857103e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.882800142427897e-08</v>
+        <v>6.882800142427877e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.079342249230935e-08</v>
+        <v>7.079342249230933e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.987837363362632e-08</v>
+        <v>6.987837363362635e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.099673539985004e-07</v>
+        <v>1.099673539985005e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.076404268642707e-08</v>
+        <v>1.019962602319145e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.028532261726537e-07</v>
+        <v>7.133289734304349e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.9581060852982e-08</v>
+        <v>6.958106085298196e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.977623178930495e-08</v>
+        <v>6.977623178930493e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2618,25 +2618,25 @@
         <v>8.034334157769774e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.028993520033859e-08</v>
+        <v>8.028993520033858e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.03425253962367e-08</v>
+        <v>8.034252539623671e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.137817806364334e-08</v>
+        <v>8.137817806364325e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.137817806364334e-08</v>
+        <v>8.137817806364325e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.049981728167232e-08</v>
+        <v>8.049981728167229e-08</v>
       </c>
       <c r="H5" t="n">
         <v>8.034334157769774e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.1385486334473e-08</v>
+        <v>8.138548633447301e-08</v>
       </c>
       <c r="J5" t="n">
         <v>8.034334157769774e-08</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.084190599305006e-07</v>
+        <v>1.084190599305007e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497259654686804e-07</v>
+        <v>1.497259654706131e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.583535720438186e-07</v>
+        <v>1.583535720438187e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.395102884085555e-07</v>
+        <v>1.395102884085556e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.107683340263617e-07</v>
+        <v>1.107683340263618e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.49934083442793e-07</v>
+        <v>1.499340834427931e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.497776077393383e-07</v>
+        <v>1.497776077393386e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.508197524955938e-07</v>
+        <v>1.508197524955939e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.497857357383425e-07</v>
+        <v>1.497857357383426e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.076508036831227e-07</v>
+        <v>1.076508036831228e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.929800691415808e-07</v>
+        <v>1.92980069141581e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.610199290271932e-07</v>
+        <v>2.610199290271927e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.211704969303305e-07</v>
+        <v>3.211704969303303e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.212239291317069e-07</v>
+        <v>3.212239291317065e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.917401733704958e-07</v>
+        <v>3.917401733704953e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.222660418024177e-07</v>
+        <v>3.222660418024173e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.213803790116643e-07</v>
+        <v>3.21380379011664e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.212239033076895e-07</v>
+        <v>3.212239033076897e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.222660480644649e-07</v>
+        <v>3.222660480644648e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.212239033076895e-07</v>
+        <v>3.212239033076896e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.454163466241175e-07</v>
+        <v>2.863414950317952e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.212239033076895e-07</v>
+        <v>3.212239033076896e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.726079164659563e-07</v>
+        <v>5.726079164659571e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.208781072950082e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.632223986867768e-08</v>
+        <v>3.632223986867772e-08</v>
       </c>
       <c r="E8" t="n">
         <v>9.983679767553909e-07</v>
@@ -2750,10 +2750,10 @@
         <v>9.983679767553909e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.714468849406338e-07</v>
+        <v>5.714468849406343e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.353605425327827e-08</v>
+        <v>3.353605425327832e-08</v>
       </c>
       <c r="I8" t="n">
         <v>9.983679767553909e-07</v>
@@ -2762,10 +2762,10 @@
         <v>1.375104276976851e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.155914714759269e-07</v>
+        <v>6.155914714759272e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.712625840405658e-07</v>
+        <v>6.71262584040566e-07</v>
       </c>
     </row>
     <row r="9">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.658888635895559e-07</v>
+        <v>5.658888635895562e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.192374943306634e-06</v>
@@ -2790,22 +2790,22 @@
         <v>9.871861892539558e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.675186890715065e-07</v>
+        <v>5.675186890715066e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.66998260863451e-08</v>
+        <v>3.669982608634514e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.871861892539558e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.366590708601563e-06</v>
+        <v>1.366590708601562e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.11183701398709e-07</v>
+        <v>6.111837013987088e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.647388155952291e-07</v>
+        <v>6.647388155952293e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.212381940206896e-07</v>
+        <v>1.212381940206895e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.260614206980184e-07</v>
+        <v>1.260614206980181e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.447612693967903e-07</v>
+        <v>1.447612693967901e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.918620519011315e-07</v>
+        <v>1.91862051901109e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.918620519011315e-07</v>
+        <v>1.91862051901109e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.239557343130894e-07</v>
+        <v>2.239557343130899e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93911807510704e-07</v>
+        <v>1.939118075106987e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.918620519011315e-07</v>
+        <v>1.91862051901109e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.708898504316583e-07</v>
+        <v>5.708898504316628e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.749240912159106e-07</v>
+        <v>1.749240912159089e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.042822863572645e-07</v>
+        <v>2.042822863572636e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.153134762405945e-08</v>
+        <v>5.153134762406029e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.634633210089123e-08</v>
+        <v>5.6346332100891e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.634633210089123e-08</v>
+        <v>5.6346332100891e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.603140014959353e-08</v>
+        <v>5.603140014959396e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.69137975000073e-08</v>
+        <v>5.691379750000715e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.587552229371649e-08</v>
+        <v>5.587552229371702e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.508766856880554e-08</v>
+        <v>6.508766856880561e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.405602588764053e-08</v>
+        <v>6.40560258876401e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.476949573581952e-08</v>
+        <v>9.493330869811857e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.43581736965702e-08</v>
+        <v>6.43581736965718e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.61092437201507e-08</v>
+        <v>6.610924372014991e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.335145385016319e-08</v>
+        <v>6.524354642468225e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.021521070218849e-07</v>
+        <v>1.021521070218844e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.423385120057699e-08</v>
+        <v>9.423385120057319e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.641426483429231e-08</v>
+        <v>9.494778423736623e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.477994034404902e-08</v>
+        <v>6.477994034404842e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.513791563818303e-08</v>
+        <v>6.51379156381825e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.453418125473954e-08</v>
+        <v>7.45341812547392e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.448391929422198e-08</v>
+        <v>7.448391929422184e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.453356423376252e-08</v>
+        <v>7.4533564233762e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.548614878535402e-08</v>
+        <v>7.548614878535311e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.548614878535402e-08</v>
+        <v>7.548614878535311e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.469005911061659e-08</v>
+        <v>7.469005911061615e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.453418125473954e-08</v>
+        <v>7.45341812547392e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.557245646103045e-08</v>
+        <v>7.557245646102963e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.453418125473954e-08</v>
+        <v>7.45341812547392e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.453418125473954e-08</v>
+        <v>7.45341812547392e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.453418125473954e-08</v>
+        <v>7.45341812547392e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.995041764097188e-08</v>
+        <v>9.995041764097278e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.366130199922847e-07</v>
+        <v>1.366130199905529e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.443663376745014e-07</v>
+        <v>1.443663376745029e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2764854399629e-07</v>
+        <v>1.27648543996291e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.021036889046734e-07</v>
+        <v>1.021036889046738e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.368940375699006e-07</v>
+        <v>1.368940375699021e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.367381597146809e-07</v>
+        <v>1.367381597146821e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.377764349203145e-07</v>
+        <v>1.377764349203153e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.367453894347393e-07</v>
+        <v>1.367453894347406e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.926706645540779e-08</v>
+        <v>9.926706645540876e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.751660323366892e-07</v>
+        <v>1.751660323366914e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.222151731883001e-07</v>
+        <v>2.22215173188299e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.719898246378541e-07</v>
+        <v>2.71989824637852e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.720401076283873e-07</v>
+        <v>2.720401076283853e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.305752681740153e-07</v>
+        <v>3.305752681740126e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.730783567984771e-07</v>
+        <v>2.730783567984748e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.721959644542479e-07</v>
+        <v>2.721959644542465e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.720400865983716e-07</v>
+        <v>2.720400865983695e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.730783618046628e-07</v>
+        <v>2.730783618046599e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.720400865983716e-07</v>
+        <v>2.720400865983695e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.093016214489792e-07</v>
+        <v>2.431713449361798e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.720400865983716e-07</v>
+        <v>2.720400865983695e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.733623917352129e-07</v>
+        <v>5.733623917352119e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.209911892359383e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.470238000527153e-08</v>
+        <v>3.47023800052713e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.999773368974292e-07</v>
+        <v>9.9997733689743e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.999773368974294e-07</v>
+        <v>9.9997733689743e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.737892289414356e-07</v>
+        <v>5.737892289414341e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.39294244516123e-08</v>
+        <v>3.392942445161219e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.999773368974294e-07</v>
+        <v>9.9997733689743e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.382377541671312e-06</v>
+        <v>1.382377541671317e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.182696682964025e-07</v>
+        <v>6.182696682963775e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.729540559041427e-07</v>
+        <v>6.729540559041425e-07</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.654840150611579e-07</v>
+        <v>5.654840150611576e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.192150306689498e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.56307920838162e-08</v>
+        <v>3.563079208381596e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.8642285157613e-07</v>
+        <v>9.864228515761298e-07</v>
       </c>
       <c r="F9" t="n">
         <v>9.864228515761298e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.673183720756933e-07</v>
+        <v>5.673183720756916e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5318793303359e-08</v>
+        <v>3.531879330335886e-08</v>
       </c>
       <c r="I9" t="n">
         <v>9.864228515761298e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.367839843002902e-06</v>
+        <v>1.367839843002905e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.104801234575743e-07</v>
+        <v>6.1048012345755e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.644293760358331e-07</v>
+        <v>6.644293760358327e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.063842549447457e-07</v>
+        <v>1.063842549447389e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.183990167086214e-07</v>
+        <v>1.183990167086199e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.285320992297967e-07</v>
+        <v>1.285320992297899e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.458122036519393e-07</v>
+        <v>1.458122036519497e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.458122036519393e-07</v>
+        <v>1.458122036519497e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.433825436144004e-07</v>
+        <v>1.433825436144048e-07</v>
       </c>
       <c r="H2" t="n">
         <v>1.660258916891127e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.458122036519393e-07</v>
+        <v>1.458122036519497e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56917319753728e-07</v>
+        <v>2.569173197537269e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.047173153462808e-07</v>
+        <v>1.047173153462742e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.336452489062966e-07</v>
+        <v>1.336452489062934e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.685382920138267e-08</v>
+        <v>4.685382920138271e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.079547830252889e-08</v>
+        <v>5.079547830252883e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.079547830252888e-08</v>
+        <v>5.079547830252883e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.10548833935343e-08</v>
+        <v>5.10548833935304e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.194444992420984e-08</v>
+        <v>5.194444992421467e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.089736169550346e-08</v>
+        <v>5.089736169549811e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.326769433113721e-08</v>
+        <v>8.326769433113294e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.732741985542514e-08</v>
+        <v>5.732741985542637e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.804660080341185e-08</v>
+        <v>5.804660080340525e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.78004244527807e-08</v>
+        <v>5.780042445277542e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.916537128856083e-08</v>
+        <v>5.916537128855943e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.342521602916267e-08</v>
+        <v>8.342521602916452e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.950377255481025e-08</v>
+        <v>5.827434575887857e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.922824701248585e-08</v>
+        <v>8.431478255984549e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.417046208782977e-08</v>
+        <v>5.915106236207134e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.775041566355474e-08</v>
+        <v>5.775041566355642e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.823353533258985e-08</v>
+        <v>5.823353533258584e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.690989020548387e-08</v>
+        <v>6.690989020548244e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.686688276882272e-08</v>
+        <v>6.686688276882188e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.690925439390052e-08</v>
+        <v>6.690925439389646e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.767691974059077e-08</v>
+        <v>6.767691974059368e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.767691974059077e-08</v>
+        <v>6.767691974059368e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.706741190351546e-08</v>
+        <v>6.706741190350896e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.690989020548387e-08</v>
+        <v>6.690989020548244e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.795697843418819e-08</v>
+        <v>6.795697843420822e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.690989020548387e-08</v>
+        <v>6.690989020548244e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.690989020548387e-08</v>
+        <v>6.690989020548244e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.690989020548387e-08</v>
+        <v>6.690989020548244e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.919201300142936e-08</v>
+        <v>8.919201300142872e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.201658665646622e-07</v>
+        <v>1.201658665659909e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.269557996416756e-07</v>
+        <v>1.269557996416743e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.127295623219886e-07</v>
+        <v>1.127295623219893e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.106387862608444e-08</v>
+        <v>9.106387862607454e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.206276089019646e-07</v>
+        <v>1.206276089019663e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.204700872043332e-07</v>
+        <v>1.204700872043319e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215171754326547e-07</v>
+        <v>1.215171754326559e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.204762341515392e-07</v>
+        <v>1.204762341515339e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.861100672221471e-08</v>
+        <v>8.861100672221165e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.531426510564062e-07</v>
+        <v>1.531426510564072e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.97842925008606e-07</v>
+        <v>1.978429250086042e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.414617555158052e-07</v>
+        <v>2.414617555158043e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.415047793673527e-07</v>
+        <v>2.415047793673568e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.929366945686387e-07</v>
+        <v>2.929366945686355e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.425518458548069e-07</v>
+        <v>2.425518458548013e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.41662284650497e-07</v>
+        <v>2.416622846504925e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.415047629524662e-07</v>
+        <v>2.415047629524601e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.425518511811808e-07</v>
+        <v>2.425518511811844e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.415047629524662e-07</v>
+        <v>2.415047629524601e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.15180563752603e-07</v>
+        <v>2.1620692947856e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.415047629524662e-07</v>
+        <v>2.415047629524601e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.714605312138737e-07</v>
+        <v>5.714605312138724e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.207822696639414e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.046675125959653e-08</v>
+        <v>3.046675125959589e-08</v>
       </c>
       <c r="E8" t="n">
         <v>9.966126915387463e-07</v>
@@ -3542,10 +3542,10 @@
         <v>9.966126915387463e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.720011509307662e-07</v>
+        <v>5.720011509307645e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.990478520057681e-08</v>
+        <v>2.990478520057553e-08</v>
       </c>
       <c r="I8" t="n">
         <v>9.966126915387463e-07</v>
@@ -3554,10 +3554,10 @@
         <v>1.382353241751081e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.147606327686486e-07</v>
+        <v>6.147606327686469e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.707206256930867e-07</v>
+        <v>6.707206256930864e-07</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.634265118705511e-07</v>
+        <v>5.634265118705507e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.190008250608653e-06</v>
+        <v>1.190008250608654e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.125401448268455e-08</v>
+        <v>3.125401448268678e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.824899466384876e-07</v>
+        <v>9.824899466384874e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.824899466384876e-07</v>
+        <v>9.824899466384874e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.64476853295174e-07</v>
+        <v>5.644768532951726e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.10274550837469e-08</v>
+        <v>3.102745508374571e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.824899466384876e-07</v>
+        <v>9.824899466384874e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.363635611409166e-06</v>
+        <v>1.363635611409167e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.060625119644019e-07</v>
+        <v>6.060625119644004e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.613865369439543e-07</v>
+        <v>6.613865369439522e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.766439132527079e-07</v>
+        <v>1.766439132527104e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41367846521528e-07</v>
+        <v>1.413678465215281e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.713561481769538e-07</v>
+        <v>1.713561481769581e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.833018930098664e-07</v>
+        <v>2.833018930098737e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.833018930098664e-07</v>
+        <v>2.833018930098737e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.788642494698241e-07</v>
+        <v>3.788642494698229e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.319996164058542e-07</v>
+        <v>3.319996164058604e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.833018930098664e-07</v>
+        <v>2.833018930098737e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.075410452094657e-06</v>
+        <v>1.075410452094659e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.457565485923312e-07</v>
+        <v>3.457565485923295e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.170563873745524e-07</v>
+        <v>3.170563873745565e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.401011315913714e-08</v>
+        <v>5.401011315913781e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.880685631910296e-08</v>
+        <v>5.880685631910287e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.880685631910296e-08</v>
+        <v>5.880685631910288e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.834732931642356e-08</v>
+        <v>5.834732931642254e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.922378259203538e-08</v>
+        <v>5.922378259203625e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.81925572164962e-08</v>
+        <v>5.819255721649891e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.867648054411139e-08</v>
+        <v>6.867648054411592e-08</v>
       </c>
       <c r="C4" t="n">
         <v>6.746471193613842e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.812483156189453e-08</v>
+        <v>6.812483156189691e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.770204611319032e-08</v>
+        <v>6.770204611319154e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.970273529214806e-08</v>
+        <v>6.970273529214852e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.955951570106221e-08</v>
+        <v>6.883125264404026e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084199255763917e-07</v>
+        <v>1.084199255763948e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.004359689766764e-07</v>
+        <v>6.970770591965319e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.012710892331712e-07</v>
+        <v>7.0275163422341e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.844764490078441e-08</v>
+        <v>6.844764490078654e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.87268557803065e-08</v>
+        <v>6.872685578030791e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.901987278427724e-08</v>
+        <v>7.901987278427973e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.89651931241299e-08</v>
+        <v>7.896519312413112e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.901904785353336e-08</v>
+        <v>7.90190478535386e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.000630718976051e-08</v>
+        <v>8.000630718976026e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.000630718976051e-08</v>
+        <v>8.000630718976026e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.917464488420155e-08</v>
+        <v>7.917464488420591e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.901987278427724e-08</v>
+        <v>7.901987278427973e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.005109815981661e-08</v>
+        <v>8.005109815981638e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.901987278427724e-08</v>
+        <v>7.901987278427973e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.901987278427724e-08</v>
+        <v>7.901987278427973e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.901987278427724e-08</v>
+        <v>7.901987278427973e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.06642179451642e-07</v>
+        <v>1.066421794516439e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.470600016596963e-07</v>
+        <v>1.470600016577727e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.555482139878796e-07</v>
+        <v>1.555482139878804e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.370714356528442e-07</v>
+        <v>1.37071435652843e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.089311770437707e-07</v>
+        <v>1.0893117704377e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.473036568718507e-07</v>
+        <v>1.473036568718545e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.471488847724635e-07</v>
+        <v>1.471488847724625e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.481801101474655e-07</v>
+        <v>1.48180110147464e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.471568453614892e-07</v>
+        <v>1.47156845361491e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.058897466156903e-07</v>
+        <v>1.058897466156914e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.894615254674261e-07</v>
+        <v>1.894615254674287e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.582722815895054e-07</v>
+        <v>2.582722815894848e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.177823389852126e-07</v>
+        <v>3.177823389851836e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.178370436902227e-07</v>
+        <v>3.178370436901968e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.876047021830422e-07</v>
+        <v>3.876047021830071e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.188682375697885e-07</v>
+        <v>3.188682375697604e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.179917907452842e-07</v>
+        <v>3.179917907452577e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.178370186453594e-07</v>
+        <v>3.178370186453317e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188682440208967e-07</v>
+        <v>3.188682440208687e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.178370186453594e-07</v>
+        <v>3.178370186453317e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.833249866001937e-07</v>
+        <v>2.833249866001696e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.178370186453594e-07</v>
+        <v>3.178370186453317e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.731203115254531e-07</v>
+        <v>5.731203115254553e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.207655281151202e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.588885666679891e-08</v>
+        <v>3.588885666679946e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.995396310036018e-07</v>
+        <v>9.995396310036016e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.995396310036018e-07</v>
+        <v>9.995396310036016e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.716820257315582e-07</v>
+        <v>5.716820257315586e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.295371791897211e-08</v>
+        <v>3.295371791897287e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.995396310036018e-07</v>
+        <v>9.995396310036016e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.37416313258959e-06</v>
+        <v>1.374163132589592e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.164160213517005e-07</v>
+        <v>6.164160213516872e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.720383972943345e-07</v>
+        <v>6.720383972943355e-07</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.658984657521877e-07</v>
+        <v>5.658984657521902e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.190058398340923e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.706864139015713e-08</v>
+        <v>3.706864139015897e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.870811669827976e-07</v>
+        <v>9.87081166982797e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.870811669827976e-07</v>
+        <v>9.87081166982797e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.671107653749767e-07</v>
+        <v>5.671107653749761e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.587842638614206e-08</v>
+        <v>3.587842638614432e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.870811669827976e-07</v>
+        <v>9.87081166982797e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.365764632101802e-06</v>
+        <v>1.365764632101806e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.108176296535233e-07</v>
+        <v>6.108176296535097e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.647188664909138e-07</v>
+        <v>6.647188664909147e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.192091674977187e-07</v>
+        <v>1.192091674977141e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.247027282164053e-07</v>
+        <v>1.247027282163956e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.387546650531726e-07</v>
+        <v>1.387546650531634e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.615920838866305e-07</v>
+        <v>1.615920838866202e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.615920838866305e-07</v>
+        <v>1.615920838866202e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.557269304226085e-07</v>
+        <v>1.557269304225903e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.842228356564022e-07</v>
+        <v>1.842228356563971e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.615920838866305e-07</v>
+        <v>1.615920838866202e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.843754977457667e-07</v>
+        <v>1.843754977457573e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.208092184787639e-07</v>
+        <v>1.208092184787571e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.437148963108235e-07</v>
+        <v>1.437148963108124e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.020022798752001e-08</v>
+        <v>5.020022798751849e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.438009855124385e-08</v>
+        <v>5.43800985512418e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.438009855124387e-08</v>
+        <v>5.43800985512418e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.44587287238554e-08</v>
+        <v>5.445872872385419e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.534157225054709e-08</v>
+        <v>5.534157225054588e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.430262303189605e-08</v>
+        <v>5.430262303189468e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.240607821584041e-08</v>
+        <v>8.930709787768919e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.151841977814711e-08</v>
+        <v>6.151841977814088e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.213850192852807e-08</v>
+        <v>6.213881420755608e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.182455998806448e-08</v>
+        <v>6.182455998805922e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.339805742715605e-08</v>
+        <v>6.339805742715181e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.256218390780325e-08</v>
+        <v>6.256218390779653e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.822952213242882e-08</v>
+        <v>9.82295221324243e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.03460470963529e-08</v>
+        <v>9.034604709634041e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.088105572810441e-08</v>
+        <v>6.349894146124716e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.190039909917767e-08</v>
+        <v>6.19003990991755e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.245560620281968e-08</v>
+        <v>6.245560620281571e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.16480292103107e-08</v>
+        <v>7.164802921030026e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.160177829018393e-08</v>
+        <v>7.160177829017387e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.164739164226667e-08</v>
+        <v>7.164739164225624e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.247703354359825e-08</v>
+        <v>7.247703354358823e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.247703354359825e-08</v>
+        <v>7.247703354358823e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.180413490227004e-08</v>
+        <v>7.180413490225972e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.16480292103107e-08</v>
+        <v>7.164802921030026e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.268697842896174e-08</v>
+        <v>7.268697842895163e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.16480292103107e-08</v>
+        <v>7.164802921030026e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.16480292103107e-08</v>
+        <v>7.164802921030026e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.16480292103107e-08</v>
+        <v>7.164802921030026e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.579391058065838e-08</v>
+        <v>9.579391058065327e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300917762300091e-07</v>
+        <v>1.300917762300014e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.374930922295651e-07</v>
+        <v>1.374930922295569e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.217518933302648e-07</v>
+        <v>1.21751893330259e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.780278609653183e-08</v>
+        <v>9.780278609652614e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.304876041014462e-07</v>
+        <v>1.304876041014371e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.303314984102302e-07</v>
+        <v>1.303314984102224e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31370447628137e-07</v>
+        <v>1.313704476281305e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.303382859202289e-07</v>
+        <v>1.303382859202198e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.515235716464268e-08</v>
+        <v>9.515235716463732e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.664088967782748e-07</v>
+        <v>1.664088967782661e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.180134272130771e-07</v>
+        <v>2.180134272130519e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.668001939874451e-07</v>
+        <v>2.668001939874137e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.668464629632144e-07</v>
+        <v>2.668464629631826e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.242376709448353e-07</v>
+        <v>3.242376709447958e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.678853889298127e-07</v>
+        <v>2.67885388929781e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.670025505995313e-07</v>
+        <v>2.670025505994996e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66846444907572e-07</v>
+        <v>2.668464449075401e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.678853941262227e-07</v>
+        <v>2.678853941261913e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66846444907572e-07</v>
+        <v>2.668464449075401e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.385524102674521e-07</v>
+        <v>2.053569542877197e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.66846444907572e-07</v>
+        <v>2.668464449075401e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.732000418764543e-07</v>
+        <v>5.732000418764524e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.204002895071936e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>3.30660963221478e-08</v>
+        <v>3.306609632214669e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.97292517987719e-07</v>
+        <v>9.972925179877173e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.97292517987719e-07</v>
+        <v>9.972925179877173e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.731472613426011e-07</v>
+        <v>5.73147261342595e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.235724206135308e-08</v>
+        <v>3.235724206135201e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.97292517987719e-07</v>
+        <v>9.972925179877173e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.388388126497969e-06</v>
+        <v>1.388388126497967e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.162288991410043e-07</v>
+        <v>6.162288991409264e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.727582248273289e-07</v>
+        <v>6.727582248273278e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.653001382144474e-07</v>
+        <v>5.653001382144455e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.186319511968625e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>3.394092059262716e-08</v>
+        <v>3.394092059262611e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.833636518222906e-07</v>
+        <v>9.833636518222896e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>9.833636518222906e-07</v>
+        <v>9.833636518222898e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>5.657587873789712e-07</v>
+        <v>5.657587873789652e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.365485700560387e-08</v>
+        <v>3.365485700560279e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.833636518222906e-07</v>
+        <v>9.833636518222896e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.368591187709642e-06</v>
+        <v>1.368591187709639e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.077178422282929e-07</v>
+        <v>6.077178422282167e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.635023831870771e-07</v>
+        <v>6.635023831870757e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.040361738924171e-07</v>
+        <v>1.040361738924173e-07</v>
       </c>
       <c r="C2" t="n">
         <v>1.145327242796077e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.212428010142885e-07</v>
+        <v>1.212428010142886e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.231161287571172e-07</v>
+        <v>1.231161287571173e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.231161287571172e-07</v>
+        <v>1.231161287571173e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246154643426488e-07</v>
+        <v>1.246154643426332e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.616074575865178e-07</v>
+        <v>1.616074575865177e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.231161287571172e-07</v>
+        <v>1.231161287571173e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.524220233465195e-07</v>
+        <v>1.524220233465196e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.034287307375527e-07</v>
+        <v>1.034287307375535e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.276547924451313e-07</v>
+        <v>1.27654792445132e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.520825789954438e-08</v>
+        <v>4.520825789954435e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.886966049801328e-08</v>
+        <v>4.886966049801326e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.886966049801328e-08</v>
+        <v>4.886966049801326e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.91735038685238e-08</v>
+        <v>4.917350386852396e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.006397443029901e-08</v>
+        <v>5.006397443029897e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.901566082716075e-08</v>
+        <v>4.9015660827161e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.524334576054353e-08</v>
+        <v>7.89116575557484e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.444411954825279e-08</v>
+        <v>5.444411954825284e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.495273576320083e-08</v>
+        <v>5.495246523737716e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.502327228638655e-08</v>
+        <v>5.502327228638657e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.621780388441663e-08</v>
+        <v>5.621780388441656e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.906950059711088e-08</v>
+        <v>5.540118880190661e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.535030463740137e-08</v>
+        <v>8.53503046374019e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.995997115888597e-08</v>
+        <v>5.629165936368181e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.606051092543404e-08</v>
+        <v>7.961516885990191e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.469134720318152e-08</v>
+        <v>5.469134720318144e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.527217899858372e-08</v>
+        <v>5.52721789985838e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.387840617639995e-08</v>
+        <v>6.387840617640007e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.383805168143245e-08</v>
+        <v>6.383805168143252e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.387773263699026e-08</v>
+        <v>6.3877732636991e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.462740723869477e-08</v>
+        <v>6.462740723869482e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.462740723869477e-08</v>
+        <v>6.462740723869482e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.403624921776305e-08</v>
+        <v>6.40362492177633e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.387840617639995e-08</v>
+        <v>6.387840617640007e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.492671977953821e-08</v>
+        <v>6.492671977953814e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.387840617639995e-08</v>
+        <v>6.387840617640007e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.387840617639995e-08</v>
+        <v>6.387840617640007e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.387840617639995e-08</v>
+        <v>6.387840617640007e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.48302311442671e-08</v>
+        <v>8.483023114426748e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.134264453593869e-07</v>
+        <v>1.134264453581543e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.19742886561689e-07</v>
+        <v>1.197428865616892e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066365387311282e-07</v>
+        <v>1.06636538731128e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.66170039636017e-08</v>
+        <v>8.661700396360167e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.139046825000012e-07</v>
+        <v>1.139046825000017e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.137468394591589e-07</v>
+        <v>1.137468394591592e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.147951530617765e-07</v>
+        <v>1.147951530617766e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.137525223263658e-07</v>
+        <v>1.137525223263661e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.429309030479206e-08</v>
+        <v>8.4293090304792e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4395265474334e-07</v>
+        <v>1.439526547433406e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.943341286111012e-07</v>
+        <v>1.943341286111013e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.371636747043148e-07</v>
+        <v>2.371636747043149e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.372040440025186e-07</v>
+        <v>2.372040440025183e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.877233058471783e-07</v>
+        <v>2.877233058471781e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.382523375007541e-07</v>
+        <v>2.382523375007545e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.373618722406454e-07</v>
+        <v>2.373618722406455e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.372040291992824e-07</v>
+        <v>2.372040291992829e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.382523428024204e-07</v>
+        <v>2.382523428024205e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.372040291992824e-07</v>
+        <v>2.372040291992829e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.113572971631073e-07</v>
+        <v>2.113572971631082e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372040291992824e-07</v>
+        <v>2.372040291992829e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.722201809973931e-07</v>
+        <v>5.722201809973941e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.19984645261241e-06</v>
+        <v>1.199846452612409e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>2.859360368627549e-08</v>
+        <v>2.859360368627557e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>9.942787850283559e-07</v>
+        <v>9.942787850283561e-07</v>
       </c>
       <c r="F8" t="n">
         <v>9.942787850283559e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.70230582720637e-07</v>
+        <v>5.702305827206363e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.795110563859529e-08</v>
+        <v>2.795110563859556e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.942787850283559e-07</v>
+        <v>9.942787850283561e-07</v>
       </c>
       <c r="J8" t="n">
         <v>1.381583323909194e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>6.119052460771181e-07</v>
+        <v>6.119052460771187e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.692590912163309e-07</v>
+        <v>6.692590912163308e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.641472419444775e-07</v>
+        <v>5.641472419444777e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.182109300715924e-06</v>
+        <v>1.182109300715925e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>2.931399986118401e-08</v>
+        <v>2.931399986118411e-08</v>
       </c>
       <c r="E9" t="n">
         <v>9.798825648238867e-07</v>
@@ -4773,19 +4773,19 @@
         <v>5.624835262685559e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>2.905457417908415e-08</v>
+        <v>2.905457417908417e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.798825648238867e-07</v>
+        <v>9.798825648238865e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361485920342496e-06</v>
+        <v>1.361485920342495e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>6.032401555777749e-07</v>
+        <v>6.03240155577775e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>6.598798565236766e-07</v>
+        <v>6.59879856523677e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.560961347220091e-07</v>
+        <v>3.560961347220154e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.531020946357721e-07</v>
+        <v>6.531020946357708e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.777235679896083e-07</v>
+        <v>2.777235679896101e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.531020946357721e-07</v>
+        <v>6.531020946357708e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.531020946357721e-07</v>
+        <v>6.531020946357708e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>8.231272119052904e-07</v>
+        <v>8.231272119052914e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.942039671588003e-07</v>
+        <v>4.942039671588025e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.531020946357721e-07</v>
+        <v>6.531020946357708e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.684764984685198e-06</v>
+        <v>4.6847649846852e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.34456863861704e-07</v>
+        <v>6.344568638617068e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.237044952111563e-07</v>
+        <v>9.237044952111568e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.739745089518424e-08</v>
+        <v>6.739745089518433e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.859087087664939e-08</v>
+        <v>6.859087087664941e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.85908708766494e-08</v>
+        <v>6.859087087664941e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.516383999953611e-08</v>
+        <v>6.516383999953777e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.780933812941655e-08</v>
+        <v>6.780933812941657e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.469637756763024e-08</v>
+        <v>6.469637756763342e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.098877029529405e-07</v>
+        <v>8.109268070118658e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.373158931371532e-08</v>
+        <v>8.373158931371561e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.940774043682212e-08</v>
+        <v>7.940792583449993e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.198894315522425e-08</v>
+        <v>8.198894315522424e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.425617879239842e-08</v>
+        <v>8.425617879239839e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.103551653848465e-07</v>
+        <v>8.156014313309141e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1810917316867e-07</v>
+        <v>1.181091731686728e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.130006635147266e-07</v>
+        <v>1.130006635147276e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.143624026240046e-07</v>
+        <v>8.400887522797715e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.082121162776484e-08</v>
+        <v>8.082121162776701e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.107175938146376e-08</v>
+        <v>8.107175938146669e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.676423622620812e-08</v>
+        <v>8.676423622620881e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.987719678799417e-08</v>
+        <v>8.987719678799418e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.676277835289911e-08</v>
+        <v>8.676277835290108e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.011301921084395e-08</v>
+        <v>9.011301921084399e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.011301921084395e-08</v>
+        <v>9.011301921084399e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.723169865811388e-08</v>
+        <v>8.723169865811522e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.676423622620812e-08</v>
+        <v>8.676423622620881e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.987719678799417e-08</v>
+        <v>8.987719678799418e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.676423622620812e-08</v>
+        <v>8.676423622620881e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.676423622620812e-08</v>
+        <v>8.676423622620881e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.676423622620812e-08</v>
+        <v>8.676423622620881e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.130123491631595e-07</v>
+        <v>1.130123491631609e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.561264561677585e-07</v>
+        <v>1.561264561695398e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.61024884617849e-07</v>
+        <v>1.610248846178504e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.452259628581428e-07</v>
+        <v>1.452259628581426e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.175274007192e-07</v>
+        <v>1.175274007191998e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.532464711462334e-07</v>
+        <v>1.532464711462347e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.527790087144882e-07</v>
+        <v>1.527790087144907e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.558919692761135e-07</v>
+        <v>1.558919692761132e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.527868238719594e-07</v>
+        <v>1.527868238719605e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.122736630564387e-07</v>
+        <v>1.122736630564397e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.943186097291793e-07</v>
+        <v>1.943186097291797e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.832825809701794e-07</v>
+        <v>2.832825809701797e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.507931927258472e-07</v>
+        <v>3.50793192725847e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.47680258009108e-07</v>
+        <v>3.476802580091096e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.251067224271193e-07</v>
+        <v>4.25106722427119e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.507931785745979e-07</v>
+        <v>3.507931785745977e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.481476945959669e-07</v>
+        <v>3.481476945959678e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.47680232164062e-07</v>
+        <v>3.47680232164061e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.507931927258472e-07</v>
+        <v>3.50793192725847e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.47680232164062e-07</v>
+        <v>3.47680232164061e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.103679910235574e-07</v>
+        <v>3.10367991023557e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.47680232164062e-07</v>
+        <v>3.47680232164061e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.652894570132538e-07</v>
+        <v>9.652894570132564e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.197373097715513e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.672328457073086e-07</v>
+        <v>9.672328457073107e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.197373097715513e-06</v>
@@ -5126,22 +5126,22 @@
         <v>1.197373097715513e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.550233233214009e-07</v>
+        <v>9.550233233214011e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.634073528195435e-07</v>
+        <v>9.634073528195456e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.197373097715513e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.719132496815174e-07</v>
+        <v>8.719132496815183e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.589739079474118e-07</v>
+        <v>9.589739079474148e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.544258566348231e-07</v>
+        <v>9.544258566348248e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.543176507363433e-07</v>
+        <v>9.543176507363441e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.186895926487244e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.551093124164407e-07</v>
+        <v>9.551093124164421e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.186895926487244e-06</v>
@@ -5166,22 +5166,22 @@
         <v>1.186895926487244e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.501309858543973e-07</v>
+        <v>9.501309858543978e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.535592660464103e-07</v>
+        <v>9.535592660464116e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.186895926487244e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.163243769348021e-07</v>
+        <v>9.163243769348039e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.517460674476301e-07</v>
+        <v>9.517460674476312e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.499062410252693e-07</v>
+        <v>9.540295713763993e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.96882518903276e-07</v>
+        <v>1.96882518903275e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.648617551279043e-07</v>
+        <v>5.648617551279038e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.595006678443443e-07</v>
+        <v>2.595006678443473e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.648617551279043e-07</v>
+        <v>5.648617551279038e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.648617551279043e-07</v>
+        <v>5.648617551279038e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.293924905039599e-07</v>
+        <v>6.293924905039628e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.454916584920243e-07</v>
+        <v>4.454916584920233e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.648617551279043e-07</v>
+        <v>5.648617551279038e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.992482381813273e-06</v>
+        <v>3.992482381813276e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.233694574212837e-07</v>
+        <v>5.233694574212839e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.016135369881469e-06</v>
+        <v>1.016135369881468e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.788980489309566e-08</v>
+        <v>5.78898048930949e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.905329070027209e-08</v>
+        <v>5.905329070027208e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.788980489309571e-08</v>
+        <v>5.788980489309484e-08</v>
       </c>
       <c r="E3" t="n">
         <v>6.013712750401053e-08</v>
@@ -5322,22 +5322,22 @@
         <v>6.013712750401053e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.835755863408827e-08</v>
+        <v>5.83575586340884e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.788980489309571e-08</v>
+        <v>5.788980489309484e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1003911112633e-08</v>
+        <v>6.100391111263299e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.788980489309571e-08</v>
+        <v>5.788980489309484e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.788980489309571e-08</v>
+        <v>5.788980489309484e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.788980489309571e-08</v>
+        <v>5.788980489309484e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.592538001557454e-08</v>
+        <v>7.223961580027786e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.465229649753348e-08</v>
+        <v>7.465229649753343e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.077614941218306e-08</v>
+        <v>7.077614941218253e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.327949749368421e-08</v>
+        <v>7.327949749368423e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.518674242454317e-08</v>
+        <v>7.518674242454324e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.639313375656743e-08</v>
+        <v>7.27073695412703e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.027861239810654e-07</v>
+        <v>1.02786123981065e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.903948623511205e-08</v>
+        <v>9.903948623511201e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.981514618538891e-08</v>
+        <v>7.461748556370915e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.206051668620383e-08</v>
+        <v>7.20605166862033e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.21472345876408e-08</v>
+        <v>7.214723458764035e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.567383277576498e-08</v>
+        <v>7.567383277576567e-08</v>
       </c>
       <c r="C5" t="n">
         <v>7.878793899530292e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.567300907109335e-08</v>
+        <v>7.567300907109315e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.853469720658336e-08</v>
+        <v>7.853469720658342e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.853469720658336e-08</v>
+        <v>7.853469720658342e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.61415865167581e-08</v>
+        <v>7.61415865167575e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.567383277576503e-08</v>
+        <v>7.567383277576565e-08</v>
       </c>
       <c r="I5" t="n">
         <v>7.878793899530292e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.567383277576503e-08</v>
+        <v>7.567383277576565e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.567383277576503e-08</v>
+        <v>7.567383277576565e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.567383277576503e-08</v>
+        <v>7.567383277576565e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.725220178247096e-08</v>
+        <v>9.725220178247119e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.321476151567018e-07</v>
+        <v>1.321476151567021e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.359079900658172e-07</v>
+        <v>1.359079900658169e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.234167309458511e-07</v>
+        <v>1.234167309458514e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.012306140696215e-07</v>
+        <v>1.012306140696218e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.297368352354863e-07</v>
+        <v>1.297368352354861e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.292690814947301e-07</v>
+        <v>1.2926908149473e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.323831877140311e-07</v>
+        <v>1.323831877140313e-07</v>
       </c>
       <c r="J6" t="n">
         <v>1.292753736309903e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.665747181245764e-08</v>
+        <v>9.665747181245772e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.627133894713956e-07</v>
+        <v>1.627133894713955e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.352757505984565e-07</v>
+        <v>2.352757505984569e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.904964125100591e-07</v>
+        <v>2.904964125100596e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.873823245087659e-07</v>
+        <v>2.873823245087657e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.506262729053697e-07</v>
+        <v>3.506262729053701e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.904963993062331e-07</v>
+        <v>2.904963993062336e-07</v>
       </c>
       <c r="G7" t="n">
         <v>2.878500600315146e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.873823062905214e-07</v>
+        <v>2.873823062905219e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.904964125100591e-07</v>
+        <v>2.904964125100596e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.873823062905214e-07</v>
+        <v>2.873823062905219e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.217708469651427e-07</v>
+        <v>2.57191570946824e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.873823062905214e-07</v>
+        <v>2.873823062905219e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.640460749733555e-07</v>
+        <v>9.640460749733561e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.193267196643413e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.625094516832004e-07</v>
+        <v>9.625094516832e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.193267196643413e-06</v>
@@ -5522,22 +5522,22 @@
         <v>1.193267196643413e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.535361665197511e-07</v>
+        <v>9.535361665197506e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.590571061370852e-07</v>
+        <v>9.590571061370843e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.193267196643413e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.759450991640322e-07</v>
+        <v>8.759450991640328e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.553557572828947e-07</v>
+        <v>9.553557572828945e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.461286957975025e-07</v>
+        <v>9.461286957975017e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.511033658499044e-07</v>
+        <v>9.511033658499048e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.182289698969399e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.504776424194984e-07</v>
+        <v>9.50477642419499e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.182289698969399e-06</v>
@@ -5562,22 +5562,22 @@
         <v>1.182289698969399e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.46823253700882e-07</v>
+        <v>9.468232537008815e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.49079285874346e-07</v>
+        <v>9.490792858743459e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.182289698969399e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.152553438162473e-07</v>
+        <v>9.15255343816247e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.475644992253947e-07</v>
+        <v>9.475644992253956e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.438217111703416e-07</v>
+        <v>9.499295850418879e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39867350021765e-07</v>
+        <v>2.398673500217687e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.149853463913403e-07</v>
+        <v>6.149853463913446e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.044001452929847e-07</v>
+        <v>3.044001452929825e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.149853463913403e-07</v>
+        <v>6.149853463913446e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.149853463913403e-07</v>
+        <v>6.149853463913446e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.116727542544124e-07</v>
+        <v>6.116727542545785e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.253182447689147e-07</v>
+        <v>4.253182447689098e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.149853463913403e-07</v>
+        <v>6.149853463913446e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.664070906609947e-06</v>
+        <v>3.664070906609955e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.83822025422044e-07</v>
+        <v>3.838220254220429e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.090090900055488e-07</v>
+        <v>3.477901850501563e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.482968786319946e-08</v>
+        <v>5.482968786320244e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.393665913020943e-08</v>
+        <v>5.393665913020965e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.482968786319971e-08</v>
+        <v>5.482968786320245e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.509325620716305e-08</v>
+        <v>5.509325620716298e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.509325620716314e-08</v>
+        <v>5.509325620716265e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.529689005917092e-08</v>
+        <v>5.52968900591708e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.482968786319971e-08</v>
+        <v>5.482968786320245e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.794023501666361e-08</v>
+        <v>5.794023501666312e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.482968786319971e-08</v>
+        <v>5.482968786320276e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.482968786319971e-08</v>
+        <v>5.482968786320245e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.482968786319971e-08</v>
+        <v>5.482968786320245e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.84119697326493e-08</v>
+        <v>6.841196973265275e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.072951036821381e-08</v>
+        <v>7.072951036821657e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.214910656700621e-08</v>
+        <v>6.721175376257896e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.954237899580737e-08</v>
+        <v>6.954237899580934e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.136784127795086e-08</v>
+        <v>7.136784127795004e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.887917192862017e-08</v>
+        <v>9.112258075132704e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.737653416716292e-08</v>
+        <v>9.737653416716348e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.376592570880459e-08</v>
+        <v>7.152251688611336e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.07365861205004e-08</v>
+        <v>9.465651852040449e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.809283467624168e-08</v>
+        <v>6.809283467624117e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.844769381149309e-08</v>
+        <v>6.844769381149515e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.130587891965207e-08</v>
+        <v>7.130587891965345e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.441642607311634e-08</v>
+        <v>7.441642607311499e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.130547512987668e-08</v>
+        <v>7.130547512987725e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.357047423991363e-08</v>
+        <v>7.357047423991138e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.357047423991363e-08</v>
+        <v>7.357047423991138e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.177308111562221e-08</v>
+        <v>7.177308111561904e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1305878919652e-08</v>
+        <v>7.130587891965099e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.441642607311634e-08</v>
+        <v>7.441642607311499e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.1305878919652e-08</v>
+        <v>7.130587891965099e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.1305878919652e-08</v>
+        <v>7.130587891965099e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.1305878919652e-08</v>
+        <v>7.130587891965099e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.182134390365202e-08</v>
+        <v>9.182134390365132e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.239315618911933e-07</v>
+        <v>1.239315618911902e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.278042716320722e-07</v>
+        <v>1.278042716320734e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.158665772737794e-07</v>
+        <v>1.15866577273776e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.5372191877954e-08</v>
+        <v>9.537219187795266e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.220916136326155e-07</v>
+        <v>1.220916136326189e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.216244114368896e-07</v>
+        <v>1.216244114368915e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.247349585901075e-07</v>
+        <v>1.247349585901088e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.216302685095492e-07</v>
+        <v>1.21630268509551e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.126773663012643e-08</v>
+        <v>9.126773663012678e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.527562074898243e-07</v>
+        <v>1.527562074898265e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.148700249999881e-07</v>
+        <v>2.14870024999973e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.64982182913005e-07</v>
+        <v>2.649821829130071e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.618716535945829e-07</v>
+        <v>2.618716535945782e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.192210467329735e-07</v>
+        <v>3.192210467329465e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.649821712938585e-07</v>
+        <v>2.649821712938558e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.623388379555337e-07</v>
+        <v>2.623388379555166e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.618716357595504e-07</v>
+        <v>2.618716357595513e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64982182913005e-07</v>
+        <v>2.649821829130071e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.618716357595504e-07</v>
+        <v>2.618716357595513e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.346387253972321e-07</v>
+        <v>2.346387253972198e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.618716357595504e-07</v>
+        <v>2.618716357595513e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.599799500439634e-07</v>
+        <v>9.599799500439619e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.188974659142726e-06</v>
+        <v>1.188974659142723e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.583496963008532e-07</v>
+        <v>9.583496963008539e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.188974659142726e-06</v>
+        <v>1.188974659142723e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.188974659142726e-06</v>
+        <v>1.188974659142723e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.507636413010038e-07</v>
+        <v>9.507636413010064e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.563610203375739e-07</v>
+        <v>9.563610203375728e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.188974659142726e-06</v>
+        <v>1.188974659142723e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.808188356371153e-07</v>
+        <v>8.808188356371144e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.557518307159819e-07</v>
+        <v>9.557518307159811e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.592810371159171e-07</v>
+        <v>9.592810371159182e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.477827344540857e-07</v>
+        <v>9.477827344540849e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.178941964164343e-06</v>
+        <v>1.178941964164342e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.471189103033147e-07</v>
+        <v>9.47118910303314e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.178941964164343e-06</v>
+        <v>1.178941964164342e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.178941964164343e-06</v>
+        <v>1.178941964164342e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.440316567055509e-07</v>
+        <v>9.440316567055506e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.463165058678702e-07</v>
+        <v>9.46316505867871e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.178941964164343e-06</v>
+        <v>1.178941964164342e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.155729087435042e-07</v>
+        <v>9.15572908743504e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.460611203535101e-07</v>
+        <v>9.460611203535095e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.475021557093166e-07</v>
+        <v>9.475021557093153e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.969081520027084e-07</v>
+        <v>3.969081520027119e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.229367595232682e-07</v>
+        <v>4.229367595232679e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.018701484619327e-07</v>
+        <v>3.01870148461933e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.229367595232682e-07</v>
+        <v>4.229367595232679e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.229367595232682e-07</v>
+        <v>4.229367595232679e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.201105697131402e-07</v>
+        <v>6.20110569713143e-07</v>
       </c>
       <c r="H2" t="n">
         <v>3.883587143939523e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.229367595232682e-07</v>
+        <v>4.229367595232679e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.138392858270232e-06</v>
+        <v>4.138392858270229e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.752498235558027e-07</v>
+        <v>5.752498235558042e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.899771097310254e-07</v>
+        <v>4.899771097310247e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.835053698114726e-08</v>
+        <v>5.835053698114722e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.968801715928852e-08</v>
+        <v>5.968801715928843e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.968801715928852e-08</v>
+        <v>5.968801715928843e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.906513040302736e-08</v>
+        <v>5.906513040302742e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.167724093411511e-08</v>
+        <v>6.167724093411508e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.860391420115937e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.292855088204951e-08</v>
+        <v>9.818588126255276e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.487557007779539e-08</v>
+        <v>7.487557007779525e-08</v>
       </c>
       <c r="D4" t="n">
         <v>1.004180843924457e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.349245999633197e-08</v>
+        <v>7.349245999633191e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.578370555964555e-08</v>
+        <v>7.57837055596455e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.338976708391723e-08</v>
+        <v>9.864709746442068e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.065811553528116e-07</v>
+        <v>7.289238984156112e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.600187761500524e-08</v>
+        <v>1.012592079955082e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.031350439096031e-07</v>
+        <v>1.031350439096029e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>7.278185614642478e-08</v>
+        <v>7.278185614642487e-08</v>
       </c>
       <c r="L4" t="n">
         <v>7.296101933718987e-08</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.730533202570356e-08</v>
+        <v>7.730533202570351e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.037865875865922e-08</v>
+        <v>8.037865875865906e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.730467390312971e-08</v>
+        <v>7.730467390312982e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.984454206426361e-08</v>
+        <v>7.984454206426349e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.984454206426361e-08</v>
+        <v>7.984454206426349e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.776654822757123e-08</v>
+        <v>7.776654822757143e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.730533202570356e-08</v>
+        <v>7.730533202570351e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.037865875865922e-08</v>
+        <v>8.037865875865906e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.730533202570356e-08</v>
+        <v>7.730533202570351e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.730533202570356e-08</v>
+        <v>7.730533202570351e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.730533202570356e-08</v>
+        <v>7.730533202570351e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.008789276429571e-07</v>
+        <v>1.008789276429572e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.381277104199427e-07</v>
+        <v>1.381277104199426e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.427492372831625e-07</v>
+        <v>1.427492372831629e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.28697210125293e-07</v>
+        <v>1.286972101252929e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.047333015808154e-07</v>
+        <v>1.047333015808153e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.360194694207557e-07</v>
+        <v>1.360194694207556e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.35558253219053e-07</v>
+        <v>1.355582532190531e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.386315799518435e-07</v>
+        <v>1.386315799518434e-07</v>
       </c>
       <c r="J6" t="n">
         <v>1.355650685893203e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.002347413745346e-07</v>
+        <v>1.002347413745347e-07</v>
       </c>
       <c r="L6" t="n">
         <v>1.71783708519735e-07</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.688713720580458e-07</v>
+        <v>2.688713720580461e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.334981371173817e-07</v>
+        <v>3.334981371173818e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.304248352224619e-07</v>
+        <v>3.30424835222462e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.045295091840249e-07</v>
+        <v>4.045295091840248e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.334981266603179e-07</v>
+        <v>3.33498126660318e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.308860265862938e-07</v>
+        <v>3.308860265862942e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.304248103844258e-07</v>
+        <v>3.304248103844264e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.334981371173817e-07</v>
+        <v>3.334981371173818e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.304248103844258e-07</v>
+        <v>3.304248103844264e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.947605169258929e-07</v>
+        <v>2.947605169258928e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.304248103844258e-07</v>
+        <v>3.304248103844264e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.592860285960918e-07</v>
+        <v>9.592860285960914e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.197246761700717e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.615840604008914e-07</v>
+        <v>9.615840604008908e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.197246761700717e-06</v>
@@ -6314,22 +6314,22 @@
         <v>1.197246761700717e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.540161238500721e-07</v>
+        <v>9.540161238500723e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.602995891377657e-07</v>
+        <v>9.602995891377649e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.197246761700717e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.787647980285461e-07</v>
+        <v>8.787647980285468e-07</v>
       </c>
       <c r="K8" t="n">
         <v>9.547308973190734e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.328338525724903e-07</v>
+        <v>9.585900382977381e-07</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.490529702813018e-07</v>
+        <v>9.490529702813021e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.183594503542899e-06</v>
+        <v>1.1835945035429e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.49989097043021e-07</v>
+        <v>9.499890970430212e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.183594503542899e-06</v>
+        <v>1.1835945035429e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.183594503542899e-06</v>
+        <v>1.1835945035429e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.468867673221043e-07</v>
+        <v>9.46886767322105e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.494723495184314e-07</v>
+        <v>9.49472349518431e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.183594503542899e-06</v>
+        <v>1.1835945035429e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.162909823430212e-07</v>
+        <v>9.162909823430207e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.47198361860858e-07</v>
+        <v>9.471983618608578e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.48776131937759e-07</v>
+        <v>9.487761319377584e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.72787079879214e-07</v>
+        <v>1.727870798792148e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108427244839812e-07</v>
+        <v>5.108427244839814e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.156547014459429e-07</v>
+        <v>5.156547014459426e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.108427244839812e-07</v>
+        <v>5.108427244839814e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.108427244839812e-07</v>
+        <v>5.108427244839814e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.747169855348104e-07</v>
+        <v>6.747169855348011e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.354918971803247e-07</v>
+        <v>3.35491897180326e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.108427244839812e-07</v>
+        <v>5.108427244839814e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.469979481970668e-06</v>
+        <v>2.469979481970671e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.25319756540229e-07</v>
+        <v>4.253197565402293e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.629948173332102e-07</v>
+        <v>5.629948173332121e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.399713790114899e-08</v>
+        <v>5.399713790114897e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
       <c r="E3" t="n">
+        <v>5.502038858557962e-08</v>
+      </c>
+      <c r="F3" t="n">
         <v>5.502038858557964e-08</v>
       </c>
-      <c r="F3" t="n">
-        <v>5.502038858557966e-08</v>
-      </c>
       <c r="G3" t="n">
-        <v>5.440623733886681e-08</v>
+        <v>5.44062373388678e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.701291601858965e-08</v>
+        <v>5.701291601858967e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.394559492253225e-08</v>
+        <v>5.394559492253218e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.70123614221464e-08</v>
+        <v>8.701236142214727e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.760262663879413e-08</v>
+        <v>6.76026266387942e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.475172933807698e-08</v>
+        <v>6.475188252241868e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.664750893541323e-08</v>
+        <v>6.664750893541327e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.833029116893815e-08</v>
+        <v>6.833029116893819e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.577666477535055e-08</v>
+        <v>8.747300383848288e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.534343628334485e-08</v>
+        <v>9.284810059040936e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.838334345507201e-08</v>
+        <v>9.007968251820468e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.128495905584146e-08</v>
+        <v>6.729345154843855e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.463714951648976e-08</v>
+        <v>6.463714951648977e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.543294855959384e-08</v>
+        <v>6.543294855959434e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.97376325669955e-08</v>
+        <v>6.973763256699557e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.280495366305295e-08</v>
+        <v>7.280495366305301e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.973703541565846e-08</v>
+        <v>6.973703541565837e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.224148344778329e-08</v>
+        <v>7.224148344778336e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.224148344778329e-08</v>
+        <v>7.224148344778336e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.019827498333137e-08</v>
+        <v>7.019827498333105e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.97376325669955e-08</v>
+        <v>6.973763256699557e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.280495366305295e-08</v>
+        <v>7.280495366305301e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.97376325669955e-08</v>
+        <v>6.973763256699557e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.97376325669955e-08</v>
+        <v>6.973763256699557e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.97376325669955e-08</v>
+        <v>6.973763256699557e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.913781908831212e-08</v>
+        <v>8.913781908831215e-08</v>
       </c>
       <c r="C6" t="n">
         <v>1.198409192926174e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.231479776751514e-07</v>
+        <v>1.231479776751524e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.121940777571657e-07</v>
+        <v>1.121940777571658e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.27622764175761e-08</v>
+        <v>9.276227641757617e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.177675716117385e-07</v>
+        <v>1.177675716117383e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.173069291953864e-07</v>
+        <v>1.173069291953869e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.203742502914603e-07</v>
+        <v>1.203742502914601e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.173124651593429e-07</v>
+        <v>1.173124651593436e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.861456341171023e-08</v>
+        <v>8.861456341171146e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.467319200979988e-07</v>
+        <v>1.46731920098e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.304213879858232e-07</v>
+        <v>2.304213879858237e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848220774795362e-07</v>
+        <v>2.848220774795364e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.817547815942701e-07</v>
+        <v>2.817547815942712e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4405970973621e-07</v>
+        <v>3.440597097362104e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.848220701027333e-07</v>
+        <v>2.848220701027336e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.822153987998139e-07</v>
+        <v>2.822153987998146e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.81754756383478e-07</v>
+        <v>2.81754756383479e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848220774795362e-07</v>
+        <v>2.848220774795364e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.81754756383478e-07</v>
+        <v>2.81754756383479e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.508053099918374e-07</v>
+        <v>2.520120117357413e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.81754756383478e-07</v>
+        <v>2.81754756383479e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.60289514052944e-07</v>
+        <v>9.602895140529453e-07</v>
       </c>
       <c r="C8" t="n">
         <v>1.189484380474567e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.506776638253945e-07</v>
+        <v>9.506776638253948e-07</v>
       </c>
       <c r="E8" t="n">
         <v>1.189484380474567e-06</v>
@@ -6710,22 +6710,22 @@
         <v>1.189484380474567e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.47000869715601e-07</v>
+        <v>9.470008697156016e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.566076163338544e-07</v>
+        <v>9.56607616333855e-07</v>
       </c>
       <c r="I8" t="n">
         <v>1.189484380474567e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.032896156218801e-07</v>
+        <v>9.032896156218805e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.534778560225699e-07</v>
+        <v>9.534778560225705e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.613822779078152e-07</v>
+        <v>9.512750444352987e-07</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.47079084488211e-07</v>
+        <v>9.47079084488212e-07</v>
       </c>
       <c r="C9" t="n">
         <v>1.177849092694762e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.431645722322149e-07</v>
+        <v>9.431645722322156e-07</v>
       </c>
       <c r="E9" t="n">
         <v>1.177849092694762e-06</v>
@@ -6750,7 +6750,7 @@
         <v>1.177849092694762e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.416515786379535e-07</v>
+        <v>9.416515786379547e-07</v>
       </c>
       <c r="H9" t="n">
         <v>9.455856410445466e-07</v>
@@ -6759,13 +6759,13 @@
         <v>1.177849092694762e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.238862592037774e-07</v>
+        <v>9.238862592037781e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.443052557190063e-07</v>
+        <v>9.44305255719007e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.475255633350877e-07</v>
+        <v>9.434164754260609e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.82019332374075e-07</v>
+        <v>1.820193323740743e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.553456445086613e-07</v>
+        <v>6.553456445086482e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.113338851792241e-07</v>
+        <v>4.113338851792235e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.553456445086613e-07</v>
+        <v>6.553456445086482e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.553456445086613e-07</v>
+        <v>6.553456445086482e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.080152697677407e-07</v>
+        <v>6.080152697677398e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.978107569365772e-07</v>
+        <v>3.978107569365758e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.553456445086613e-07</v>
+        <v>6.553456445086482e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.045317346214746e-06</v>
+        <v>2.045317346214749e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.218609484135259e-07</v>
+        <v>3.218609484135249e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.246737150840503e-07</v>
+        <v>5.263753521252685e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069968e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.303252058156963e-08</v>
+        <v>5.303252058156921e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069954e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.395905034587981e-08</v>
+        <v>5.395905034587939e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.395905034587978e-08</v>
+        <v>5.395905034587955e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.315811105959152e-08</v>
+        <v>5.315811105959145e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069954e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.580792028958779e-08</v>
+        <v>5.580792028958744e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069968e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069954e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.268930812069904e-08</v>
+        <v>5.268930812069954e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.340284777611119e-08</v>
+        <v>6.340284777611611e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.618731113851724e-08</v>
+        <v>6.61873111385171e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.275322720317992e-08</v>
+        <v>6.275322720317952e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>6.534783775919299e-08</v>
+        <v>6.534783775919145e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.656276689062066e-08</v>
+        <v>6.65627668906208e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.439843229131308e-08</v>
+        <v>6.387165071500716e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.889001148127745e-08</v>
+        <v>8.889001148127561e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.652145994500366e-08</v>
+        <v>6.652145994500238e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.801284138634334e-08</v>
+        <v>6.517224100358432e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.261093872624697e-08</v>
+        <v>6.261093872624563e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.35742923138249e-08</v>
+        <v>6.357429231382466e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.760390411068634e-08</v>
+        <v>6.760390411068579e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.072251627957506e-08</v>
+        <v>7.072251627957083e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.760330230693156e-08</v>
+        <v>6.760330230693187e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.015231055228756e-08</v>
+        <v>7.015231055228657e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.015231055228756e-08</v>
+        <v>7.015231055228657e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.807270704957882e-08</v>
+        <v>6.807270704957717e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.760390411068634e-08</v>
+        <v>6.760390411068579e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.072251627957506e-08</v>
+        <v>7.072251627957083e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.760390411068634e-08</v>
+        <v>6.760390411068579e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.760390411068634e-08</v>
+        <v>6.760390411068579e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.760390411068634e-08</v>
+        <v>6.760390411068579e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.571017254152694e-08</v>
+        <v>8.571017254152637e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.143960232375076e-07</v>
+        <v>1.14396023237509e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.172311479368945e-07</v>
+        <v>1.172311479368932e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.073137769005133e-07</v>
+        <v>1.073137769005118e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>8.931655356741948e-08</v>
+        <v>8.931655356741844e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.122864052446014e-07</v>
+        <v>1.122864052446007e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.118176023055836e-07</v>
+        <v>1.118176023055843e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.149362144745977e-07</v>
+        <v>1.149362144745968e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.118227331044253e-07</v>
+        <v>1.118227331044246e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>8.522521363452935e-08</v>
+        <v>8.522521363453061e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.390889957084214e-07</v>
+        <v>1.390889957084236e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.114822788659347e-07</v>
+        <v>2.114822788659384e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.607471375482682e-07</v>
+        <v>2.607471375482758e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.576285450506057e-07</v>
+        <v>2.576285450506026e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.139989364887204e-07</v>
+        <v>3.139989364887197e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607471304603101e-07</v>
+        <v>2.607471304603112e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.58097328318272e-07</v>
+        <v>2.580973283182691e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.576285253793794e-07</v>
+        <v>2.576285253793717e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.607471375482682e-07</v>
+        <v>2.607471375482758e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.576285253793794e-07</v>
+        <v>2.576285253793717e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.298064500273432e-07</v>
+        <v>2.298064500273388e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.576285253793794e-07</v>
+        <v>2.576285253793717e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.580715571454845e-07</v>
+        <v>9.580715571454843e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.184255866847179e-06</v>
+        <v>1.184255866847178e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.51974794700815e-07</v>
+        <v>9.519747947008151e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.184255866847179e-06</v>
+        <v>1.184255866847178e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.184255866847179e-06</v>
+        <v>1.184255866847178e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.471969044752903e-07</v>
+        <v>9.471969044752906e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.533902824056247e-07</v>
+        <v>9.533902824056246e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.184255866847179e-06</v>
+        <v>1.184255866847178e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>9.128451095632979e-07</v>
+        <v>9.128451095632968e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.541718630517404e-07</v>
+        <v>9.5417186305174e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.50345451330055e-07</v>
+        <v>9.57611705178006e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.450410572403333e-07</v>
+        <v>9.450410572403335e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.174794047074503e-06</v>
+        <v>1.174794047074501e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.425581315496517e-07</v>
+        <v>9.425581315496524e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.174794047074503e-06</v>
+        <v>1.174794047074501e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.174794047074503e-06</v>
+        <v>1.174794047074501e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.406221970404837e-07</v>
+        <v>9.406221970404845e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.431417473113775e-07</v>
+        <v>9.431417473113774e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.174794047074503e-06</v>
+        <v>1.174794047074501e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.266390912835076e-07</v>
+        <v>9.26639091283507e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.434531126198844e-07</v>
+        <v>9.434531126198849e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.448565393588735e-07</v>
+        <v>9.448565393588741e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.062226543567986e-07</v>
+        <v>5.062226543567983e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.671049605677908e-07</v>
+        <v>6.671049605677918e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.560460404301913e-07</v>
+        <v>2.560460404302162e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.671049605677908e-07</v>
+        <v>6.671049605677918e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671049605677908e-07</v>
+        <v>6.671049605677918e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>7.718337712660448e-07</v>
+        <v>7.718337712660481e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.842551739745289e-07</v>
+        <v>4.842551739745278e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.671049605677908e-07</v>
+        <v>6.671049605677918e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.554122772374571e-06</v>
+        <v>3.554122772374572e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.244263381076681e-07</v>
+        <v>6.244263381076671e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.203568833445779e-07</v>
+        <v>1.609440828698985e-06</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>6.465739713047138e-08</v>
+        <v>6.46573971304709e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.59076819269868e-08</v>
+        <v>6.59076819269864e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>6.590768192698679e-08</v>
+        <v>6.590768192698513e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.341522600175861e-08</v>
+        <v>6.341522600175912e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>6.606375380082363e-08</v>
+        <v>6.606375380082331e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.294723086391633e-08</v>
+        <v>6.294723086391605e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.853735851410272e-08</v>
+        <v>7.853735851410221e-08</v>
       </c>
       <c r="C4" t="n">
         <v>8.117223279961612e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.687313259016674e-08</v>
+        <v>7.687313259016731e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.957374251937678e-08</v>
+        <v>7.957374251937661e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>8.172294182451203e-08</v>
+        <v>8.172294182451227e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.069571174037823e-07</v>
+        <v>1.06957117403784e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.147616996408725e-07</v>
+        <v>1.147616996408689e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.096056452028473e-07</v>
+        <v>1.096056452028476e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.112431940312955e-07</v>
+        <v>1.112431940312976e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>7.836832895530327e-08</v>
+        <v>7.836832895530363e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.858523912277076e-08</v>
+        <v>7.858523912276958e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.367362809985333e-08</v>
+        <v>8.36736280998535e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.679015103676064e-08</v>
+        <v>8.679015103675968e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.367244904557228e-08</v>
+        <v>8.367244904557193e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.675166253061045e-08</v>
+        <v>8.675166253060992e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.675166253061045e-08</v>
+        <v>8.675166253060992e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.414162323769557e-08</v>
+        <v>8.414162323769465e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.367362809985333e-08</v>
+        <v>8.36736280998535e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.679015103676064e-08</v>
+        <v>8.679015103675968e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.367362809985333e-08</v>
+        <v>8.36736280998535e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.367362809985333e-08</v>
+        <v>8.36736280998535e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.367362809985333e-08</v>
+        <v>8.36736280998535e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.088407724338534e-07</v>
+        <v>1.08840772433855e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497290795665471e-07</v>
+        <v>1.497290795650207e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.544793048037807e-07</v>
+        <v>1.544793048037808e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.393943686858502e-07</v>
+        <v>1.39394368685852e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.131332521529973e-07</v>
+        <v>1.131332521529983e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.471091453686375e-07</v>
+        <v>1.471091453686383e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466411502309143e-07</v>
+        <v>1.466411502309154e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.497576731677026e-07</v>
+        <v>1.497576731677019e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.466485789634861e-07</v>
+        <v>1.466485789634877e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.081386110195879e-07</v>
+        <v>1.081386110195886e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.861268055411403e-07</v>
+        <v>1.861268055411417e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.796060956004486e-07</v>
+        <v>2.796060956004609e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.464013585823207e-07</v>
+        <v>3.464013585823299e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.432848615408195e-07</v>
+        <v>3.432848615408272e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.198852831165373e-07</v>
+        <v>4.198852831165298e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.46401346838986e-07</v>
+        <v>3.464013468390007e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.437528307832554e-07</v>
+        <v>3.437528307832552e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.432848356454133e-07</v>
+        <v>3.432848356454387e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.464013585823207e-07</v>
+        <v>3.464013585823299e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.432848356454133e-07</v>
+        <v>3.432848356454387e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.063891344691541e-07</v>
+        <v>3.063891344691623e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.432848356454133e-07</v>
+        <v>3.432848356454387e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7490,34 +7490,34 @@
         <v>9.598131685813158e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.195013134710443e-06</v>
+        <v>1.195013134710444e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.65902116290978e-07</v>
+        <v>9.659021162909766e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.195013134710443e-06</v>
+        <v>1.195013134710444e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.195013134710443e-06</v>
+        <v>1.195013134710444e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.53947399337002e-07</v>
+        <v>9.539473993370016e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.613582117981299e-07</v>
+        <v>9.613582117981297e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.195013134710443e-06</v>
+        <v>1.195013134710444e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.945598358425241e-07</v>
+        <v>8.945598358425232e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.570887758942139e-07</v>
+        <v>9.570887758942152e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.63316503016842e-07</v>
+        <v>9.633165030168428e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.510347979893053e-07</v>
+        <v>9.510347979893047e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.184813155924981e-06</v>
+        <v>1.184813155924982e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.535149067236387e-07</v>
+        <v>9.535149067236383e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.184813155924981e-06</v>
+        <v>1.184813155924982e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.184813155924981e-06</v>
+        <v>1.184813155924982e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.486429195383485e-07</v>
+        <v>9.4864291953835e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.516724887813905e-07</v>
+        <v>9.516724887813892e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.184813155924981e-06</v>
+        <v>1.184813155924982e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.244864602515114e-07</v>
+        <v>9.244864602515115e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.499258737056276e-07</v>
+        <v>9.499258737056274e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.524670382604044e-07</v>
+        <v>9.423686817430942e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.984562540200129e-07</v>
+        <v>1.984562540200111e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.679574107153634e-07</v>
+        <v>5.679574107153602e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.579252718966981e-07</v>
+        <v>4.579252718966921e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.679574107153634e-07</v>
+        <v>5.679574107153602e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>5.679574107153634e-07</v>
+        <v>5.679574107153602e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.595927124765129e-07</v>
+        <v>6.595927124764963e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.30911279901211e-07</v>
+        <v>3.309112799012073e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.679574107153634e-07</v>
+        <v>5.679574107153602e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>3.203828208276981e-06</v>
+        <v>3.203828208276978e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.341222405233018e-07</v>
+        <v>4.341222405232992e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.742624636048826e-07</v>
+        <v>6.446636552686798e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.724101265926788e-08</v>
+        <v>5.724101265926706e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.830232435828817e-08</v>
+        <v>5.83023243582874e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.830232435828816e-08</v>
+        <v>5.830232435828752e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.695146291902348e-08</v>
+        <v>5.695146291902255e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.958420465312265e-08</v>
+        <v>5.958420465312175e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.648613816354677e-08</v>
+        <v>5.648613816354618e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.266190658235317e-08</v>
+        <v>9.2661906582347e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.20918204245405e-08</v>
+        <v>7.209182042453863e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.874885201663269e-08</v>
+        <v>6.874901036778689e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.088485408614574e-08</v>
+        <v>7.088485408614335e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>7.267811493009334e-08</v>
+        <v>7.267811493009117e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.008195596518686e-08</v>
+        <v>9.31272313378234e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.938523782923768e-08</v>
+        <v>9.938523782923468e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.575997307192908e-08</v>
+        <v>9.575997307192285e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.183051625962772e-08</v>
+        <v>7.18305162596268e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.919266782289999e-08</v>
+        <v>6.919266782289955e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.979487387080524e-08</v>
+        <v>6.979487387080445e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.33367192868272e-08</v>
+        <v>7.333671928682519e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.643478577640306e-08</v>
+        <v>7.643478577640109e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.33359786456929e-08</v>
+        <v>7.333597864569099e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.60658290695939e-08</v>
+        <v>7.606582906959206e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.60658290695939e-08</v>
+        <v>7.606582906959206e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.380204404230385e-08</v>
+        <v>7.380204404230186e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.33367192868272e-08</v>
+        <v>7.333671928682519e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.643478577640306e-08</v>
+        <v>7.643478577640109e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.33367192868272e-08</v>
+        <v>7.333671928682519e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.33367192868272e-08</v>
+        <v>7.333671928682519e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.33367192868272e-08</v>
+        <v>7.333671928682519e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.400845676587588e-08</v>
+        <v>9.400845676587244e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.271386430611337e-07</v>
+        <v>1.271386430611285e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.306864919480152e-07</v>
+        <v>1.306864919480096e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.188675929819749e-07</v>
+        <v>1.1886759298197e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.784982542253027e-08</v>
+        <v>9.784982542252681e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.248525758142736e-07</v>
+        <v>1.24852575814268e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.243872510589558e-07</v>
+        <v>1.243872510589504e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.274853175483728e-07</v>
+        <v>1.274853175483675e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.24393221273546e-07</v>
+        <v>1.243932212735405e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.344415507262006e-08</v>
+        <v>9.344415507261652e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.561204418495441e-07</v>
+        <v>1.561204418495366e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.339802182581242e-07</v>
+        <v>2.339802182581213e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.89010640704183e-07</v>
+        <v>2.890106407041788e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.859125977697173e-07</v>
+        <v>2.859125977697134e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.489394891022995e-07</v>
+        <v>3.48939489102295e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.890106322840555e-07</v>
+        <v>2.890106322840518e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.863778989700832e-07</v>
+        <v>2.8637789897008e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.859125742146069e-07</v>
+        <v>2.859125742146031e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.89010640704183e-07</v>
+        <v>2.890106407041788e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.859125742146069e-07</v>
+        <v>2.859125742146031e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.20520462067668e-07</v>
+        <v>2.558227731265018e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.859125742146069e-07</v>
+        <v>2.859125742146031e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.621942091671553e-07</v>
+        <v>9.621942091671538e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.191094169148415e-06</v>
+        <v>1.191094169148413e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>9.552097875347029e-07</v>
+        <v>9.552097875347012e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191094169148415e-06</v>
+        <v>1.191094169148413e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191094169148415e-06</v>
+        <v>1.191094169148413e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>9.503852576339491e-07</v>
+        <v>9.503852576339477e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.594910966189632e-07</v>
+        <v>9.594910966189613e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191094169148415e-06</v>
+        <v>1.191094169148413e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>8.924718252191181e-07</v>
+        <v>8.924718252191167e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.55828554066831e-07</v>
+        <v>9.558285540668295e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.530545946794433e-07</v>
+        <v>9.530545946794414e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.493138418347028e-07</v>
+        <v>9.493138418347004e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.180242318970954e-06</v>
+        <v>1.180242318970952e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.464694110313826e-07</v>
+        <v>9.464694110313804e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.180242318970954e-06</v>
+        <v>1.180242318970952e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.180242318970954e-06</v>
+        <v>1.180242318970952e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>9.444993911146547e-07</v>
+        <v>9.444993911146531e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.482187085352908e-07</v>
+        <v>9.482187085352899e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.180242318970954e-06</v>
+        <v>1.180242318970952e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>9.209443160471563e-07</v>
+        <v>9.209443160471556e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.467216759316999e-07</v>
+        <v>9.46721675931698e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.4560095150249e-07</v>
+        <v>9.456009515024878e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ozone depletion results.xlsx
+++ b/Results/Hydrogen/hydrogen ozone depletion results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.651706613531729e-07</v>
+        <v>9.605960709186793e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>9.145166026168603e-07</v>
+        <v>1.196700028947705e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.886506705675617e-07</v>
+        <v>9.602984776820811e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>9.145166026168603e-07</v>
+        <v>1.196700028947705e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>9.145166026168603e-07</v>
+        <v>1.196700028947705e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.170287915693583e-06</v>
+        <v>9.610450291534732e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.583624398793613e-07</v>
+        <v>9.60606445288133e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.145166026168603e-07</v>
+        <v>1.196700028947705e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.710107555988503e-06</v>
+        <v>9.635256467482761e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>8.000979962771263e-07</v>
+        <v>9.607202254084738e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.283447018299208e-07</v>
+        <v>9.625740444379414e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>7.146815117158661e-08</v>
+        <v>1.214662691967795e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>7.289208792807714e-08</v>
+        <v>1.214662691967795e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.289208792807714e-08</v>
+        <v>1.214662691967795e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.97964972366892e-08</v>
+        <v>9.75026937035472e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>7.242081946543869e-08</v>
+        <v>1.214662691967795e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>6.933311182666949e-08</v>
+        <v>9.750579337005343e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.736415401978689e-08</v>
+        <v>6.651706613531745e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.990345209973942e-08</v>
+        <v>9.145166026168642e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>8.601949473044726e-08</v>
+        <v>3.886506705675618e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.796760607962473e-08</v>
+        <v>9.145166026168642e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>9.060176395991117e-08</v>
+        <v>9.145166026168642e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.220987756510046e-07</v>
+        <v>1.170287915693583e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.310842478698963e-07</v>
+        <v>7.583624398793624e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.247230978797541e-07</v>
+        <v>9.145166026168642e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.268610746429592e-07</v>
+        <v>3.710107555988503e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>8.686774140965324e-08</v>
+        <v>8.000979962771271e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>8.737489341768643e-08</v>
+        <v>5.283447018299216e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.558818217367315e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.867588981244244e-08</v>
+        <v>7.146815117158665e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.558656465495107e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.883174185922789e-08</v>
+        <v>7.289208792807713e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.883174185922789e-08</v>
+        <v>7.289208792807711e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.605156758369289e-08</v>
+        <v>6.97964972366892e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.558818217367315e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.867588981244244e-08</v>
+        <v>7.242081946543866e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.558818217367315e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.558818217367315e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.558818217367315e-08</v>
+        <v>6.933311182666948e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.264874851429993e-07</v>
+        <v>8.736415401978689e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.768963367553359e-07</v>
+        <v>8.990345209973968e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.834282182585277e-07</v>
+        <v>8.60194947304473e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.639813380197947e-07</v>
+        <v>8.79676060796246e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.311640775478342e-07</v>
+        <v>9.060176395991122e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.741123613369166e-07</v>
+        <v>1.220987756510046e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.736489759269881e-07</v>
+        <v>1.310842478698963e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.767366835656661e-07</v>
+        <v>1.24723097879754e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.736582443555252e-07</v>
+        <v>1.268610746429592e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.256114362518045e-07</v>
+        <v>8.686774140965382e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.229130964863801e-07</v>
+        <v>8.737489341768638e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.450186398299924e-07</v>
+        <v>9.558818217367318e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.290694212158801e-07</v>
+        <v>9.867588981244238e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.259817466955902e-07</v>
+        <v>9.558656465495107e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.224990991591156e-07</v>
+        <v>9.88317418592279e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.290694032919895e-07</v>
+        <v>9.88317418592279e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.264450989871308e-07</v>
+        <v>9.605156758369289e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.25981713577111e-07</v>
+        <v>9.558818217367318e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.290694212158801e-07</v>
+        <v>9.867588981244238e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.259817135771109e-07</v>
+        <v>9.558818217367318e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.240347432883453e-07</v>
+        <v>9.558818217367318e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.25981713577111e-07</v>
+        <v>9.558818217367318e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.618847530618522e-07</v>
+        <v>1.264874851429993e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.196254784845937e-06</v>
+        <v>1.76896336755336e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.681262228516215e-07</v>
+        <v>1.834282182585278e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.196254784845937e-06</v>
+        <v>1.639813380197946e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.196254784845937e-06</v>
+        <v>1.311640775478341e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.519081480508309e-07</v>
+        <v>1.741123613369166e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.619239155570971e-07</v>
+        <v>1.736489759269882e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.196254784845937e-06</v>
+        <v>1.767366835656661e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.010721441791361e-07</v>
+        <v>1.736582443555253e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.592999478218282e-07</v>
+        <v>1.256114362518045e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.212678980879043e-07</v>
+        <v>2.2291309648638e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.450186398299922e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.290694212158801e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.259817466955901e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.224990991591153e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.290694032919894e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.264450989871307e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.259817135771109e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.290694212158801e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.259817135771109e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.240347432883454e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.259817135771109e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.61884753061853e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.196254784845938e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.681262228516223e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.196254784845938e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.196254784845938e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.519081480508317e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.619239155570977e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.196254784845938e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.010721441791367e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.592999478218282e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.212678980879052e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.546022317476422e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.54602231747643e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.188324372544741e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>9.571445271557733e-07</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>9.571445271557744e-07</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.188324372544741e-06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.188324372544741e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.505259064902516e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.546304251772352e-07</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.505259064902525e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.546304251772366e-07</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.188324372544741e-06</v>
       </c>
-      <c r="J9" t="n">
-        <v>9.29861876737318e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.535502916159398e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.565226839205542e-07</v>
+      <c r="J11" t="n">
+        <v>9.298618767373194e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.535502916159406e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.565226839205553e-07</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.475130347171903e-07</v>
+        <v>9.487238500119072e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.838389911660792e-07</v>
+        <v>1.184343977346457e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.439260096538662e-07</v>
+        <v>9.490979833487007e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.838389911660792e-07</v>
+        <v>1.184343977346457e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.838389911660792e-07</v>
+        <v>1.184343977346457e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.186226459757295e-07</v>
+        <v>9.493099992807397e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.675904616680553e-07</v>
+        <v>9.489570172345315e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.838389911660792e-07</v>
+        <v>1.184343977346457e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.726095295142049e-06</v>
+        <v>9.516291421764076e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>5.446507954769093e-07</v>
+        <v>9.49247531690062e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.753245644778097e-07</v>
+        <v>9.491139903496063e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.444262604538139e-08</v>
+        <v>1.202255386285129e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.547887594297984e-08</v>
+        <v>1.202255386285129e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.547887594298086e-08</v>
+        <v>1.202255386285129e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.49093477114241e-08</v>
+        <v>9.635837274231003e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>5.756452016117526e-08</v>
+        <v>1.202255386285129e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.443971439316263e-08</v>
+        <v>9.635700013179132e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.651514678564649e-08</v>
+        <v>1.475130347171891e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.924052549912012e-08</v>
+        <v>6.838389911660801e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>8.974800379447538e-08</v>
+        <v>4.439260096538658e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.821874712574116e-08</v>
+        <v>6.838389911660801e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.968366978411532e-08</v>
+        <v>6.838389911660801e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.836858293309386e-08</v>
+        <v>6.186226459757303e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.450549148719053e-08</v>
+        <v>3.67590461668056e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.963995255365935e-08</v>
+        <v>6.838389911660801e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.858014111086841e-08</v>
+        <v>2.726095295142041e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.629819472816505e-08</v>
+        <v>5.44650795476909e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.665318060854031e-08</v>
+        <v>1.753245644778106e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.030873602672601e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.34335417947353e-08</v>
+        <v>5.444262604538203e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.030817142273557e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.279352432970044e-08</v>
+        <v>5.547887594297944e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.279352432970071e-08</v>
+        <v>5.547887594297944e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.077836934498628e-08</v>
+        <v>5.49093477114245e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.030873602672601e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.34335417947353e-08</v>
+        <v>5.7564520161175e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.030873602672601e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.030873602672601e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.030873602672601e-08</v>
+        <v>5.443971439316266e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.970295806046272e-08</v>
+        <v>6.651514678564649e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.204650566051792e-07</v>
+        <v>6.924052549911958e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.238033691448631e-07</v>
+        <v>8.974800379447414e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.128055641474674e-07</v>
+        <v>6.821874712574172e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.334158602433013e-08</v>
+        <v>6.968366978411638e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.184164536378084e-07</v>
+        <v>8.836858293309079e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.179468203197195e-07</v>
+        <v>9.450549148719026e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.210716260875565e-07</v>
+        <v>6.963995255365944e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.179523709729652e-07</v>
+        <v>6.858014111086915e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.917831382451304e-08</v>
+        <v>6.629819472816375e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.474498960940471e-07</v>
+        <v>6.665318060853834e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.144458524949816e-07</v>
+        <v>7.030873602672461e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.643621599381836e-07</v>
+        <v>7.343354179473734e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.612373747481765e-07</v>
+        <v>7.030817142273417e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.183585702326962e-07</v>
+        <v>7.279352432970156e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.643621526576768e-07</v>
+        <v>7.279352432970156e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.617069874884336e-07</v>
+        <v>7.077836934498711e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.612373541701734e-07</v>
+        <v>7.030873602672461e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.643621599381836e-07</v>
+        <v>7.343354179473734e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.612373541701734e-07</v>
+        <v>7.030873602672461e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.341261829901865e-07</v>
+        <v>7.030873602672461e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.612373541701734e-07</v>
+        <v>7.030873602672461e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.612930077641645e-07</v>
+        <v>8.970295806046398e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.185957163084507e-06</v>
+        <v>1.204650566051788e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.534567430148303e-07</v>
+        <v>1.238033691448623e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.185957163084507e-06</v>
+        <v>1.128055641474687e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.185957163084507e-06</v>
+        <v>9.334158602433069e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.493788248246632e-07</v>
+        <v>1.184164536378073e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.565431502931288e-07</v>
+        <v>1.17946820319718e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.185957163084507e-06</v>
+        <v>1.210716260875581e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.008988771526812e-07</v>
+        <v>1.179523709729648e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.503312476463095e-07</v>
+        <v>8.917831382451037e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.610340821585901e-07</v>
+        <v>1.474498960940465e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.144458524949804e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.643621599381836e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.612373747481765e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.183585702326969e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.643621526576785e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.617069874884334e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.612373541701714e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.643621599381836e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.612373541701713e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.341261829901847e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.612373541701713e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.612930077641649e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.185957163084507e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.534567430148292e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.185957163084507e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.185957163084507e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.493788248246643e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.565431502931296e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.185957163084507e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.008988771526798e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.503312476463104e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.610340821585918e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.476878106886036e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.476878106886041e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.176928233850819e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>9.444964185917542e-07</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>9.444964185917548e-07</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.176928233850819e-06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.176928233850819e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.428467233301125e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.45759777625009e-07</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.428467233301127e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.457597776250095e-07</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.176928233850819e-06</v>
       </c>
-      <c r="J9" t="n">
-        <v>9.231135809602029e-07</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>9.231135809602031e-07</v>
+      </c>
+      <c r="K11" t="n">
         <v>9.432238565800785e-07</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.475842820453202e-07</v>
+      <c r="L11" t="n">
+        <v>9.475842820453215e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.684115361692702e-07</v>
+        <v>5.673436589734793e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.377296150015388e-07</v>
+        <v>1.194711877543685e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.277963524738293e-07</v>
+        <v>3.968602648013988e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.752036481341675e-07</v>
+        <v>9.909692783802535e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.752036481341675e-07</v>
+        <v>9.909692783802535e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.996003791307242e-07</v>
+        <v>5.716137699868949e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.044317049764738e-07</v>
+        <v>3.984094624141465e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>4.752036481341675e-07</v>
+        <v>9.909692783802535e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.220415052425719e-06</v>
+        <v>1.376627097037597e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.448715532207486e-07</v>
+        <v>6.159113254269195e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.876440021599351e-07</v>
+        <v>6.681472153659024e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.893887053238868e-08</v>
+        <v>5.759756013386485e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.516582858269598e-08</v>
+        <v>1.213242662477878e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.893887053238893e-08</v>
+        <v>3.996386081295053e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>6.041194414595592e-08</v>
+        <v>1.006103498047401e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.041194414595619e-08</v>
+        <v>1.006103498047401e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.909743560655121e-08</v>
+        <v>5.800591977709903e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.893887053238894e-08</v>
+        <v>3.996386081295053e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.99935657162377e-08</v>
+        <v>1.006103498047401e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.893887053238894e-08</v>
+        <v>1.397110466503615e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.893887053238893e-08</v>
+        <v>6.249994533178541e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.893887053238893e-08</v>
+        <v>6.780897327664205e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.008238354638956e-07</v>
+        <v>2.684115361692733e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.85498641529188e-08</v>
+        <v>3.377296150015423e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.88714451809248e-08</v>
+        <v>2.277963524738261e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.889256437478184e-08</v>
+        <v>4.752036481341722e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.070121073508047e-08</v>
+        <v>4.752036481341722e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.971843633652768e-08</v>
+        <v>4.996003791307274e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.091995555556219e-07</v>
+        <v>4.044317049764706e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.061456644622121e-08</v>
+        <v>4.752036481341722e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.025200001969132e-07</v>
+        <v>1.220415052425718e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.939300626067934e-08</v>
+        <v>5.448715532207497e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.966067796935321e-08</v>
+        <v>5.876440021599344e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.085189186332941e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.080157235464091e-08</v>
+        <v>5.51658285826959e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.085095861459082e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.207601514683053e-08</v>
+        <v>6.041194414595562e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.207601514683053e-08</v>
+        <v>6.041194414595564e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.101045693749119e-08</v>
+        <v>5.909743560655101e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.085189186332941e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.190658704718272e-08</v>
+        <v>5.999356571623768e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.085189186332941e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.085189186332941e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.085189186332941e-08</v>
+        <v>5.893887053238828e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.087042663100691e-07</v>
+        <v>1.008238354638944e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.501457263465836e-07</v>
+        <v>6.854986415292765e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.585933706016204e-07</v>
+        <v>6.887144518093334e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.399318850551353e-07</v>
+        <v>6.889256437478557e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1117040033247e-07</v>
+        <v>7.070121073508244e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.501837699017647e-07</v>
+        <v>6.971843633653096e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500252048280627e-07</v>
+        <v>1.091995555556241e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.510799000114511e-07</v>
+        <v>7.061456644621769e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.500333254429225e-07</v>
+        <v>1.025200001969281e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.079367086740627e-07</v>
+        <v>6.939300626068479e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.931883801877562e-07</v>
+        <v>6.966067796935504e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.631479067484249e-07</v>
+        <v>8.085189186333136e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.237948198342674e-07</v>
+        <v>8.080157235464046e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.238451650457061e-07</v>
+        <v>8.085095861459175e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.949431684101668e-07</v>
+        <v>8.207601514682976e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.24899827505821e-07</v>
+        <v>8.207601514682976e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.240037044171208e-07</v>
+        <v>8.101045693749406e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.238451393429469e-07</v>
+        <v>8.085189186333136e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.248998345268082e-07</v>
+        <v>8.190658704718078e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.238451393429469e-07</v>
+        <v>8.085189186333136e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.886769352117147e-07</v>
+        <v>8.085189186333136e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.238451393429511e-07</v>
+        <v>8.085189186333136e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.711656339046955e-07</v>
+        <v>1.087042663100694e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206842989184607e-06</v>
+        <v>1.501457263465832e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.592185194276417e-08</v>
+        <v>1.585933706016183e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.964684810564903e-07</v>
+        <v>1.39931885055136e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.964684810564903e-07</v>
+        <v>1.111704003324709e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.700466237019583e-07</v>
+        <v>1.501837699017636e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.281251597253452e-08</v>
+        <v>1.500252048280624e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.964684810564903e-07</v>
+        <v>1.510799000114503e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.371500598471986e-06</v>
+        <v>1.500333254429179e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.136779640394429e-07</v>
+        <v>1.079367086740642e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674226905299175e-07</v>
+        <v>1.931883801877546e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.631479067484283e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.237948198342676e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.238451650457045e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.949431684101657e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.2489982750582e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.240037044171215e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.238451393429586e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.248998345268081e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.238451393429586e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.886769352117323e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.238451393429586e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.711656339046958e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.206842989184607e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.592185194276437e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.964684810564918e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.964684810564918e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.700466237019576e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.28125159725343e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.964684810564918e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.371500598471986e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.136779640394428e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.674226905299182e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.651551084625736e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>5.651551084625735e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.191800005800699e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.78468995630876e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>3.784689956308719e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.86585314944413e-07</v>
+      </c>
+      <c r="F11" t="n">
         <v>9.865853149444128e-07</v>
       </c>
-      <c r="F9" t="n">
-        <v>9.865853149444128e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.670580168773052e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.658706154904132e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.865853149444128e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.364974525469399e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.107600117257975e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.632936771544477e-07</v>
+      <c r="G11" t="n">
+        <v>5.670580168773047e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.658706154904149e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.86585314944413e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.3649745254694e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.107600117257966e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.632936771544471e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.930205179167467e-07</v>
+        <v>5.656510560206408e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.567427364819262e-07</v>
+        <v>1.192971109353156e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.717677948667371e-07</v>
+        <v>3.608188596215634e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.933874534988121e-07</v>
+        <v>9.873467550937322e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.933874534988121e-07</v>
+        <v>9.873467550937322e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.795768030329382e-07</v>
+        <v>5.688303456690382e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.890933125390752e-07</v>
+        <v>3.618978588581353e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.933874534988121e-07</v>
+        <v>9.873467550937322e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.809511653008765e-07</v>
+        <v>1.371753984378581e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.515092495209962e-07</v>
+        <v>6.116313698446436e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.525009403705531e-07</v>
+        <v>6.655583051175118e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.504719649941047e-08</v>
+        <v>5.743405595698583e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.180555251339389e-08</v>
+        <v>1.211561132287911e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.504719649941046e-08</v>
+        <v>3.636841854713621e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.590084141095882e-08</v>
+        <v>1.002621803886411e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.590084141095882e-08</v>
+        <v>1.002621803886411e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.520293644031196e-08</v>
+        <v>5.773536644705775e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.504719649941046e-08</v>
+        <v>3.636841854713621e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.608347072618096e-08</v>
+        <v>1.002621803886411e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.504719649941047e-08</v>
+        <v>1.392371889360257e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.504719649941046e-08</v>
+        <v>6.208594184984581e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.504719649941046e-08</v>
+        <v>6.755816897615089e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.10514741416204e-08</v>
+        <v>1.930205179167444e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.253897927794259e-08</v>
+        <v>2.567427364819242e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>9.222046342392537e-08</v>
+        <v>1.717677948667329e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.286347269133237e-08</v>
+        <v>2.933874534988092e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.442764116672289e-08</v>
+        <v>2.933874534988092e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.120721408252172e-08</v>
+        <v>3.795768030329285e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.857563758921073e-08</v>
+        <v>2.890933125390701e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.441765714880621e-08</v>
+        <v>2.933874534988092e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.461921849424194e-08</v>
+        <v>9.809511653008676e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.294990548143357e-08</v>
+        <v>3.515092495209807e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.352402193428534e-08</v>
+        <v>4.525009403705516e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.407663557115943e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.402801875925795e-08</v>
+        <v>5.180555251339346e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.407575110472261e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.513286305213256e-08</v>
+        <v>5.590084141095849e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.513286305213256e-08</v>
+        <v>5.590084141095828e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.423237551206089e-08</v>
+        <v>5.520293644031111e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.407663557115943e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.511290979792982e-08</v>
+        <v>5.608347072618061e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.407663557115943e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.407663557115943e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.407663557115943e-08</v>
+        <v>5.504719649940869e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.886143361549724e-08</v>
+        <v>9.105147414161622e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.347419433204388e-07</v>
+        <v>6.253897927794395e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.422081539269602e-07</v>
+        <v>9.222046342392022e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.260050858448053e-07</v>
+        <v>6.286347269133183e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.010481820058196e-07</v>
+        <v>6.44276411667212e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349193447889149e-07</v>
+        <v>9.120721408251659e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.347636048485596e-07</v>
+        <v>9.85756375892065e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.357998790747835e-07</v>
+        <v>6.441765714880502e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.347706605499621e-07</v>
+        <v>6.4619218494241e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.819453236127965e-08</v>
+        <v>6.294990548143253e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.722664246974548e-07</v>
+        <v>6.352402193428424e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.243163960205558e-07</v>
+        <v>7.407663557115692e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.745895115943333e-07</v>
+        <v>7.402801875925536e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.746381505062766e-07</v>
+        <v>7.407575110471977e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.337446266715934e-07</v>
+        <v>7.513286305213135e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.756743961375125e-07</v>
+        <v>7.513286305213135e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.747938683471349e-07</v>
+        <v>7.42323755120575e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.746381284062335e-07</v>
+        <v>7.407663557115692e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.75674402633005e-07</v>
+        <v>7.511290979792806e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.746381284062335e-07</v>
+        <v>7.407663557115692e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.454815283284676e-07</v>
+        <v>7.407663557115692e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.746381284062335e-07</v>
+        <v>7.407663557115692e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.709927100153066e-07</v>
+        <v>9.886143361549422e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.20667328271264e-06</v>
+        <v>1.347419433204359e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.341309731079307e-08</v>
+        <v>1.422081539269573e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.967854867729927e-07</v>
+        <v>1.26005085844803e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.967854867729927e-07</v>
+        <v>1.010481820058177e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.695713428358408e-07</v>
+        <v>1.349193447889126e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.125015593165609e-08</v>
+        <v>1.347636048485543e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.967854867729927e-07</v>
+        <v>1.357998790747813e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.370827874554988e-06</v>
+        <v>1.3477066054996e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.135498401006255e-07</v>
+        <v>9.819453236127904e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.671209314619245e-07</v>
+        <v>1.722664246974507e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.243163960205483e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.745895115943101e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.746381505062679e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.337446266715862e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.756743961375027e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.747938683471167e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.746381284062115e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.756744026329891e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.746381284062115e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.454815283284566e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.746381284062115e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.70992710015306e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.206673282712639e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.34130973107912e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.967854867729919e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.967854867729919e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.69571342835838e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.125015593165551e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.967854867729919e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.370827874554986e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.135498401005895e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.671209314619236e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.641277738043558e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>5.64127773804355e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.190747122219755e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.473720538157054e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.846912122078883e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.846912122078883e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.652893645244476e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.386096008483532e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.846912122078883e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.361951388985484e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.083054883794049e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.617086331283648e-07</v>
+      <c r="D11" t="n">
+        <v>3.473720538156969e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.84691212207887e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.84691212207887e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.652893645244447e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.386096008483457e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.84691212207887e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.36195138898548e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.083054883793686e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.617086331283647e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.430818418219322e-07</v>
+        <v>5.637681633130661e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.021409557848441e-07</v>
+        <v>1.191066013655336e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394058599055381e-07</v>
+        <v>3.219502436090516e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.860452532413253e-07</v>
+        <v>9.836177123087476e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.860452532413253e-07</v>
+        <v>9.836177123087476e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.180869472938011e-07</v>
+        <v>5.658570122696573e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.360056276851484e-07</v>
+        <v>3.228487565601583e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.860452532413253e-07</v>
+        <v>9.836177123087476e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>9.139398838645532e-07</v>
+        <v>1.366160910433905e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.271744490846728e-07</v>
+        <v>6.070197842885954e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.919824820513345e-07</v>
+        <v>6.624532573932971e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1539869067582e-08</v>
+        <v>5.724985559079549e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.942000662450269e-08</v>
+        <v>1.209702118013901e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.153986906758194e-08</v>
+        <v>3.247125571168122e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.167317095285261e-08</v>
+        <v>9.989729580597559e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>5.167317095285262e-08</v>
+        <v>9.989729580597559e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>5.16949729872688e-08</v>
+        <v>5.744173629746042e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.153986906758194e-08</v>
+        <v>3.247125571168122e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.257115760343028e-08</v>
+        <v>9.989729580597559e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>5.153986906758194e-08</v>
+        <v>1.386779030168311e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.153986906758194e-08</v>
+        <v>6.163343044323283e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.153986906758194e-08</v>
+        <v>6.726075322444616e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.823882886917265e-08</v>
+        <v>1.43081841821933e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>5.763740479516209e-08</v>
+        <v>2.021409557848446e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.765329530731227e-08</v>
+        <v>1.394058599055399e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.784280952083274e-08</v>
+        <v>1.860452532413268e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.920877332639862e-08</v>
+        <v>1.860452532413268e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.398354639670263e-08</v>
+        <v>3.18086947293801e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.882808915444292e-08</v>
+        <v>2.360056276851497e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.485973101286379e-08</v>
+        <v>1.860452532413268e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.419023895399402e-08</v>
+        <v>9.139398838645543e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.764273358703846e-08</v>
+        <v>2.271744490846702e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.841024113549502e-08</v>
+        <v>2.919824820513355e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.858610737589773e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.854091973238528e-08</v>
+        <v>4.942000662450278e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.858508035110437e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.942499982982412e-08</v>
+        <v>5.167317095285264e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.942499982982412e-08</v>
+        <v>5.167317095285265e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.874121129558466e-08</v>
+        <v>5.169497298726922e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.858610737589773e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.961739591174622e-08</v>
+        <v>5.257115760343068e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.858610737589773e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.858610737589773e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.858610737589773e-08</v>
+        <v>5.153986906758247e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.11475497724e-08</v>
+        <v>5.823882886917257e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.227538233194209e-07</v>
+        <v>5.763740479516172e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.295753841224727e-07</v>
+        <v>5.765329530731207e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.151442433243396e-07</v>
+        <v>5.784280952083252e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.307357826966711e-08</v>
+        <v>5.920877332639852e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.231307292417553e-07</v>
+        <v>8.398354639670011e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.229756253223444e-07</v>
+        <v>8.882808915444316e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.240069138579188e-07</v>
+        <v>8.485973101286162e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.229818803753225e-07</v>
+        <v>8.419023895399426e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.055632693461026e-08</v>
+        <v>5.764273358703849e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56222711586047e-07</v>
+        <v>5.841024113549504e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.017777755573644e-07</v>
+        <v>6.8586107375899e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.461812024815246e-07</v>
+        <v>6.854091973238643e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.462264092339761e-07</v>
+        <v>6.858508035110544e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.985504458215232e-07</v>
+        <v>6.942499982982529e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.472576715715594e-07</v>
+        <v>6.942499982982529e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.463814940447241e-07</v>
+        <v>6.874121129558588e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.462263901250375e-07</v>
+        <v>6.8586107375899e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.472576786608855e-07</v>
+        <v>6.961739591174733e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.462263901250375e-07</v>
+        <v>6.8586107375899e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.194278356537009e-07</v>
+        <v>6.8586107375899e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.462263901250375e-07</v>
+        <v>6.8586107375899e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.702909729747515e-07</v>
+        <v>9.114754977240107e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.206067817808554e-06</v>
+        <v>1.22753823319421e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.026118776717987e-08</v>
+        <v>1.295753841224734e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.956849416095827e-07</v>
+        <v>1.15144243324342e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.956849416095827e-07</v>
+        <v>9.307357826966811e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.68048048531849e-07</v>
+        <v>1.231307292417582e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.845538807153997e-08</v>
+        <v>1.229756253223463e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.956849416095827e-07</v>
+        <v>1.240069138579197e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.366744791912017e-06</v>
+        <v>1.229818803753229e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.120014577396682e-07</v>
+        <v>9.055632693461136e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.674930865384454e-07</v>
+        <v>1.562227115860493e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.017777755573591e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.461812024815174e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.46226409233969e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.985504458215143e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.472576715715523e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.46381494044717e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.4622639012503e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.472576786608786e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.4622639012503e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.194278356536946e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.4622639012503e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.702909729747518e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.206067817808553e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.026118776718035e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.956849416095833e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.956849416095833e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.680480485318489e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.845538807154046e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.956849416095833e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.36674479191202e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.12001457739655e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.674930865384457e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.627637060433089e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.189412395480074e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.118943640308798e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.821216543456315e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.821216543456315e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.629589539004033e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.045764308194032e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.821216543456317e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.357045268181961e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.050483252354791e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.601261682982879e-07</v>
+      <c r="B11" t="n">
+        <v>5.627637060433098e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.189412395480075e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.118943640308861e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.821216543456325e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.821216543456325e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.629589539004026e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.045764308194096e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.821216543456327e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.357045268181964e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.05048325235466e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.601261682982886e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.152042427132999e-07</v>
+        <v>5.675386293656178e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.347979805044364e-07</v>
+        <v>1.194238182166581e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.967110820847214e-07</v>
+        <v>3.934509557644058e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>3.789229292124395e-07</v>
+        <v>9.905719839168416e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.789229292124395e-07</v>
+        <v>9.905719839168416e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.285558527460869e-07</v>
+        <v>5.713531125990512e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.533757532110297e-07</v>
+        <v>3.948365303330996e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.789229292124395e-07</v>
+        <v>9.905719839168416e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.067811903731846e-06</v>
+        <v>1.376723526153271e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.347613317958937e-07</v>
+        <v>6.151858700034952e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.852416688421908e-07</v>
+        <v>6.677558758867114e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>5.762337499191789e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.467719030070814e-08</v>
+        <v>1.212876074730191e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>3.965431238346044e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.969019451427657e-08</v>
+        <v>1.005809231588387e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.969019451427657e-08</v>
+        <v>1.005809231588387e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.905798412985643e-08</v>
+        <v>5.798741303725172e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>3.965431238346044e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.994365318265718e-08</v>
+        <v>1.005809231588387e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>1.397374049684883e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>6.243873848250998e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.890150842588185e-08</v>
+        <v>6.778934393377085e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.972189792965175e-08</v>
+        <v>2.152042427133002e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.857464483886109e-08</v>
+        <v>2.347979805044366e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.911138403857103e-08</v>
+        <v>1.967110820847218e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.882800142427877e-08</v>
+        <v>3.789229292124818e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.079342249230933e-08</v>
+        <v>3.789229292124818e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.987837363362635e-08</v>
+        <v>4.285558527460899e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.099673539985005e-07</v>
+        <v>3.533757532110323e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.019962602319145e-07</v>
+        <v>3.789229292124818e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.133289734304349e-08</v>
+        <v>1.067811903731848e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.958106085298196e-08</v>
+        <v>4.347613317958941e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.977623178930493e-08</v>
+        <v>3.852416688421913e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.034334157769774e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.028993520033858e-08</v>
+        <v>5.467719030070813e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.034252539623671e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.137817806364325e-08</v>
+        <v>5.969019451427673e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.137817806364325e-08</v>
+        <v>5.969019451427674e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.049981728167229e-08</v>
+        <v>5.905798412985651e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.034334157769774e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.138548633447301e-08</v>
+        <v>5.994365318265728e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.034334157769774e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.034334157769774e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.034334157769774e-08</v>
+        <v>5.890150842588203e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.084190599305007e-07</v>
+        <v>6.972189792965198e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497259654706131e-07</v>
+        <v>6.857464483886334e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.583535720438187e-07</v>
+        <v>6.911138403857123e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.395102884085556e-07</v>
+        <v>6.882800142427918e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.107683340263618e-07</v>
+        <v>7.07934224923097e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.499340834427931e-07</v>
+        <v>6.987837363362657e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.497776077393386e-07</v>
+        <v>1.099673539985007e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.508197524955939e-07</v>
+        <v>1.019962602319148e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.497857357383426e-07</v>
+        <v>7.133289734304354e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.076508036831228e-07</v>
+        <v>6.95810608529821e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.92980069141581e-07</v>
+        <v>6.977623178930505e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.610199290271927e-07</v>
+        <v>8.034334157769803e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.211704969303303e-07</v>
+        <v>8.028993520033886e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.212239291317065e-07</v>
+        <v>8.034252539623696e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.917401733704953e-07</v>
+        <v>8.13781780636435e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.222660418024173e-07</v>
+        <v>8.13781780636435e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.21380379011664e-07</v>
+        <v>8.049981728167251e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.212239033076897e-07</v>
+        <v>8.034334157769803e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.222660480644648e-07</v>
+        <v>8.138548633447331e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.212239033076896e-07</v>
+        <v>8.034334157769803e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.863414950317952e-07</v>
+        <v>8.034334157769803e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.212239033076896e-07</v>
+        <v>8.034334157769803e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.726079164659571e-07</v>
+        <v>1.08419059930501e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.208781072950082e-06</v>
+        <v>1.497259654706137e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.632223986867772e-08</v>
+        <v>1.583535720438192e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.983679767553909e-07</v>
+        <v>1.39510288408556e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.983679767553909e-07</v>
+        <v>1.107683340263622e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.714468849406343e-07</v>
+        <v>1.499340834427936e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.353605425327832e-08</v>
+        <v>1.49777607739339e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.983679767553909e-07</v>
+        <v>1.508197524955944e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.375104276976851e-06</v>
+        <v>1.497857357383431e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.155914714759272e-07</v>
+        <v>1.076508036831232e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.71262584040566e-07</v>
+        <v>1.929800691415816e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.610199290271937e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.211704969303314e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.212239291317073e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.917401733704968e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.222660418024181e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.21380379011665e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.212239033076907e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.222660480644658e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.212239033076907e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.863414950317961e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.212239033076907e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.726079164659568e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.208781072950082e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.632223986867779e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.983679767553911e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.983679767553911e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.714468849406341e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.353605425327838e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.983679767553911e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.375104276976852e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.155914714759277e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.712625840405661e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.658888635895562e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>5.658888635895561e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.192374943306634e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.782899196352931e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.871861892539558e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.871861892539558e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.675186890715066e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.669982608634514e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.871861892539558e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.366590708601562e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.111837013987088e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.647388155952293e-07</v>
+      <c r="D11" t="n">
+        <v>3.782899196352946e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.87186189253956e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.87186189253956e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.675186890715067e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.669982608634525e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.87186189253956e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.366590708601563e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.111837013987097e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.647388155952295e-07</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.212381940206895e-07</v>
+        <v>5.662370087925691e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.260614206980181e-07</v>
+        <v>1.192966814425322e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.447612693967901e-07</v>
+        <v>3.66785951916798e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.91862051901109e-07</v>
+        <v>9.879656526680524e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.91862051901109e-07</v>
+        <v>9.879656526680524e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.239557343130899e-07</v>
+        <v>5.69185328157695e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.939118075106987e-07</v>
+        <v>3.671829365140108e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.91862051901109e-07</v>
+        <v>9.879656526680524e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.708898504316628e-07</v>
+        <v>1.373323344185344e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.749240912159089e-07</v>
+        <v>6.118567687273479e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.042822863572636e-07</v>
+        <v>6.658994323986473e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>5.750173114220162e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.153134762406029e-08</v>
+        <v>1.211706402286987e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>3.700522784949829e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6346332100891e-08</v>
+        <v>1.003368084779299e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6346332100891e-08</v>
+        <v>1.003368084779299e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.603140014959396e-08</v>
+        <v>5.778924003831277e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>3.700522784949829e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.691379750000715e-08</v>
+        <v>1.003368084779299e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>1.394429108212803e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>6.212952411048532e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.587552229371702e-08</v>
+        <v>6.761849263802763e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.508766856880561e-08</v>
+        <v>1.212381940206892e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.40560258876401e-08</v>
+        <v>1.260614206980184e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>9.493330869811857e-08</v>
+        <v>1.447612693967902e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.43581736965718e-08</v>
+        <v>1.918620519011126e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.610924372014991e-08</v>
+        <v>1.918620519011126e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.524354642468225e-08</v>
+        <v>2.239557343130948e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.021521070218844e-07</v>
+        <v>1.939118075107028e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.423385120057319e-08</v>
+        <v>1.918620519011126e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.494778423736623e-08</v>
+        <v>5.70889850431658e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.477994034404842e-08</v>
+        <v>1.749240912159104e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.51379156381825e-08</v>
+        <v>2.042822863572644e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.45341812547392e-08</v>
+        <v>5.587552229371682e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.448391929422184e-08</v>
+        <v>5.153134762405947e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4533564233762e-08</v>
+        <v>5.587552229371681e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.548614878535311e-08</v>
+        <v>5.634633210089134e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.548614878535311e-08</v>
+        <v>5.634633210089135e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.469005911061615e-08</v>
+        <v>5.603140014959321e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.45341812547392e-08</v>
+        <v>5.587552229371682e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.557245646102963e-08</v>
+        <v>5.691379750000742e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.45341812547392e-08</v>
+        <v>5.587552229371682e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.45341812547392e-08</v>
+        <v>5.587552229371682e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.45341812547392e-08</v>
+        <v>5.587552229371682e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.995041764097278e-08</v>
+        <v>6.508766856880529e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.366130199905529e-07</v>
+        <v>6.405602588764061e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.443663376745029e-07</v>
+        <v>9.493330869811222e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.27648543996291e-07</v>
+        <v>6.435817369656998e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.021036889046738e-07</v>
+        <v>6.610924372015072e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.368940375699021e-07</v>
+        <v>6.524354642468255e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.367381597146821e-07</v>
+        <v>1.02152107021884e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.377764349203153e-07</v>
+        <v>9.423385120057723e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.367453894347406e-07</v>
+        <v>9.494778423736512e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.926706645540876e-08</v>
+        <v>6.477994034405038e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.751660323366914e-07</v>
+        <v>6.513791563818261e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.22215173188299e-07</v>
+        <v>7.453418125473967e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.71989824637852e-07</v>
+        <v>7.448391929422203e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.720401076283853e-07</v>
+        <v>7.453356423376237e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.305752681740126e-07</v>
+        <v>7.548614878535399e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.730783567984748e-07</v>
+        <v>7.548614878535399e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.721959644542465e-07</v>
+        <v>7.469005911061638e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.720400865983695e-07</v>
+        <v>7.453418125473967e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.730783618046599e-07</v>
+        <v>7.557245646103043e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.720400865983695e-07</v>
+        <v>7.453418125473967e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.431713449361798e-07</v>
+        <v>7.453418125473967e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.720400865983695e-07</v>
+        <v>7.453418125473967e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.733623917352119e-07</v>
+        <v>9.995041764097173e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.209911892359383e-06</v>
+        <v>1.36613019990551e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.47023800052713e-08</v>
+        <v>1.443663376745007e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9997733689743e-07</v>
+        <v>1.276485439962903e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.9997733689743e-07</v>
+        <v>1.021036889046734e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.737892289414341e-07</v>
+        <v>1.368940375698999e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.392942445161219e-08</v>
+        <v>1.367381597146797e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.9997733689743e-07</v>
+        <v>1.377764349203144e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.382377541671317e-06</v>
+        <v>1.367453894347391e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.182696682963775e-07</v>
+        <v>9.926706645540733e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.729540559041425e-07</v>
+        <v>1.751660323366889e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.222151731883006e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.719898246378543e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.720401076283873e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.305752681740162e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.730783567984777e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.721959644542488e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.720400865983718e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.730783618046628e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.720400865983718e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.431713449361818e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.720400865983718e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.733623917352125e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.209911892359383e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.470238000527146e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.999773368974296e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.999773368974296e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.737892289414354e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.392942445161229e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.999773368974296e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.382377541671312e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.182696682964017e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.729540559041426e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>5.654840150611576e-07</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>1.192150306689498e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.563079208381596e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.864228515761298e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.864228515761298e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.673183720756916e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.531879330335886e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.864228515761298e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.367839843002905e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.1048012345755e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.644293760358327e-07</v>
+      <c r="D11" t="n">
+        <v>3.56307920838159e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.864228515761296e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.864228515761296e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.673183720756934e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.531879330335909e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.864228515761296e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.367839843002902e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.104801234575737e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.644293760358331e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.063842549447389e-07</v>
+        <v>5.64047556156142e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.183990167086199e-07</v>
+        <v>1.190771553743719e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.285320992297899e-07</v>
+        <v>3.21525452137101e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.458122036519497e-07</v>
+        <v>9.835572517733161e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.458122036519497e-07</v>
+        <v>9.835572517733163e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.433825436144048e-07</v>
+        <v>5.655056561865222e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.660258916891127e-07</v>
+        <v>3.218168216250599e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.458122036519497e-07</v>
+        <v>9.835572517733163e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.569173197537269e-07</v>
+        <v>1.365839521660428e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.047173153462742e-07</v>
+        <v>6.066938027105285e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.336452489062934e-07</v>
+        <v>6.622060065343925e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>5.728254541497837e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.685382920138271e-08</v>
+        <v>1.209500274197533e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>3.244153024372456e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.079547830252883e-08</v>
+        <v>9.989584006804992e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>5.079547830252883e-08</v>
+        <v>9.989584006804992e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>5.10548833935304e-08</v>
+        <v>5.742622403498505e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>3.244153024372456e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.194444992421467e-08</v>
+        <v>9.989584006804992e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>1.387196966619715e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>6.161480752403186e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.089736169549811e-08</v>
+        <v>6.725216451456789e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.326769433113294e-08</v>
+        <v>1.063842549447461e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>5.732741985542637e-08</v>
+        <v>1.183990167086218e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.804660080340525e-08</v>
+        <v>1.28532099229797e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.780042445277542e-08</v>
+        <v>1.458122036519623e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.916537128855943e-08</v>
+        <v>1.458122036519623e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.342521602916452e-08</v>
+        <v>1.433825436144067e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>5.827434575887857e-08</v>
+        <v>1.660258916891164e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.431478255984549e-08</v>
+        <v>1.458122036519623e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.915106236207134e-08</v>
+        <v>2.569173197537289e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.775041566355642e-08</v>
+        <v>1.04717315346281e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.823353533258584e-08</v>
+        <v>1.336452489062969e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.690989020548244e-08</v>
+        <v>5.089736169550357e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.686688276882188e-08</v>
+        <v>4.685382920138245e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.690925439389646e-08</v>
+        <v>5.089736169550357e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.767691974059368e-08</v>
+        <v>5.079547830253633e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.767691974059368e-08</v>
+        <v>5.079547830253635e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.706741190350896e-08</v>
+        <v>5.105488339353306e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.690989020548244e-08</v>
+        <v>5.089736169550357e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.795697843420822e-08</v>
+        <v>5.194444992421976e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.690989020548244e-08</v>
+        <v>5.089736169550355e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.690989020548244e-08</v>
+        <v>5.089736169550357e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.690989020548244e-08</v>
+        <v>5.089736169550357e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.919201300142872e-08</v>
+        <v>8.326769433113693e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.201658665659909e-07</v>
+        <v>5.732741985542516e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.269557996416743e-07</v>
+        <v>5.804660080341201e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.127295623219893e-07</v>
+        <v>5.780042445278241e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.106387862607454e-08</v>
+        <v>5.916537128856098e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.206276089019663e-07</v>
+        <v>8.342521602916644e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.204700872043319e-07</v>
+        <v>5.827434575888391e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215171754326559e-07</v>
+        <v>8.43147825598531e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.204762341515339e-07</v>
+        <v>5.915106236207441e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.861100672221165e-08</v>
+        <v>5.775041566355502e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.531426510564072e-07</v>
+        <v>5.823353533259006e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.978429250086042e-07</v>
+        <v>6.690989020548403e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.414617555158043e-07</v>
+        <v>6.686688276882276e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.415047793673568e-07</v>
+        <v>6.690925439390063e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.929366945686355e-07</v>
+        <v>6.767691974059418e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.425518458548013e-07</v>
+        <v>6.767691974059418e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.416622846504925e-07</v>
+        <v>6.706741190351348e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.415047629524601e-07</v>
+        <v>6.690989020548403e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.425518511811844e-07</v>
+        <v>6.795697843420014e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.415047629524601e-07</v>
+        <v>6.690989020548403e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1620692947856e-07</v>
+        <v>6.690989020548403e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.415047629524601e-07</v>
+        <v>6.690989020548403e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.714605312138724e-07</v>
+        <v>8.919201300142965e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.207822696639414e-06</v>
+        <v>1.201658665659925e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.046675125959589e-08</v>
+        <v>1.269557996416757e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.966126915387463e-07</v>
+        <v>1.127295623219911e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.966126915387463e-07</v>
+        <v>9.10638786260819e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.720011509307645e-07</v>
+        <v>1.206276089019664e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.990478520057553e-08</v>
+        <v>1.204700872043333e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.966126915387463e-07</v>
+        <v>1.215171754326532e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.382353241751081e-06</v>
+        <v>1.204762341515394e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.147606327686469e-07</v>
+        <v>8.861100672221491e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.707206256930864e-07</v>
+        <v>1.531426510564064e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.978429250086063e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.414617555158053e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.415047793673531e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.929366945686363e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.425518458548192e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.416622846504962e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.415047629524668e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.425518511811827e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.415047629524668e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.162069294785594e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.415047629524668e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.714605312138744e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.207822696639414e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.046675125959657e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.966126915387465e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.966126915387465e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.720011509307665e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.990478520057686e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.966126915387465e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.382353241751082e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.147606327686483e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.707206256930867e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.634265118705507e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.190008250608654e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.125401448268678e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.824899466384874e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.824899466384874e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.644768532951726e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.102745508374571e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.824899466384874e-07</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>5.634265118705517e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.190008250608653e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.125401448268463e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.824899466384878e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.824899466384878e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.644768532951744e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.102745508374699e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.824899466384878e-07</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.363635611409167e-06</v>
       </c>
-      <c r="K9" t="n">
-        <v>6.060625119644004e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.613865369439522e-07</v>
+      <c r="K11" t="n">
+        <v>6.060625119644017e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.613865369439546e-07</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.766439132527104e-07</v>
+        <v>5.671606403022356e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.413678465215281e-07</v>
+        <v>1.190971591527794e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.713561481769581e-07</v>
+        <v>3.832397080798664e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.833018930098737e-07</v>
+        <v>9.894776201936939e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.833018930098737e-07</v>
+        <v>9.894776201936939e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.788642494698229e-07</v>
+        <v>5.704437200674446e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.319996164058604e-07</v>
+        <v>3.846925328796507e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.833018930098737e-07</v>
+        <v>9.894776201936939e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.075410452094659e-06</v>
+        <v>1.375978883898679e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.457565485923295e-07</v>
+        <v>6.13893637568479e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.170563873745565e-07</v>
+        <v>6.671212725339871e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>5.758943020965815e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.401011315913781e-08</v>
+        <v>1.209662285087115e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>3.864780309666122e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.880685631910287e-08</v>
+        <v>1.004806524248226e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.880685631910288e-08</v>
+        <v>1.004806524248226e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.834732931642254e-08</v>
+        <v>5.79007149574819e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>3.864780309666122e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.922378259203625e-08</v>
+        <v>1.004806524248226e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>1.396611880407082e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>6.231764309578917e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.819255721649891e-08</v>
+        <v>6.773183735949649e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.867648054411592e-08</v>
+        <v>1.766439132527106e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.746471193613842e-08</v>
+        <v>1.413678465216945e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.812483156189691e-08</v>
+        <v>1.71356148176958e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.770204611319154e-08</v>
+        <v>2.83301893009886e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.970273529214852e-08</v>
+        <v>2.83301893009886e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.883125264404026e-08</v>
+        <v>3.788642494698351e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084199255763948e-07</v>
+        <v>3.319996164058599e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.970770591965319e-08</v>
+        <v>2.83301893009886e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0275163422341e-08</v>
+        <v>1.075410452094663e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.844764490078654e-08</v>
+        <v>3.457565485923293e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.872685578030791e-08</v>
+        <v>3.170563873745555e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.901987278427973e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.896519312413112e-08</v>
+        <v>5.401011315940928e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.90190478535386e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.000630718976026e-08</v>
+        <v>5.880685631910277e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.000630718976026e-08</v>
+        <v>5.880685631910285e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.917464488420591e-08</v>
+        <v>5.834732931642446e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.901987278427973e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.005109815981638e-08</v>
+        <v>5.922378259203626e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.901987278427973e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.901987278427973e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.901987278427973e-08</v>
+        <v>5.819255721649832e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.066421794516439e-07</v>
+        <v>6.867648054411536e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.470600016577727e-07</v>
+        <v>6.7464711936329e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.555482139878804e-07</v>
+        <v>6.812483156189533e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.37071435652843e-07</v>
+        <v>6.770204611319104e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0893117704377e-07</v>
+        <v>6.970273529214844e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.473036568718545e-07</v>
+        <v>6.883125264404162e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.471488847724625e-07</v>
+        <v>1.084199255763958e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.48180110147464e-07</v>
+        <v>6.970770591965315e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47156845361491e-07</v>
+        <v>7.027516342233903e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.058897466156914e-07</v>
+        <v>6.844764490078738e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.894615254674287e-07</v>
+        <v>6.872685578030823e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.582722815894848e-07</v>
+        <v>7.901987278427861e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.177823389851836e-07</v>
+        <v>7.896519312408784e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.178370436901968e-07</v>
+        <v>7.901904785353726e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.876047021830071e-07</v>
+        <v>8.00063071897603e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.188682375697604e-07</v>
+        <v>8.00063071897603e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.179917907452577e-07</v>
+        <v>7.917464488420467e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.178370186453317e-07</v>
+        <v>7.901987278427861e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188682440208687e-07</v>
+        <v>8.005109815981635e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.178370186453317e-07</v>
+        <v>7.901987278427861e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.833249866001696e-07</v>
+        <v>7.901987278427861e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.178370186453317e-07</v>
+        <v>7.901987278427861e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.731203115254553e-07</v>
+        <v>1.066421794516435e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.207655281151202e-06</v>
+        <v>1.470600016579983e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.588885666679946e-08</v>
+        <v>1.555482139878811e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>1.370714356528429e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>1.089311770437701e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.716820257315586e-07</v>
+        <v>1.473036568718518e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.295371791897287e-08</v>
+        <v>1.471488847724633e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.995396310036016e-07</v>
+        <v>1.481801101474636e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.374163132589592e-06</v>
+        <v>1.4715684536149e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.164160213516872e-07</v>
+        <v>1.05889746615692e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.720383972943355e-07</v>
+        <v>1.89461525467427e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.582722815894853e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.177823389852175e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.178370436901945e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.876047021830076e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.18868237569761e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.179917907452572e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.178370186453307e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.188682440208682e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.178370186453307e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.833249866001693e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.178370186453307e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.731203115254545e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.207655281151325e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.588885666679957e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.995396310036012e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.995396310036012e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.71682025731558e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.295371791897258e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.995396310036012e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.374163132589594e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.164160213516864e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.720383972943354e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.658984657521902e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.190058398340923e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.706864139015897e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>5.658984657521888e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.190058398341034e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.706864139015914e-08</v>
+      </c>
+      <c r="E11" t="n">
         <v>9.87081166982797e-07</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>9.87081166982797e-07</v>
       </c>
-      <c r="G9" t="n">
-        <v>5.671107653749761e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.587842638614432e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>5.671107653749763e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.587842638614401e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>9.87081166982797e-07</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.365764632101806e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.108176296535097e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.647188664909147e-07</v>
+      <c r="J11" t="n">
+        <v>1.365764632101807e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.108176296535087e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.647188664909146e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.192091674977141e-07</v>
+        <v>5.660400507480904e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.247027282163956e-07</v>
+        <v>1.187130652047124e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.387546650531634e-07</v>
+        <v>3.493220971711358e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.615920838866202e-07</v>
+        <v>9.84583903005182e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.615920838866202e-07</v>
+        <v>9.84583903005182e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.557269304225903e-07</v>
+        <v>5.669004461583835e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.842228356563971e-07</v>
+        <v>3.496867707773618e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.615920838866202e-07</v>
+        <v>9.84583903005182e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.843754977457573e-07</v>
+        <v>1.370010736205663e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.208092184787571e-07</v>
+        <v>6.085063773375018e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.437148963108124e-07</v>
+        <v>6.644002287149156e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>5.7482621187942e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.020022798751849e-08</v>
+        <v>1.205785608033107e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>3.524473847943676e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.43800985512418e-08</v>
+        <v>9.999743699357097e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>5.43800985512418e-08</v>
+        <v>9.999743699357097e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>5.445872872385419e-08</v>
+        <v>5.756563839432995e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>3.524473847943676e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.534157225054588e-08</v>
+        <v>9.999743699357097e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>1.391507991450942e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>6.179619311990586e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.430262303189468e-08</v>
+        <v>6.747314978809368e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.930709787768919e-08</v>
+        <v>1.192091674977138e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.151841977814088e-08</v>
+        <v>1.247027282163941e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.213881420755608e-08</v>
+        <v>1.387546650531626e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.182455998805922e-08</v>
+        <v>1.615920838866178e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.339805742715181e-08</v>
+        <v>1.615920838866178e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.256218390779653e-08</v>
+        <v>1.557269304225941e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.82295221324243e-08</v>
+        <v>1.842228356563915e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.034604709634041e-08</v>
+        <v>1.615920838866178e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.349894146124716e-08</v>
+        <v>1.843754977457548e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>6.19003990991755e-08</v>
+        <v>1.208092184787553e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.245560620281571e-08</v>
+        <v>1.43714896310811e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.164802921030026e-08</v>
+        <v>5.430262303189517e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.160177829017387e-08</v>
+        <v>5.02002279875162e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.164739164225624e-08</v>
+        <v>5.430262303189517e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.247703354358823e-08</v>
+        <v>5.438009855124192e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.247703354358823e-08</v>
+        <v>5.438009855124192e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.180413490225972e-08</v>
+        <v>5.445872872385312e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.164802921030026e-08</v>
+        <v>5.430262303189517e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.268697842895163e-08</v>
+        <v>5.534157225054555e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.164802921030026e-08</v>
+        <v>5.430262303189504e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.164802921030026e-08</v>
+        <v>5.430262303189517e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.164802921030026e-08</v>
+        <v>5.430262303189517e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.579391058065327e-08</v>
+        <v>8.930709787768814e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.300917762300014e-07</v>
+        <v>6.151841977813891e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.374930922295569e-07</v>
+        <v>6.213881420755652e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.21751893330259e-07</v>
+        <v>6.182455998805888e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.780278609652614e-08</v>
+        <v>6.339805742715112e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.304876041014371e-07</v>
+        <v>6.256218390779642e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.303314984102224e-07</v>
+        <v>9.822952213242112e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.313704476281305e-07</v>
+        <v>9.034604709633985e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.303382859202198e-07</v>
+        <v>6.349894146124682e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.515235716463732e-08</v>
+        <v>6.190039909917636e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.664088967782661e-07</v>
+        <v>6.245560620281454e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.180134272130519e-07</v>
+        <v>7.164802921030021e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.668001939874137e-07</v>
+        <v>7.160177829017369e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.668464629631826e-07</v>
+        <v>7.164739164225722e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.242376709447958e-07</v>
+        <v>7.247703354358901e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.67885388929781e-07</v>
+        <v>7.247703354358901e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.670025505994996e-07</v>
+        <v>7.180413490226015e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.668464449075401e-07</v>
+        <v>7.164802921030021e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.678853941261913e-07</v>
+        <v>7.268697842895231e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.668464449075401e-07</v>
+        <v>7.164802921030021e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.053569542877197e-07</v>
+        <v>7.164802921030021e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.668464449075401e-07</v>
+        <v>7.164802921030021e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.732000418764524e-07</v>
+        <v>9.57939105806506e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.204002895071936e-06</v>
+        <v>1.300917762299945e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>3.306609632214669e-08</v>
+        <v>1.374930922295537e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.972925179877173e-07</v>
+        <v>1.217518933302559e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.972925179877173e-07</v>
+        <v>9.780278609652545e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.73147261342595e-07</v>
+        <v>1.304876041014362e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>3.235724206135201e-08</v>
+        <v>1.303314984102203e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.972925179877173e-07</v>
+        <v>1.313704476281276e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.388388126497967e-06</v>
+        <v>1.303382859202192e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.162288991409264e-07</v>
+        <v>9.5152357164636e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.727582248273278e-07</v>
+        <v>1.66408896778263e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.180134272130479e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.6680019398741e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.668464629631792e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.242376709447921e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.678853889297782e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.670025505994964e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.668464449075373e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.678853941261886e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.668464449075373e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.053569542877163e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.668464449075373e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.732000418764522e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.204002895071936e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.3066096322146e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.972925179877171e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.972925179877171e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.731472613425923e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.235724206135207e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.972925179877171e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.388388126497966e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.162288991409066e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.727582248273277e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.653001382144455e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.186319511968625e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.394092059262611e-08</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>5.653001382144434e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.186319511968622e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.394092059262558e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.833636518222894e-07</v>
+      </c>
+      <c r="F11" t="n">
         <v>9.833636518222896e-07</v>
       </c>
-      <c r="F9" t="n">
-        <v>9.833636518222898e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.657587873789652e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.365485700560279e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>5.657587873789626e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.36548570056022e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>9.833636518222896e-07</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1.368591187709639e-06</v>
       </c>
-      <c r="K9" t="n">
-        <v>6.077178422282167e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.635023831870757e-07</v>
+      <c r="K11" t="n">
+        <v>6.077178422281963e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.635023831870749e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.040361738924173e-07</v>
+        <v>5.647522666054482e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.145327242796077e-07</v>
+        <v>1.182840415472235e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.212428010142886e-07</v>
+        <v>3.014201624811896e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.231161287571173e-07</v>
+        <v>9.807107781946193e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.231161287571173e-07</v>
+        <v>9.807107781946193e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.246154643426332e-07</v>
+        <v>5.633202305112611e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.616074575865177e-07</v>
+        <v>3.017492922523352e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.231161287571173e-07</v>
+        <v>9.807107781946193e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.524220233465196e-07</v>
+        <v>1.36259846505508e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.034287307375535e-07</v>
+        <v>6.038675742278659e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27654792445132e-07</v>
+        <v>6.606510833020116e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>5.735498962136975e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.520825789954435e-08</v>
+        <v>1.201453286976436e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>3.041340717542965e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.886966049801326e-08</v>
+        <v>9.96099021445901e-07</v>
       </c>
       <c r="F3" t="n">
-        <v>4.886966049801326e-08</v>
+        <v>9.96099021445901e-07</v>
       </c>
       <c r="G3" t="n">
-        <v>4.917350386852396e-08</v>
+        <v>5.720694802645621e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>3.041340717542965e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.006397443029897e-08</v>
+        <v>9.96099021445901e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>1.384028459997982e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>6.13284178507201e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9015660827161e-08</v>
+        <v>6.709540832530677e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.89116575557484e-08</v>
+        <v>1.040361738924203e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>5.444411954825284e-08</v>
+        <v>1.145327242796028e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.495246523737716e-08</v>
+        <v>1.212428010142922e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.502327228638657e-08</v>
+        <v>1.231161287571208e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.621780388441656e-08</v>
+        <v>1.231161287571208e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.540118880190661e-08</v>
+        <v>1.246154643426617e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.53503046374019e-08</v>
+        <v>1.616074575865221e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.629165936368181e-08</v>
+        <v>1.231161287571208e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.961516885990191e-08</v>
+        <v>1.524220233465279e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.469134720318144e-08</v>
+        <v>1.034287307375545e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.52721789985838e-08</v>
+        <v>1.276547924451344e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.387840617640007e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.383805168143252e-08</v>
+        <v>4.520825789954631e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.3877732636991e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.462740723869482e-08</v>
+        <v>4.886966049801391e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.462740723869482e-08</v>
+        <v>4.886966049801392e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.40362492177633e-08</v>
+        <v>4.917350386852373e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.387840617640007e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.492671977953814e-08</v>
+        <v>5.006397443029953e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.387840617640007e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.387840617640007e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.387840617640007e-08</v>
+        <v>4.901566082716156e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.483023114426748e-08</v>
+        <v>7.891165755575686e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.134264453581543e-07</v>
+        <v>5.444411954825382e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.197428865616892e-07</v>
+        <v>5.495246523737894e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.06636538731128e-07</v>
+        <v>5.50232722863936e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.661700396360167e-08</v>
+        <v>5.621780388442004e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.139046825000017e-07</v>
+        <v>5.540118880190823e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.137468394591592e-07</v>
+        <v>8.535030463740251e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.147951530617766e-07</v>
+        <v>5.629165936369503e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.137525223263661e-07</v>
+        <v>7.961516885990359e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4293090304792e-08</v>
+        <v>5.469134720318417e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.439526547433406e-07</v>
+        <v>5.527217899858675e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.943341286111013e-07</v>
+        <v>6.387840617640333e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.371636747043149e-07</v>
+        <v>6.383805168143612e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.372040440025183e-07</v>
+        <v>6.387773263699382e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.877233058471781e-07</v>
+        <v>6.462740723870562e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.382523375007545e-07</v>
+        <v>6.462740723870562e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.373618722406455e-07</v>
+        <v>6.403624921776712e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.372040291992829e-07</v>
+        <v>6.387840617640333e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.382523428024205e-07</v>
+        <v>6.492671977955277e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.372040291992829e-07</v>
+        <v>6.387840617640333e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.113572971631082e-07</v>
+        <v>6.387840617640333e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372040291992829e-07</v>
+        <v>6.387840617640333e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.722201809973941e-07</v>
+        <v>8.483023114426849e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.199846452612409e-06</v>
+        <v>1.134264453581557e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.859360368627557e-08</v>
+        <v>1.19742886561691e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.942787850283561e-07</v>
+        <v>1.066365387311291e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>9.942787850283559e-07</v>
+        <v>8.661700396360139e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.702305827206363e-07</v>
+        <v>1.139046825000016e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.795110563859556e-08</v>
+        <v>1.137468394591609e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>9.942787850283561e-07</v>
+        <v>1.147951530617802e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.381583323909194e-06</v>
+        <v>1.13752522326368e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>6.119052460771187e-07</v>
+        <v>8.429309030479346e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.692590912163308e-07</v>
+        <v>1.439526547433425e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.943341286111153e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.371636747043343e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.372040440025368e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.877233058471794e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.382523375007645e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.373618722406624e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.372040291993008e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.382523428024354e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.372040291993008e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.113572971631238e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.372040291993008e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.722201809973961e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.19984645261241e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.859360368627643e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.942787850283574e-07</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.942787850283574e-07</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.702305827206378e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.795110563859621e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>9.942787850283574e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.381583323909197e-06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.119052460771288e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.692590912163317e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.641472419444777e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>5.641472419444797e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.182109300715925e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>2.931399986118411e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9.798825648238867e-07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9.798825648238867e-07</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.624835262685559e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.905457417908417e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9.798825648238865e-07</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.361485920342495e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.03240155577775e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.59879856523677e-07</v>
+      <c r="D11" t="n">
+        <v>2.931399986118464e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.798825648238876e-07</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.798825648238876e-07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.624835262685574e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.905457417908486e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.798825648238876e-07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.361485920342498e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.032401555777855e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.598798565236776e-07</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.560961347220154e-07</v>
+        <v>9.574544616950983e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.531020946357708e-07</v>
+        <v>1.193286903039039e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.777235679896101e-07</v>
+        <v>9.573618753261894e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.531020946357708e-07</v>
+        <v>1.193286903039039e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.531020946357708e-07</v>
+        <v>1.193286903039039e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.231272119052914e-07</v>
+        <v>9.579317199315759e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.942039671588025e-07</v>
+        <v>9.57552440411214e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.531020946357708e-07</v>
+        <v>1.193286903039039e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6847649846852e-06</v>
+        <v>9.619476598018141e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>6.344568638617068e-07</v>
+        <v>9.57756473357804e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.237044952111568e-07</v>
+        <v>9.579860247764498e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>6.739745089518433e-08</v>
+        <v>1.21141910164922e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>6.859087087664941e-08</v>
+        <v>1.21141910164922e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.859087087664941e-08</v>
+        <v>1.21141910164922e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.516383999953777e-08</v>
+        <v>9.721676737420065e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>6.780933812941657e-08</v>
+        <v>1.21141910164922e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>6.469637756763342e-08</v>
+        <v>9.721834987467663e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.109268070118658e-08</v>
+        <v>3.560961347220139e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.373158931371561e-08</v>
+        <v>6.531020946357728e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.940792583449993e-08</v>
+        <v>2.777235679896089e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.198894315522424e-08</v>
+        <v>6.531020946357728e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.425617879239839e-08</v>
+        <v>6.531020946357728e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.156014313309141e-08</v>
+        <v>8.231272119052832e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.181091731686728e-07</v>
+        <v>4.942039671588017e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.130006635147276e-07</v>
+        <v>6.531020946357728e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.400887522797715e-08</v>
+        <v>4.6847649846852e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>8.082121162776701e-08</v>
+        <v>6.344568638617075e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>8.107175938146669e-08</v>
+        <v>9.237044952111545e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.676423622620881e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.987719678799418e-08</v>
+        <v>6.739745089518423e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.676277835290108e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.011301921084399e-08</v>
+        <v>6.859087087664941e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.011301921084399e-08</v>
+        <v>6.859087087664944e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.723169865811522e-08</v>
+        <v>6.516383999953645e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.676423622620881e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.987719678799418e-08</v>
+        <v>6.780933812941657e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.676423622620881e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.676423622620881e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.676423622620881e-08</v>
+        <v>6.469637756763073e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.130123491631609e-07</v>
+        <v>8.109268070118446e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.561264561695398e-07</v>
+        <v>8.373158931371558e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.610248846178504e-07</v>
+        <v>7.940792583449823e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.452259628581426e-07</v>
+        <v>8.198894315522416e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.175274007191998e-07</v>
+        <v>8.425617879239834e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.532464711462347e-07</v>
+        <v>8.156014313309006e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.527790087144907e-07</v>
+        <v>1.181091731686702e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.558919692761132e-07</v>
+        <v>1.130006635147269e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.527868238719605e-07</v>
+        <v>8.400887522797475e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.122736630564397e-07</v>
+        <v>8.082121162776585e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.943186097291797e-07</v>
+        <v>8.107175938146416e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.832825809701797e-07</v>
+        <v>8.67642362262086e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.50793192725847e-07</v>
+        <v>8.987719678799414e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.476802580091096e-07</v>
+        <v>8.676277835289845e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.25106722427119e-07</v>
+        <v>9.011301921084394e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.507931785745977e-07</v>
+        <v>9.011301921084394e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.481476945959678e-07</v>
+        <v>8.723169865811401e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.47680232164061e-07</v>
+        <v>8.67642362262086e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.50793192725847e-07</v>
+        <v>8.987719678799414e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.47680232164061e-07</v>
+        <v>8.67642362262086e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.10367991023557e-07</v>
+        <v>8.67642362262086e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.47680232164061e-07</v>
+        <v>8.67642362262086e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.652894570132564e-07</v>
+        <v>1.130123491631605e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.197373097715513e-06</v>
+        <v>1.561264561695397e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.672328457073107e-07</v>
+        <v>1.610248846178498e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.197373097715513e-06</v>
+        <v>1.452259628581427e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.197373097715513e-06</v>
+        <v>1.175274007192e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.550233233214011e-07</v>
+        <v>1.532464711462339e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.634073528195456e-07</v>
+        <v>1.52779008714488e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.197373097715513e-06</v>
+        <v>1.558919692761135e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.719132496815183e-07</v>
+        <v>1.527868238719592e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.589739079474148e-07</v>
+        <v>1.122736630564385e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.544258566348248e-07</v>
+        <v>1.943186097291792e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.832825809701788e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.507931927258474e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.476802580091086e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.251067224271193e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.507931785745978e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.481476945959669e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.476802321640613e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.507931927258474e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.476802321640613e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.103679910235567e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.476802321640613e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.652894570132547e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.197373097715513e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.672328457073092e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.197373097715513e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.197373097715513e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.550233233213998e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.634073528195446e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.197373097715513e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.719132496815185e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.589739079474127e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.544258566348244e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.543176507363441e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.186895926487244e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.551093124164421e-07</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.186895926487244e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.186895926487244e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.501309858543978e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.535592660464116e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.186895926487244e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.163243769348039e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.517460674476312e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.540295713763993e-07</v>
+      <c r="B11" t="n">
+        <v>9.543176507363431e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.186895926487243e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.551093124164417e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.186895926487243e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.186895926487243e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.501309858543966e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.535592660464103e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.186895926487243e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.163243769348021e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.517460674476306e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.540295713763987e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.96882518903275e-07</v>
+        <v>9.526858914229067e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.648617551279038e-07</v>
+        <v>1.188250251688427e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.595006678443473e-07</v>
+        <v>9.527593364864497e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.648617551279038e-07</v>
+        <v>1.188250251688427e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.648617551279038e-07</v>
+        <v>1.188250251688427e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.293924905039628e-07</v>
+        <v>9.53185678504453e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.454916584920233e-07</v>
+        <v>9.529318081667518e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.648617551279038e-07</v>
+        <v>1.188250251688427e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.992482381813276e-06</v>
+        <v>9.569240941436426e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>5.233694574212839e-07</v>
+        <v>9.53101147041956e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.016135369881468e-06</v>
+        <v>9.535567013676563e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.78898048930949e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.905329070027208e-08</v>
+        <v>1.206367220757105e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.788980489309484e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>6.013712750401053e-08</v>
+        <v>1.206367220757105e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.013712750401053e-08</v>
+        <v>1.206367220757105e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.83575586340884e-08</v>
+        <v>9.675194197979636e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.788980489309484e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>6.100391111263299e-08</v>
+        <v>1.206367220757105e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.788980489309484e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.788980489309484e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.788980489309484e-08</v>
+        <v>9.675241287955606e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.223961580027786e-08</v>
+        <v>1.968825189032801e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.465229649753343e-08</v>
+        <v>5.648617551279049e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.077614941218253e-08</v>
+        <v>2.595006678443492e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.327949749368423e-08</v>
+        <v>5.648617551279049e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.518674242454324e-08</v>
+        <v>5.648617551279049e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.27073695412703e-08</v>
+        <v>6.293924905039635e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02786123981065e-07</v>
+        <v>4.454916584920242e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.903948623511201e-08</v>
+        <v>5.648617551279049e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.461748556370915e-08</v>
+        <v>3.992482381813273e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.20605166862033e-08</v>
+        <v>5.233694574212832e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.214723458764035e-08</v>
+        <v>1.016135369881467e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.567383277576567e-08</v>
+        <v>5.788980489309554e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.878793899530292e-08</v>
+        <v>5.905329070027207e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.567300907109315e-08</v>
+        <v>5.788980489309551e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.853469720658342e-08</v>
+        <v>6.013712750401043e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.853469720658342e-08</v>
+        <v>6.013712750401048e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.61415865167575e-08</v>
+        <v>5.835755863408795e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.567383277576565e-08</v>
+        <v>5.788980489309551e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.878793899530292e-08</v>
+        <v>6.100391111263293e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.567383277576565e-08</v>
+        <v>5.788980489309551e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.567383277576565e-08</v>
+        <v>5.788980489309551e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.567383277576565e-08</v>
+        <v>5.788980489309551e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.725220178247119e-08</v>
+        <v>7.223961580027764e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.321476151567021e-07</v>
+        <v>7.465229649753357e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.359079900658169e-07</v>
+        <v>7.0776149412182e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.234167309458514e-07</v>
+        <v>7.327949749368416e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.012306140696218e-07</v>
+        <v>7.518674242454321e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.297368352354861e-07</v>
+        <v>7.270736954127103e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2926908149473e-07</v>
+        <v>1.027861239810656e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.323831877140313e-07</v>
+        <v>9.903948623511193e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.292753736309903e-07</v>
+        <v>7.461748556370978e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.665747181245772e-08</v>
+        <v>7.20605166862029e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.627133894713955e-07</v>
+        <v>7.214723458764052e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.352757505984569e-07</v>
+        <v>7.567383277576511e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.904964125100596e-07</v>
+        <v>7.878793899530289e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.873823245087657e-07</v>
+        <v>7.567300907109274e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.506262729053701e-07</v>
+        <v>7.853469720658331e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.904963993062336e-07</v>
+        <v>7.853469720658332e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.878500600315146e-07</v>
+        <v>7.614158651675805e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.873823062905219e-07</v>
+        <v>7.567383277576511e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.904964125100596e-07</v>
+        <v>7.878793899530289e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.873823062905219e-07</v>
+        <v>7.567383277576511e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.57191570946824e-07</v>
+        <v>7.567383277576511e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.873823062905219e-07</v>
+        <v>7.567383277576511e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.640460749733561e-07</v>
+        <v>9.72522017824708e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.193267196643413e-06</v>
+        <v>1.321476151567018e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.625094516832e-07</v>
+        <v>1.359079900658174e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.193267196643413e-06</v>
+        <v>1.23416730945851e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.193267196643413e-06</v>
+        <v>1.012306140696216e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.535361665197506e-07</v>
+        <v>1.297368352354859e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.590571061370843e-07</v>
+        <v>1.292690814947298e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.193267196643413e-06</v>
+        <v>1.32383187714031e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.759450991640328e-07</v>
+        <v>1.292753736309901e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.553557572828945e-07</v>
+        <v>9.665747181245733e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.461286957975017e-07</v>
+        <v>1.627133894713955e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.352757505984563e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.904964125100597e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.873823245087656e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.506262729053703e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.904963993062336e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.878500600315144e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.873823062905221e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.904964125100597e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.873823062905221e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.571915709468235e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.873823062905221e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.640460749733553e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.193267196643413e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.625094516831996e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.193267196643413e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.193267196643413e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.535361665197505e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.590571061370848e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.193267196643413e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.75945099164032e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.553557572828939e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.461286957975016e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.511033658499048e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.511033658499036e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.182289698969399e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>9.50477642419499e-07</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>9.504776424194967e-07</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.182289698969399e-06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.182289698969399e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.468232537008815e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.490792858743459e-07</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.468232537008818e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.490792858743449e-07</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.182289698969399e-06</v>
       </c>
-      <c r="J9" t="n">
-        <v>9.15255343816247e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.475644992253956e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.499295850418879e-07</v>
+      <c r="J11" t="n">
+        <v>9.152553438162463e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.475644992253941e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.49929585041887e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.398673500217687e-07</v>
+        <v>9.499122161147989e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.149853463913446e-07</v>
+        <v>1.185603614472129e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.044001452929825e-07</v>
+        <v>9.499901626124535e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.149853463913446e-07</v>
+        <v>1.185603614472129e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.149853463913446e-07</v>
+        <v>1.185603614472129e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.116727542545785e-07</v>
+        <v>9.503541219261199e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.253182447689098e-07</v>
+        <v>9.500926120778374e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.149853463913446e-07</v>
+        <v>1.185603614472129e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.664070906609955e-06</v>
+        <v>9.537209497308386e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.838220254220429e-07</v>
+        <v>9.501144097826728e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.477901850501563e-07</v>
+        <v>9.499496449795949e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.482968786320244e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.393665913020965e-08</v>
+        <v>1.203615546285684e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.482968786320245e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.509325620716298e-08</v>
+        <v>1.203615546285684e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.509325620716265e-08</v>
+        <v>1.203615546285684e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.52968900591708e-08</v>
+        <v>9.64659071934979e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.482968786320245e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>5.794023501666312e-08</v>
+        <v>1.203615546285684e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.482968786320276e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.482968786320245e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.482968786320245e-08</v>
+        <v>9.646600967384037e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.841196973265275e-08</v>
+        <v>2.398673500217664e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.072951036821657e-08</v>
+        <v>6.149853463913462e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.721175376257896e-08</v>
+        <v>3.044001452929869e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.954237899580934e-08</v>
+        <v>6.149853463913462e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.136784127795004e-08</v>
+        <v>6.149853463913462e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.112258075132704e-08</v>
+        <v>6.11672754254573e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.737653416716348e-08</v>
+        <v>4.253182447689158e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.152251688611336e-08</v>
+        <v>6.149853463913462e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.465651852040449e-08</v>
+        <v>3.664070906609969e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.809283467624117e-08</v>
+        <v>3.838220254220492e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.844769381149515e-08</v>
+        <v>3.477901850501601e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.130587891965345e-08</v>
+        <v>5.482968786320071e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.441642607311499e-08</v>
+        <v>5.393665913020779e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.130547512987725e-08</v>
+        <v>5.482968786320044e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.357047423991138e-08</v>
+        <v>5.509325620716157e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.357047423991138e-08</v>
+        <v>5.509325620716189e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.177308111561904e-08</v>
+        <v>5.529689005917186e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.130587891965099e-08</v>
+        <v>5.482968786320044e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.441642607311499e-08</v>
+        <v>5.794023501666169e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.130587891965099e-08</v>
+        <v>5.482968786320044e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.130587891965099e-08</v>
+        <v>5.482968786320044e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.130587891965099e-08</v>
+        <v>5.482968786320044e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.182134390365132e-08</v>
+        <v>6.841196973265682e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.239315618911902e-07</v>
+        <v>7.072951036821398e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.278042716320734e-07</v>
+        <v>6.721175376258132e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.15866577273776e-07</v>
+        <v>6.954237899580768e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.537219187795266e-08</v>
+        <v>7.136784127795034e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.220916136326189e-07</v>
+        <v>9.11225807513167e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.216244114368915e-07</v>
+        <v>9.737653416716951e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.247349585901088e-07</v>
+        <v>7.152251688610919e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.21630268509551e-07</v>
+        <v>9.465651852040833e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.126773663012678e-08</v>
+        <v>6.809283467624554e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.527562074898265e-07</v>
+        <v>6.844769381150119e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.14870024999973e-07</v>
+        <v>7.130587891965948e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.649821829130071e-07</v>
+        <v>7.441642607312039e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.618716535945782e-07</v>
+        <v>7.130547512987996e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.192210467329465e-07</v>
+        <v>7.357047423991582e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.649821712938558e-07</v>
+        <v>7.357047423991582e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.623388379555166e-07</v>
+        <v>7.177308111562887e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.618716357595513e-07</v>
+        <v>7.130587891965703e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.649821829130071e-07</v>
+        <v>7.441642607312039e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.618716357595513e-07</v>
+        <v>7.130587891965703e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.346387253972198e-07</v>
+        <v>7.130587891965703e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.618716357595513e-07</v>
+        <v>7.130587891965703e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.599799500439619e-07</v>
+        <v>9.182134390365494e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.188974659142723e-06</v>
+        <v>1.239315618911946e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.583496963008539e-07</v>
+        <v>1.27804271632079e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.188974659142723e-06</v>
+        <v>1.158665772737761e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.188974659142723e-06</v>
+        <v>9.537219187795642e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.507636413010064e-07</v>
+        <v>1.220916136326213e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.563610203375728e-07</v>
+        <v>1.216244114368942e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.188974659142723e-06</v>
+        <v>1.247349585901126e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.808188356371144e-07</v>
+        <v>1.216302685095538e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.557518307159811e-07</v>
+        <v>9.126773663013111e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.592810371159182e-07</v>
+        <v>1.527562074898308e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.148700250000005e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.649821829130296e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.61871653594584e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.192210467329749e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.649821712938777e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.623388379555393e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.61871635759577e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.649821829130296e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.61871635759577e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.346387253972419e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.61871635759577e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.599799500439629e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.188974659142725e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.583496963008545e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.188974659142725e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.188974659142725e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.507636413010097e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.563610203375735e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.188974659142725e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.808188356371153e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.557518307159823e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.592810371159182e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.477827344540849e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.178941964164342e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.47118910303314e-07</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.178941964164342e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.178941964164342e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.440316567055506e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.46316505867871e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.178941964164342e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.15572908743504e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.460611203535095e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.475021557093153e-07</v>
+      <c r="B11" t="n">
+        <v>9.477827344540867e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.178941964164344e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.471189103033148e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.178941964164344e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.178941964164344e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.440316567055519e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.463165058678723e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.178941964164344e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.155729087435058e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.460611203535105e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.475021557093169e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.969081520027119e-07</v>
+        <v>9.527152047372971e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.229367595232679e-07</v>
+        <v>1.187498621999372e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.01870148461933e-07</v>
+        <v>9.526057197044397e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.229367595232679e-07</v>
+        <v>1.187498621999372e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.229367595232679e-07</v>
+        <v>1.187498621999372e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.20110569713143e-07</v>
+        <v>9.529292175234419e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.883587143939523e-07</v>
+        <v>9.526734106979384e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.229367595232679e-07</v>
+        <v>1.187498621999372e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>4.138392858270229e-06</v>
+        <v>9.56590633313185e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>5.752498235558042e-07</v>
+        <v>9.529331955642375e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.899771097310247e-07</v>
+        <v>9.540029883002731e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.835053698114722e-08</v>
+        <v>1.205827181727742e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.968801715928843e-08</v>
+        <v>1.205827181727742e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.968801715928843e-08</v>
+        <v>1.205827181727742e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.906513040302742e-08</v>
+        <v>9.672961411697066e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>6.167724093411508e-08</v>
+        <v>1.205827181727742e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.860391420115953e-08</v>
+        <v>9.673348391586348e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.818588126255276e-08</v>
+        <v>3.969081520027083e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.487557007779525e-08</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.004180843924457e-07</v>
+        <v>3.018701484619327e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.349245999633191e-08</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.57837055596455e-08</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.864709746442068e-08</v>
+        <v>6.201105697131447e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>7.289238984156112e-08</v>
+        <v>3.883587143939522e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.012592079955082e-07</v>
+        <v>4.229367595232682e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.031350439096029e-07</v>
+        <v>4.138392858270238e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.278185614642487e-08</v>
+        <v>5.752498235558038e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.296101933718987e-08</v>
+        <v>4.899771097310245e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.730533202570351e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.037865875865906e-08</v>
+        <v>5.835053698114727e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.730467390312982e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.984454206426349e-08</v>
+        <v>5.968801715928851e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.984454206426349e-08</v>
+        <v>5.968801715928851e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.776654822757143e-08</v>
+        <v>5.906513040302746e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.730533202570351e-08</v>
+        <v>5.860391420115956e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.037865875865906e-08</v>
+        <v>6.167724093411508e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.730533202570351e-08</v>
+        <v>5.860391420115954e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.730533202570351e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.730533202570351e-08</v>
+        <v>5.860391420115953e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.008789276429572e-07</v>
+        <v>9.818588126255281e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.381277104199426e-07</v>
+        <v>7.487557007779536e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.427492372831629e-07</v>
+        <v>1.004180843924457e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.286972101252929e-07</v>
+        <v>7.349245999633197e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.047333015808153e-07</v>
+        <v>7.578370555964555e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.360194694207556e-07</v>
+        <v>9.86470974644207e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.355582532190531e-07</v>
+        <v>7.289238984156118e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.386315799518434e-07</v>
+        <v>1.012592079955083e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.355650685893203e-07</v>
+        <v>1.03135043909603e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.002347413745347e-07</v>
+        <v>7.278185614642491e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.71783708519735e-07</v>
+        <v>7.29610193371899e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.688713720580461e-07</v>
+        <v>7.73053320257036e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.334981371173818e-07</v>
+        <v>8.03786587586591e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.30424835222462e-07</v>
+        <v>7.73046739031299e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.045295091840248e-07</v>
+        <v>7.984454206426356e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.33498126660318e-07</v>
+        <v>7.984454206426355e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.308860265862942e-07</v>
+        <v>7.776654822757153e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.304248103844264e-07</v>
+        <v>7.73053320257036e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.334981371173818e-07</v>
+        <v>8.03786587586591e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.304248103844264e-07</v>
+        <v>7.73053320257036e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.947605169258928e-07</v>
+        <v>7.73053320257036e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.304248103844264e-07</v>
+        <v>7.73053320257036e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.592860285960914e-07</v>
+        <v>1.008789276429573e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.197246761700717e-06</v>
+        <v>1.381277104199426e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.615840604008908e-07</v>
+        <v>1.42749237283163e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.197246761700717e-06</v>
+        <v>1.28697210125293e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.197246761700717e-06</v>
+        <v>1.047333015808154e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.540161238500723e-07</v>
+        <v>1.360194694207558e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.602995891377649e-07</v>
+        <v>1.355582532190533e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.197246761700717e-06</v>
+        <v>1.386315799518435e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.787647980285468e-07</v>
+        <v>1.355650685893205e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.547308973190734e-07</v>
+        <v>1.002347413745348e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.585900382977381e-07</v>
+        <v>1.71783708519735e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.688713720580457e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.334981371173814e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.30424835222462e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.045295091840249e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.334981266603178e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.308860265862939e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.304248103844258e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.334981371173814e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.304248103844258e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.947605169258926e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.304248103844258e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.592860285960914e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.197246761700717e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.615840604008912e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.197246761700717e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.197246761700717e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.540161238500728e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.602995891377649e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.197246761700717e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.787647980285456e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.547308973190732e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.585900382977381e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.490529702813021e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.1835945035429e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.499890970430212e-07</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.1835945035429e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.1835945035429e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.46886767322105e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.49472349518431e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.1835945035429e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.162909823430207e-07</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>9.490529702813019e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.183594503542899e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.499890970430214e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.183594503542899e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.183594503542899e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.468867673221045e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.494723495184304e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.183594503542899e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.162909823430205e-07</v>
+      </c>
+      <c r="K11" t="n">
         <v>9.471983618608578e-07</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.487761319377584e-07</v>
+      <c r="L11" t="n">
+        <v>9.487761319377587e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.727870798792148e-07</v>
+        <v>9.484135298051107e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>1.183254777514252e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.156547014459426e-07</v>
+        <v>9.488724400337986e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>1.183254777514252e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>1.183254777514252e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.747169855348011e-07</v>
+        <v>9.490178559178587e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35491897180326e-07</v>
+        <v>9.485953615571427e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.108427244839814e-07</v>
+        <v>1.183254777514252e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.469979481970671e-06</v>
+        <v>9.511558399547098e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.253197565402293e-07</v>
+        <v>9.487390271471925e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.629948173332121e-07</v>
+        <v>9.488525331463982e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.399713790114897e-08</v>
+        <v>1.201364923240383e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.502038858557962e-08</v>
+        <v>1.201364923240383e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.502038858557964e-08</v>
+        <v>1.201364923240383e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.44062373388678e-08</v>
+        <v>9.631903767200131e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>5.701291601858967e-08</v>
+        <v>1.201364923240383e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.394559492253218e-08</v>
+        <v>9.632223403618144e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.701236142214727e-08</v>
+        <v>1.72787079879215e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.76026266387942e-08</v>
+        <v>5.10842724483981e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.475188252241868e-08</v>
+        <v>5.156547014459424e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.664750893541327e-08</v>
+        <v>5.10842724483981e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.833029116893819e-08</v>
+        <v>5.10842724483981e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.747300383848288e-08</v>
+        <v>6.747169855348136e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.284810059040936e-08</v>
+        <v>3.354918971803259e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.007968251820468e-08</v>
+        <v>5.10842724483981e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.729345154843855e-08</v>
+        <v>2.469979481970666e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.463714951648977e-08</v>
+        <v>4.253197565402294e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.543294855959434e-08</v>
+        <v>5.629948173332111e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.973763256699557e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.280495366305301e-08</v>
+        <v>5.3997137901149e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.973703541565837e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.224148344778336e-08</v>
+        <v>5.502038858557969e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.224148344778336e-08</v>
+        <v>5.502038858557967e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.019827498333105e-08</v>
+        <v>5.440623733886794e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.973763256699557e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.280495366305301e-08</v>
+        <v>5.701291601858968e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.973763256699557e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.973763256699557e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.973763256699557e-08</v>
+        <v>5.394559492253242e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.913781908831215e-08</v>
+        <v>8.701236142214753e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.198409192926174e-07</v>
+        <v>6.760262663879399e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.231479776751524e-07</v>
+        <v>6.475188252241886e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.121940777571658e-07</v>
+        <v>6.664750893541327e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.276227641757617e-08</v>
+        <v>6.833029116893818e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.177675716117383e-07</v>
+        <v>8.747300383848288e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.173069291953869e-07</v>
+        <v>9.284810059040934e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.203742502914601e-07</v>
+        <v>9.007968251820472e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.173124651593436e-07</v>
+        <v>6.72934515484386e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.861456341171146e-08</v>
+        <v>6.463714951648988e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46731920098e-07</v>
+        <v>6.543294855959438e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.304213879858237e-07</v>
+        <v>6.973763256699573e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.848220774795364e-07</v>
+        <v>7.280495366305299e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.817547815942712e-07</v>
+        <v>6.973703541565845e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.440597097362104e-07</v>
+        <v>7.224148344778333e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.848220701027336e-07</v>
+        <v>7.224148344778333e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.822153987998146e-07</v>
+        <v>7.019827498333117e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.81754756383479e-07</v>
+        <v>6.973763256699573e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.848220774795364e-07</v>
+        <v>7.280495366305299e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.81754756383479e-07</v>
+        <v>6.973763256699573e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.520120117357413e-07</v>
+        <v>6.973763256699573e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.81754756383479e-07</v>
+        <v>6.973763256699573e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.602895140529453e-07</v>
+        <v>8.913781908831219e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.189484380474567e-06</v>
+        <v>1.198409192926174e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.506776638253948e-07</v>
+        <v>1.231479776751527e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.189484380474567e-06</v>
+        <v>1.121940777571657e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.189484380474567e-06</v>
+        <v>9.276227641757609e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.470008697156016e-07</v>
+        <v>1.177675716117384e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.56607616333855e-07</v>
+        <v>1.173069291953869e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.189484380474567e-06</v>
+        <v>1.203742502914601e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.032896156218805e-07</v>
+        <v>1.173124651593437e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.534778560225705e-07</v>
+        <v>8.861456341171129e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.512750444352987e-07</v>
+        <v>1.467319200979998e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.304213879858237e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.84822077479536e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.817547815942711e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.440597097362102e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.848220701027332e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.822153987998141e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.81754756383479e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.84822077479536e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.81754756383479e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.520120117357412e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.81754756383479e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.602895140529449e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.189484380474567e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.506776638253955e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.189484380474567e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.189484380474567e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.470008697156019e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.566076163338557e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.189484380474567e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.032896156218809e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.534778560225699e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.512750444352988e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.47079084488212e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.470790844882128e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.177849092694762e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>9.431645722322156e-07</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>9.431645722322161e-07</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.177849092694762e-06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.177849092694762e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.416515786379547e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.455856410445466e-07</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.416515786379539e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.455856410445471e-07</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.177849092694762e-06</v>
       </c>
-      <c r="J9" t="n">
-        <v>9.238862592037781e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.44305255719007e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.434164754260609e-07</v>
+      <c r="J11" t="n">
+        <v>9.238862592037787e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.443052557190067e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.434164754260611e-07</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.820193323740743e-07</v>
+        <v>9.464945257107696e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.553456445086482e-07</v>
+        <v>1.18185162025044e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.113338851792235e-07</v>
+        <v>9.467856463616413e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.553456445086482e-07</v>
+        <v>1.18185162025044e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.553456445086482e-07</v>
+        <v>1.18185162025044e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.080152697677398e-07</v>
+        <v>9.470290389341958e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.978107569365758e-07</v>
+        <v>9.467252107067874e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.553456445086482e-07</v>
+        <v>1.18185162025044e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.045317346214749e-06</v>
+        <v>9.486707375319755e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.218609484135249e-07</v>
+        <v>9.466809543305618e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.263753521252685e-07</v>
+        <v>9.468712949610896e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.268930812069968e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.303252058156921e-08</v>
+        <v>1.199766908045379e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.268930812069954e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.395905034587939e-08</v>
+        <v>1.199766908045379e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.395905034587955e-08</v>
+        <v>1.199766908045379e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.315811105959145e-08</v>
+        <v>9.612777770481106e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.268930812069954e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>5.580792028958744e-08</v>
+        <v>1.199766908045379e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.268930812069968e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.268930812069954e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.268930812069954e-08</v>
+        <v>9.612659709706352e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.340284777611611e-08</v>
+        <v>1.820193323740749e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>6.61873111385171e-08</v>
+        <v>6.553456445086617e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.275322720317952e-08</v>
+        <v>4.113338851792241e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.534783775919145e-08</v>
+        <v>6.553456445086617e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>6.65627668906208e-08</v>
+        <v>6.553456445086617e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.387165071500716e-08</v>
+        <v>6.080152697677406e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.889001148127561e-08</v>
+        <v>3.978107569365766e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>6.652145994500238e-08</v>
+        <v>6.553456445086617e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>6.517224100358432e-08</v>
+        <v>2.045317346214746e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.261093872624563e-08</v>
+        <v>3.218609484135256e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.357429231382466e-08</v>
+        <v>5.263753521252704e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.760390411068579e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.072251627957083e-08</v>
+        <v>5.303252058156963e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.760330230693187e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.015231055228657e-08</v>
+        <v>5.395905034587972e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.015231055228657e-08</v>
+        <v>5.395905034587971e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.807270704957717e-08</v>
+        <v>5.31581110595914e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.760390411068579e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.072251627957083e-08</v>
+        <v>5.580792028958775e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.760390411068579e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.760390411068579e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.760390411068579e-08</v>
+        <v>5.268930812069895e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.571017254152637e-08</v>
+        <v>6.340284777611313e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.14396023237509e-07</v>
+        <v>6.618731113851712e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.172311479368932e-07</v>
+        <v>6.275322720317977e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.073137769005118e-07</v>
+        <v>6.534783775919302e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>8.931655356741844e-08</v>
+        <v>6.656276689062053e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.122864052446007e-07</v>
+        <v>6.387165071500561e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.118176023055843e-07</v>
+        <v>8.889001148127736e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.149362144745968e-07</v>
+        <v>6.652145994500189e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.118227331044246e-07</v>
+        <v>6.517224100358637e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.522521363453061e-08</v>
+        <v>6.261093872624685e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.390889957084236e-07</v>
+        <v>6.357429231382482e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.114822788659384e-07</v>
+        <v>6.760390411068616e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.607471375482758e-07</v>
+        <v>7.072251627957508e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.576285450506026e-07</v>
+        <v>6.760330230693142e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.139989364887197e-07</v>
+        <v>7.01523105522875e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607471304603112e-07</v>
+        <v>7.01523105522875e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.580973283182691e-07</v>
+        <v>6.807270704957872e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.576285253793717e-07</v>
+        <v>6.760390411068616e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.607471375482758e-07</v>
+        <v>7.072251627957508e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.576285253793717e-07</v>
+        <v>6.760390411068616e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.298064500273388e-07</v>
+        <v>6.760390411068616e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.576285253793717e-07</v>
+        <v>6.760390411068616e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.580715571454843e-07</v>
+        <v>8.57101725415269e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.184255866847178e-06</v>
+        <v>1.143960232375075e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.519747947008151e-07</v>
+        <v>1.172311479368943e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.184255866847178e-06</v>
+        <v>1.073137769005133e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.184255866847178e-06</v>
+        <v>8.931655356741947e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.471969044752906e-07</v>
+        <v>1.122864052446012e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.533902824056246e-07</v>
+        <v>1.118176023055833e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.184255866847178e-06</v>
+        <v>1.149362144745977e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>9.128451095632968e-07</v>
+        <v>1.11822733104425e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.5417186305174e-07</v>
+        <v>8.522521363452938e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.57611705178006e-07</v>
+        <v>1.390889957084209e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.114822788659346e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.607471375482682e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.576285450506061e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.139989364887204e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.607471304603102e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.580973283182718e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.576285253793795e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.607471375482682e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.576285253793794e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.29806450027343e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.576285253793794e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.580715571454843e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.184255866847178e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.519747947008154e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.184255866847178e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.184255866847178e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.471969044752905e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.533902824056244e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.184255866847178e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.128451095632975e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.541718630517406e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.576117051780065e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.450410572403335e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.174794047074501e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.425581315496524e-07</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.174794047074501e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.174794047074501e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.406221970404845e-07</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>9.450410572403331e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.174794047074503e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.425581315496513e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.174794047074503e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.174794047074503e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.406221970404834e-07</v>
+      </c>
+      <c r="H11" t="n">
         <v>9.431417473113774e-07</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.174794047074501e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.26639091283507e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.434531126198849e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.448565393588741e-07</v>
+      <c r="I11" t="n">
+        <v>1.174794047074503e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.266390912835072e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.434531126198838e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.448565393588733e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.062226543567983e-07</v>
+        <v>9.558387546622519e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>6.671049605677918e-07</v>
+        <v>1.19139860108342e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.560460404302162e-07</v>
+        <v>9.555483727843639e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>6.671049605677918e-07</v>
+        <v>1.19139860108342e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671049605677918e-07</v>
+        <v>1.19139860108342e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.718337712660481e-07</v>
+        <v>9.56110707450983e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>4.842551739745278e-07</v>
+        <v>9.557734458669267e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>6.671049605677918e-07</v>
+        <v>1.19139860108342e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.554122772374572e-06</v>
+        <v>9.589808912706405e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>6.244263381076671e-07</v>
+        <v>9.559694377333296e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.609440828698985e-06</v>
+        <v>9.556769666007229e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>6.46573971304709e-08</v>
+        <v>1.20948653918173e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>6.59076819269864e-08</v>
+        <v>1.20948653918173e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.590768192698513e-08</v>
+        <v>1.20948653918173e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.341522600175912e-08</v>
+        <v>9.703600050705497e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>6.606375380082331e-08</v>
+        <v>1.20948653918173e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>6.294723086391605e-08</v>
+        <v>9.70371241166734e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.853735851410221e-08</v>
+        <v>5.062226543567978e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.117223279961612e-08</v>
+        <v>6.671049605677889e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.687313259016731e-08</v>
+        <v>2.560460404301914e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.957374251937661e-08</v>
+        <v>6.671049605677889e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>8.172294182451227e-08</v>
+        <v>6.671049605677889e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.06957117403784e-07</v>
+        <v>7.718337712660461e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.147616996408689e-07</v>
+        <v>4.842551739745273e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.096056452028476e-07</v>
+        <v>6.671049605677889e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.112431940312976e-07</v>
+        <v>3.554122772374564e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.836832895530363e-08</v>
+        <v>6.244263381076672e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.858523912276958e-08</v>
+        <v>1.60944082869899e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.36736280998535e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.679015103675968e-08</v>
+        <v>6.465739713047127e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.367244904557193e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.675166253060992e-08</v>
+        <v>6.590768192698675e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.675166253060992e-08</v>
+        <v>6.590768192698676e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.414162323769465e-08</v>
+        <v>6.341522600175851e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.36736280998535e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.679015103675968e-08</v>
+        <v>6.606375380082355e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.36736280998535e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.36736280998535e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.36736280998535e-08</v>
+        <v>6.294723086391622e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.08840772433855e-07</v>
+        <v>7.853735851410273e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.497290795650207e-07</v>
+        <v>8.117223279961594e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.544793048037808e-07</v>
+        <v>7.687313259016692e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.39394368685852e-07</v>
+        <v>7.957374251937666e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.131332521529983e-07</v>
+        <v>8.172294182451195e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.471091453686383e-07</v>
+        <v>1.069571174037822e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466411502309154e-07</v>
+        <v>1.147616996408724e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.497576731677019e-07</v>
+        <v>1.096056452028472e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.466485789634877e-07</v>
+        <v>1.112431940312954e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.081386110195886e-07</v>
+        <v>7.836832895530323e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.861268055411417e-07</v>
+        <v>7.858523912277073e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.796060956004609e-07</v>
+        <v>8.367362809985327e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>3.464013585823299e-07</v>
+        <v>8.679015103676053e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.432848615408272e-07</v>
+        <v>8.36724490455722e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.198852831165298e-07</v>
+        <v>8.675166253061032e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.464013468390007e-07</v>
+        <v>8.675166253061032e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.437528307832552e-07</v>
+        <v>8.414162323769551e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.432848356454387e-07</v>
+        <v>8.367362809985327e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>3.464013585823299e-07</v>
+        <v>8.679015103676053e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.432848356454387e-07</v>
+        <v>8.367362809985327e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.063891344691623e-07</v>
+        <v>8.367362809985327e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>3.432848356454387e-07</v>
+        <v>8.367362809985327e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.598131685813158e-07</v>
+        <v>1.088407724338532e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.497290795650209e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.659021162909766e-07</v>
+        <v>1.544793048037804e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.393943686858499e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.13133252152997e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>9.539473993370016e-07</v>
+        <v>1.471091453686372e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.613582117981297e-07</v>
+        <v>1.466411502309141e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.195013134710444e-06</v>
+        <v>1.497576731677022e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.945598358425232e-07</v>
+        <v>1.466485789634858e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.570887758942152e-07</v>
+        <v>1.081386110195878e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.633165030168428e-07</v>
+        <v>1.861268055411395e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.796060956004482e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.464013585823204e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.432848615408192e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.198852831165371e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.464013468389857e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.437528307832553e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.432848356454131e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.464013585823204e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.432848356454131e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.063891344691539e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.432848356454131e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.598131685813156e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.195013134710443e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.65902116290977e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.195013134710443e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.195013134710443e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.539473993370026e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.613582117981294e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.195013134710443e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.945598358425242e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.570887758942139e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.633165030168415e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.510347979893047e-07</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.510347979893053e-07</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.184813155924982e-06</v>
       </c>
-      <c r="D9" t="n">
-        <v>9.535149067236383e-07</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>9.535149067236387e-07</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.184813155924982e-06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.184813155924982e-06</v>
       </c>
-      <c r="G9" t="n">
-        <v>9.4864291953835e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.516724887813892e-07</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>9.486429195383483e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.516724887813908e-07</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.184813155924982e-06</v>
       </c>
-      <c r="J9" t="n">
-        <v>9.244864602515115e-07</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>9.244864602515114e-07</v>
+      </c>
+      <c r="K11" t="n">
         <v>9.499258737056274e-07</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.423686817430942e-07</v>
+      <c r="L11" t="n">
+        <v>9.423686817430953e-07</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.984562540200111e-07</v>
+        <v>9.509258836464646e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>5.679574107153602e-07</v>
+        <v>1.186278685010741e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.579252718966921e-07</v>
+        <v>9.512593869439416e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>5.679574107153602e-07</v>
+        <v>1.186278685010741e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.679574107153602e-07</v>
+        <v>1.186278685010741e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.595927124764963e-07</v>
+        <v>9.514781269305157e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.309112799012073e-07</v>
+        <v>9.510606751707902e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>5.679574107153602e-07</v>
+        <v>1.186278685010741e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.203828208276978e-06</v>
+        <v>9.542802647473307e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.341222405232992e-07</v>
+        <v>9.512301111002474e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>6.446636552686798e-07</v>
+        <v>9.513277224653124e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>5.724101265926706e-08</v>
+        <v>1.204360814778074e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
       <c r="E3" t="n">
-        <v>5.83023243582874e-08</v>
+        <v>1.204360814778074e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.830232435828752e-08</v>
+        <v>1.204360814778074e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.695146291902255e-08</v>
+        <v>9.657230311224722e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>5.958420465312175e-08</v>
+        <v>1.204360814778074e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.648613816354618e-08</v>
+        <v>9.65737133389423e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.2661906582347e-08</v>
+        <v>1.984562540200137e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.209182042453863e-08</v>
+        <v>5.679574107153673e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.874901036778689e-08</v>
+        <v>4.579252718966922e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.088485408614335e-08</v>
+        <v>5.679574107153673e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>7.267811493009117e-08</v>
+        <v>5.679574107153673e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.31272313378234e-08</v>
+        <v>6.595927124764963e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.938523782923468e-08</v>
+        <v>3.309112799012112e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.575997307192285e-08</v>
+        <v>5.679574107153673e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.18305162596268e-08</v>
+        <v>3.203828208276981e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>6.919266782289955e-08</v>
+        <v>4.34122240523301e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.979487387080445e-08</v>
+        <v>6.446636552686848e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.333671928682519e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.643478577640109e-08</v>
+        <v>5.724101265926932e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.333597864569099e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.606582906959206e-08</v>
+        <v>5.83023243582894e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.606582906959206e-08</v>
+        <v>5.830232435828856e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.380204404230186e-08</v>
+        <v>5.695146291902336e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.333671928682519e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.643478577640109e-08</v>
+        <v>5.958420465312239e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.333671928682519e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.333671928682519e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.333671928682519e-08</v>
+        <v>5.648613816354652e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.400845676587244e-08</v>
+        <v>9.266190658235023e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.271386430611285e-07</v>
+        <v>7.209182042453853e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.306864919480096e-07</v>
+        <v>6.874901036778357e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1886759298197e-07</v>
+        <v>7.088485408614574e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.784982542252681e-08</v>
+        <v>7.267811493009141e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.24852575814268e-07</v>
+        <v>9.312723133783544e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.243872510589504e-07</v>
+        <v>9.938523782923512e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.274853175483675e-07</v>
+        <v>9.575997307193095e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.243932212735405e-07</v>
+        <v>7.18305162596269e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.344415507261652e-08</v>
+        <v>6.919266782289996e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.561204418495366e-07</v>
+        <v>6.979487387080253e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.339802182581213e-07</v>
+        <v>7.333671928682546e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.890106407041788e-07</v>
+        <v>7.643478577639824e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.859125977697134e-07</v>
+        <v>7.333597864569649e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.48939489102295e-07</v>
+        <v>7.606582906959511e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.890106322840518e-07</v>
+        <v>7.606582906959511e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8637789897008e-07</v>
+        <v>7.380204404230141e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.859125742146031e-07</v>
+        <v>7.333671928682546e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.890106407041788e-07</v>
+        <v>7.643478577639824e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.859125742146031e-07</v>
+        <v>7.333671928682546e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.558227731265018e-07</v>
+        <v>7.333671928682546e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.859125742146031e-07</v>
+        <v>7.333671928682546e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.621942091671538e-07</v>
+        <v>9.400845676587618e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>1.191094169148413e-06</v>
+        <v>1.271386430611313e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>9.552097875347012e-07</v>
+        <v>1.30686491948016e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.191094169148413e-06</v>
+        <v>1.188675929819761e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.191094169148413e-06</v>
+        <v>9.784982542253051e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.503852576339477e-07</v>
+        <v>1.248525758142725e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.594910966189613e-07</v>
+        <v>1.243872510589543e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>1.191094169148413e-06</v>
+        <v>1.274853175483728e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>8.924718252191167e-07</v>
+        <v>1.243932212735419e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.558285540668295e-07</v>
+        <v>9.344415507262052e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.530545946794414e-07</v>
+        <v>1.561204418495407e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.339802182581227e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.890106407041435e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.859125977697066e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.48939489102286e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.890106322840575e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.86377898970038e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.85912574214588e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.890106407041435e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.85912574214588e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.558227731265034e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.85912574214588e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.621942091671549e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.191094169148416e-06</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.552097875347037e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.191094169148416e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.191094169148416e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.503852576339502e-07</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.594910966189636e-07</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.191094169148416e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.924718252191179e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.558285540668301e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.530545946794442e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.493138418347004e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.180242318970952e-06</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.464694110313804e-07</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.180242318970952e-06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.180242318970952e-06</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.444993911146531e-07</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9.482187085352899e-07</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.180242318970952e-06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.209443160471556e-07</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.46721675931698e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.456009515024878e-07</v>
+      <c r="B11" t="n">
+        <v>9.49313841834704e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.180242318970955e-06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.464694110313839e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.180242318970955e-06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.180242318970955e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.444993911146543e-07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.482187085352918e-07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.180242318970955e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.209443160471583e-07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.467216759316999e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.456009515024898e-07</v>
       </c>
     </row>
   </sheetData>
